--- a/templates/RoadCoda-template-Office-staff.xlsx
+++ b/templates/RoadCoda-template-Office-staff.xlsx
@@ -664,7 +664,7 @@
     <col width="11" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Full Name *</t>
@@ -8730,7 +8730,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Full Name *</t>
@@ -16795,12 +16795,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
@@ -16829,78 +16829,63 @@
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
+          <t>Columns shaded yellow are STRONGLY RECOMMENDED. RoadCoda works without them, but the features listed below stay switched off until they're filled in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
           <t>Some columns are set as text on purpose, so zip codes, store numbers, VINs and toll tags keep every digit. Please don't change them.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Paste values only (Paste Special → Values), so the formatting stays. Don't add title rows above the header or totals below the rows.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Send the finished file back to RoadCoda, or upload it yourself once your office login is set up. Questions: support@roadcoda.com</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Required?</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>What to enter</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Allowed values</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Full Name</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>As it should appear in RoadCoda.</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Donna Reilly</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr"/>
-    </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Full Name</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -16910,12 +16895,12 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Their work email. RoadCoda sends a set-password invitation here, after you confirm.</t>
+          <t>As it should appear in RoadCoda.</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>donna@yourcompany.example.com</t>
+          <t>Donna Reilly</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr"/>
@@ -16923,7 +16908,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Role</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -16933,142 +16918,142 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Sets which screens they get; you can fine-tune each person afterwards on the Users screen.</t>
+          <t>Their work email. RoadCoda sends a set-password invitation here, after you confirm.</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
+          <t>donna@yourcompany.example.com</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Sets which screens they get; you can fine-tune each person afterwards on the Users screen.</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
           <t>Billing</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Owner, Dispatcher, Billing, Safety, Payroll, Accountant</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Super User (Y/N)</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr"/>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Y lets them manage other users and reopen locked invoices and pay weeks.</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>Y, N</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Super User (Y/N)</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr"/>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Job title.</t>
+          <t>Y lets them manage other users and reopen locked invoices and pay weeks.</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Billing Manager</t>
+          <t>N</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr"/>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Y, N</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Employee #</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr"/>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Kept as text.</t>
+          <t>Job title.</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
+          <t>Billing Manager</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Employee #</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr"/>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Kept as text.</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
           <t>00118</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr"/>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr"/>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>OFFICE PAY TAB (optional, red): only if you use RoadCoda's office payroll. Fill it in and upload it yourself from inside RoadCoda (Office payroll screen). Please DON'T email a file with pay rates or salaries to anyone, RoadCoda included.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Column (pay tab)</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B20" s="16" t="inlineStr">
         <is>
           <t>Required?</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>What to enter</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>Allowed values</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Full Name</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>Must match the name on the first tab.</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>Donna Reilly</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr"/>
-    </row>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Full Name</t>
         </is>
       </c>
       <c r="B21" s="18" t="inlineStr">
@@ -17078,12 +17063,12 @@
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>Must match the email on the first tab.</t>
+          <t>Must match the name on the first tab.</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>donna@yourcompany.example.com</t>
+          <t>Donna Reilly</t>
         </is>
       </c>
       <c r="E21" s="18" t="inlineStr"/>
@@ -17091,7 +17076,7 @@
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t>Pay Type</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
@@ -17101,120 +17086,144 @@
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>Hourly or Salary.</t>
+          <t>Must match the email on the first tab.</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
+          <t>donna@yourcompany.example.com</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>Pay Type</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Hourly or Salary.</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
           <t>Hourly</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>Hourly, Salary</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>Hourly Rate</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr"/>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>For hourly staff, dollars per hour.</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="E23" s="18" t="inlineStr"/>
-    </row>
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>Annual Salary</t>
+          <t>Hourly Rate</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr"/>
       <c r="C24" s="18" t="inlineStr">
         <is>
+          <t>For hourly staff, dollars per hour.</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E24" s="18" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>Annual Salary</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr"/>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
           <t>For salaried staff, dollars per year.</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr"/>
-      <c r="E24" s="18" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="D25" s="18" t="inlineStr"/>
+      <c r="E25" s="18" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>Overtime Eligible (Y/N)</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr"/>
-      <c r="C25" s="18" t="inlineStr"/>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr"/>
+      <c r="C26" s="18" t="inlineStr"/>
+      <c r="D26" s="18" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>Y, N</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>Time Entry</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr"/>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>Typed = office types hours; Clock = they clock in on RoadCoda; None = salaried, no hours.</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>Clock</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>Typed, Clock, None</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>Hire Date</t>
+          <t>Time Entry</t>
         </is>
       </c>
       <c r="B27" s="18" t="inlineStr"/>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>MM/DD/YYYY.</t>
+          <t>Typed = office types hours; Clock = they clock in on RoadCoda; None = salaried, no hours.</t>
         </is>
       </c>
       <c r="D27" s="18" t="inlineStr">
         <is>
+          <t>Clock</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>Typed, Clock, None</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Hire Date</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr"/>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>MM/DD/YYYY.</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
           <t>06/01/2022</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr"/>
+      <c r="E28" s="18" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/templates/RoadCoda-template-Office-staff.xlsx
+++ b/templates/RoadCoda-template-Office-staff.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +49,12 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -103,12 +109,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004B2BB8"/>
+        <fgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
+        <fgColor rgb="004B2BB8"/>
       </patternFill>
     </fill>
   </fills>
@@ -138,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -151,34 +157,37 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -269,7 +278,8 @@
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <t>REQUIRED. As it should appear in RoadCoda.
-Example: Donna Reilly</t>
+Example: Donna Reilly
+NEVER include Social Security numbers or bank details. RoadCoda does not store them.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
@@ -315,49 +325,57 @@
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <t>REQUIRED on this tab. Must match the name on the first tab.
-DON'T EMAIL PAY DATA: upload this tab yourself inside RoadCoda.</t>
+DON'T EMAIL PAY DATA: upload this tab yourself inside RoadCoda.
+NEVER include Social Security numbers or bank account / routing numbers.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>REQUIRED on this tab. Must match the email on the first tab.
-DON'T EMAIL PAY DATA: upload this tab yourself inside RoadCoda.</t>
+DON'T EMAIL PAY DATA: upload this tab yourself inside RoadCoda.
+NEVER include Social Security numbers or bank account / routing numbers.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>REQUIRED on this tab. Hourly or Salary.
-DON'T EMAIL PAY DATA: upload this tab yourself inside RoadCoda.</t>
+DON'T EMAIL PAY DATA: upload this tab yourself inside RoadCoda.
+NEVER include Social Security numbers or bank account / routing numbers.</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <t>For hourly staff, dollars per hour.
-DON'T EMAIL PAY DATA: upload this tab yourself inside RoadCoda.</t>
+DON'T EMAIL PAY DATA: upload this tab yourself inside RoadCoda.
+NEVER include Social Security numbers or bank account / routing numbers.</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <t>For salaried staff, dollars per year.
-DON'T EMAIL PAY DATA: upload this tab yourself inside RoadCoda.</t>
+DON'T EMAIL PAY DATA: upload this tab yourself inside RoadCoda.
+NEVER include Social Security numbers or bank account / routing numbers.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">
-DON'T EMAIL PAY DATA: upload this tab yourself inside RoadCoda.</t>
+DON'T EMAIL PAY DATA: upload this tab yourself inside RoadCoda.
+NEVER include Social Security numbers or bank account / routing numbers.</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>Typed = office types hours; Clock = they clock in on RoadCoda; None = salaried, no hours.
-DON'T EMAIL PAY DATA: upload this tab yourself inside RoadCoda.</t>
+DON'T EMAIL PAY DATA: upload this tab yourself inside RoadCoda.
+NEVER include Social Security numbers or bank account / routing numbers.</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>MM/DD/YYYY.
-DON'T EMAIL PAY DATA: upload this tab yourself inside RoadCoda.</t>
+DON'T EMAIL PAY DATA: upload this tab yourself inside RoadCoda.
+NEVER include Social Security numbers or bank account / routing numbers.</t>
       </text>
     </comment>
   </commentList>
@@ -8778,7 +8796,7 @@
       <c r="C2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n"/>
-      <c r="H2" s="14" t="n"/>
+      <c r="H2" s="15" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
@@ -8786,7 +8804,7 @@
       <c r="C3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n"/>
-      <c r="H3" s="14" t="n"/>
+      <c r="H3" s="15" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
@@ -8794,7 +8812,7 @@
       <c r="C4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
-      <c r="H4" s="14" t="n"/>
+      <c r="H4" s="15" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
@@ -8802,7 +8820,7 @@
       <c r="C5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
-      <c r="H5" s="14" t="n"/>
+      <c r="H5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
@@ -8810,7 +8828,7 @@
       <c r="C6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
-      <c r="H6" s="14" t="n"/>
+      <c r="H6" s="15" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
@@ -8818,7 +8836,7 @@
       <c r="C7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="n"/>
-      <c r="H7" s="14" t="n"/>
+      <c r="H7" s="15" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
@@ -8826,7 +8844,7 @@
       <c r="C8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n"/>
-      <c r="H8" s="14" t="n"/>
+      <c r="H8" s="15" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n"/>
@@ -8834,7 +8852,7 @@
       <c r="C9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n"/>
-      <c r="H9" s="14" t="n"/>
+      <c r="H9" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n"/>
@@ -8842,7 +8860,7 @@
       <c r="C10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="n"/>
-      <c r="H10" s="14" t="n"/>
+      <c r="H10" s="15" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
@@ -8850,7 +8868,7 @@
       <c r="C11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n"/>
-      <c r="H11" s="14" t="n"/>
+      <c r="H11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n"/>
@@ -8858,7 +8876,7 @@
       <c r="C12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
       <c r="G12" s="3" t="n"/>
-      <c r="H12" s="14" t="n"/>
+      <c r="H12" s="15" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
@@ -8866,7 +8884,7 @@
       <c r="C13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
       <c r="G13" s="3" t="n"/>
-      <c r="H13" s="14" t="n"/>
+      <c r="H13" s="15" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
@@ -8874,7 +8892,7 @@
       <c r="C14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n"/>
-      <c r="H14" s="14" t="n"/>
+      <c r="H14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
@@ -8882,7 +8900,7 @@
       <c r="C15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n"/>
-      <c r="H15" s="14" t="n"/>
+      <c r="H15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n"/>
@@ -8890,7 +8908,7 @@
       <c r="C16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
-      <c r="H16" s="14" t="n"/>
+      <c r="H16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
@@ -8898,7 +8916,7 @@
       <c r="C17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
-      <c r="H17" s="14" t="n"/>
+      <c r="H17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
@@ -8906,7 +8924,7 @@
       <c r="C18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n"/>
-      <c r="H18" s="14" t="n"/>
+      <c r="H18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -8914,7 +8932,7 @@
       <c r="C19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n"/>
-      <c r="H19" s="14" t="n"/>
+      <c r="H19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
@@ -8922,7 +8940,7 @@
       <c r="C20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
       <c r="G20" s="3" t="n"/>
-      <c r="H20" s="14" t="n"/>
+      <c r="H20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n"/>
@@ -8930,7 +8948,7 @@
       <c r="C21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
       <c r="G21" s="3" t="n"/>
-      <c r="H21" s="14" t="n"/>
+      <c r="H21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n"/>
@@ -8938,7 +8956,7 @@
       <c r="C22" s="3" t="n"/>
       <c r="F22" s="3" t="n"/>
       <c r="G22" s="3" t="n"/>
-      <c r="H22" s="14" t="n"/>
+      <c r="H22" s="15" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
@@ -8946,7 +8964,7 @@
       <c r="C23" s="3" t="n"/>
       <c r="F23" s="3" t="n"/>
       <c r="G23" s="3" t="n"/>
-      <c r="H23" s="14" t="n"/>
+      <c r="H23" s="15" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n"/>
@@ -8954,7 +8972,7 @@
       <c r="C24" s="3" t="n"/>
       <c r="F24" s="3" t="n"/>
       <c r="G24" s="3" t="n"/>
-      <c r="H24" s="14" t="n"/>
+      <c r="H24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n"/>
@@ -8962,7 +8980,7 @@
       <c r="C25" s="3" t="n"/>
       <c r="F25" s="3" t="n"/>
       <c r="G25" s="3" t="n"/>
-      <c r="H25" s="14" t="n"/>
+      <c r="H25" s="15" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
@@ -8970,7 +8988,7 @@
       <c r="C26" s="3" t="n"/>
       <c r="F26" s="3" t="n"/>
       <c r="G26" s="3" t="n"/>
-      <c r="H26" s="14" t="n"/>
+      <c r="H26" s="15" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
@@ -8978,7 +8996,7 @@
       <c r="C27" s="3" t="n"/>
       <c r="F27" s="3" t="n"/>
       <c r="G27" s="3" t="n"/>
-      <c r="H27" s="14" t="n"/>
+      <c r="H27" s="15" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n"/>
@@ -8986,7 +9004,7 @@
       <c r="C28" s="3" t="n"/>
       <c r="F28" s="3" t="n"/>
       <c r="G28" s="3" t="n"/>
-      <c r="H28" s="14" t="n"/>
+      <c r="H28" s="15" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
@@ -8994,7 +9012,7 @@
       <c r="C29" s="3" t="n"/>
       <c r="F29" s="3" t="n"/>
       <c r="G29" s="3" t="n"/>
-      <c r="H29" s="14" t="n"/>
+      <c r="H29" s="15" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n"/>
@@ -9002,7 +9020,7 @@
       <c r="C30" s="3" t="n"/>
       <c r="F30" s="3" t="n"/>
       <c r="G30" s="3" t="n"/>
-      <c r="H30" s="14" t="n"/>
+      <c r="H30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
@@ -9010,7 +9028,7 @@
       <c r="C31" s="3" t="n"/>
       <c r="F31" s="3" t="n"/>
       <c r="G31" s="3" t="n"/>
-      <c r="H31" s="14" t="n"/>
+      <c r="H31" s="15" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n"/>
@@ -9018,7 +9036,7 @@
       <c r="C32" s="3" t="n"/>
       <c r="F32" s="3" t="n"/>
       <c r="G32" s="3" t="n"/>
-      <c r="H32" s="14" t="n"/>
+      <c r="H32" s="15" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n"/>
@@ -9026,7 +9044,7 @@
       <c r="C33" s="3" t="n"/>
       <c r="F33" s="3" t="n"/>
       <c r="G33" s="3" t="n"/>
-      <c r="H33" s="14" t="n"/>
+      <c r="H33" s="15" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n"/>
@@ -9034,7 +9052,7 @@
       <c r="C34" s="3" t="n"/>
       <c r="F34" s="3" t="n"/>
       <c r="G34" s="3" t="n"/>
-      <c r="H34" s="14" t="n"/>
+      <c r="H34" s="15" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n"/>
@@ -9042,7 +9060,7 @@
       <c r="C35" s="3" t="n"/>
       <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="n"/>
-      <c r="H35" s="14" t="n"/>
+      <c r="H35" s="15" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n"/>
@@ -9050,7 +9068,7 @@
       <c r="C36" s="3" t="n"/>
       <c r="F36" s="3" t="n"/>
       <c r="G36" s="3" t="n"/>
-      <c r="H36" s="14" t="n"/>
+      <c r="H36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n"/>
@@ -9058,7 +9076,7 @@
       <c r="C37" s="3" t="n"/>
       <c r="F37" s="3" t="n"/>
       <c r="G37" s="3" t="n"/>
-      <c r="H37" s="14" t="n"/>
+      <c r="H37" s="15" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n"/>
@@ -9066,7 +9084,7 @@
       <c r="C38" s="3" t="n"/>
       <c r="F38" s="3" t="n"/>
       <c r="G38" s="3" t="n"/>
-      <c r="H38" s="14" t="n"/>
+      <c r="H38" s="15" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n"/>
@@ -9074,7 +9092,7 @@
       <c r="C39" s="3" t="n"/>
       <c r="F39" s="3" t="n"/>
       <c r="G39" s="3" t="n"/>
-      <c r="H39" s="14" t="n"/>
+      <c r="H39" s="15" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n"/>
@@ -9082,7 +9100,7 @@
       <c r="C40" s="3" t="n"/>
       <c r="F40" s="3" t="n"/>
       <c r="G40" s="3" t="n"/>
-      <c r="H40" s="14" t="n"/>
+      <c r="H40" s="15" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n"/>
@@ -9090,7 +9108,7 @@
       <c r="C41" s="3" t="n"/>
       <c r="F41" s="3" t="n"/>
       <c r="G41" s="3" t="n"/>
-      <c r="H41" s="14" t="n"/>
+      <c r="H41" s="15" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n"/>
@@ -9098,7 +9116,7 @@
       <c r="C42" s="3" t="n"/>
       <c r="F42" s="3" t="n"/>
       <c r="G42" s="3" t="n"/>
-      <c r="H42" s="14" t="n"/>
+      <c r="H42" s="15" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n"/>
@@ -9106,7 +9124,7 @@
       <c r="C43" s="3" t="n"/>
       <c r="F43" s="3" t="n"/>
       <c r="G43" s="3" t="n"/>
-      <c r="H43" s="14" t="n"/>
+      <c r="H43" s="15" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n"/>
@@ -9114,7 +9132,7 @@
       <c r="C44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
       <c r="G44" s="3" t="n"/>
-      <c r="H44" s="14" t="n"/>
+      <c r="H44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n"/>
@@ -9122,7 +9140,7 @@
       <c r="C45" s="3" t="n"/>
       <c r="F45" s="3" t="n"/>
       <c r="G45" s="3" t="n"/>
-      <c r="H45" s="14" t="n"/>
+      <c r="H45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n"/>
@@ -9130,7 +9148,7 @@
       <c r="C46" s="3" t="n"/>
       <c r="F46" s="3" t="n"/>
       <c r="G46" s="3" t="n"/>
-      <c r="H46" s="14" t="n"/>
+      <c r="H46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n"/>
@@ -9138,7 +9156,7 @@
       <c r="C47" s="3" t="n"/>
       <c r="F47" s="3" t="n"/>
       <c r="G47" s="3" t="n"/>
-      <c r="H47" s="14" t="n"/>
+      <c r="H47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n"/>
@@ -9146,7 +9164,7 @@
       <c r="C48" s="3" t="n"/>
       <c r="F48" s="3" t="n"/>
       <c r="G48" s="3" t="n"/>
-      <c r="H48" s="14" t="n"/>
+      <c r="H48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n"/>
@@ -9154,7 +9172,7 @@
       <c r="C49" s="3" t="n"/>
       <c r="F49" s="3" t="n"/>
       <c r="G49" s="3" t="n"/>
-      <c r="H49" s="14" t="n"/>
+      <c r="H49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n"/>
@@ -9162,7 +9180,7 @@
       <c r="C50" s="3" t="n"/>
       <c r="F50" s="3" t="n"/>
       <c r="G50" s="3" t="n"/>
-      <c r="H50" s="14" t="n"/>
+      <c r="H50" s="15" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n"/>
@@ -9170,7 +9188,7 @@
       <c r="C51" s="3" t="n"/>
       <c r="F51" s="3" t="n"/>
       <c r="G51" s="3" t="n"/>
-      <c r="H51" s="14" t="n"/>
+      <c r="H51" s="15" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n"/>
@@ -9178,7 +9196,7 @@
       <c r="C52" s="3" t="n"/>
       <c r="F52" s="3" t="n"/>
       <c r="G52" s="3" t="n"/>
-      <c r="H52" s="14" t="n"/>
+      <c r="H52" s="15" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n"/>
@@ -9186,7 +9204,7 @@
       <c r="C53" s="3" t="n"/>
       <c r="F53" s="3" t="n"/>
       <c r="G53" s="3" t="n"/>
-      <c r="H53" s="14" t="n"/>
+      <c r="H53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n"/>
@@ -9194,7 +9212,7 @@
       <c r="C54" s="3" t="n"/>
       <c r="F54" s="3" t="n"/>
       <c r="G54" s="3" t="n"/>
-      <c r="H54" s="14" t="n"/>
+      <c r="H54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n"/>
@@ -9202,7 +9220,7 @@
       <c r="C55" s="3" t="n"/>
       <c r="F55" s="3" t="n"/>
       <c r="G55" s="3" t="n"/>
-      <c r="H55" s="14" t="n"/>
+      <c r="H55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n"/>
@@ -9210,7 +9228,7 @@
       <c r="C56" s="3" t="n"/>
       <c r="F56" s="3" t="n"/>
       <c r="G56" s="3" t="n"/>
-      <c r="H56" s="14" t="n"/>
+      <c r="H56" s="15" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n"/>
@@ -9218,7 +9236,7 @@
       <c r="C57" s="3" t="n"/>
       <c r="F57" s="3" t="n"/>
       <c r="G57" s="3" t="n"/>
-      <c r="H57" s="14" t="n"/>
+      <c r="H57" s="15" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n"/>
@@ -9226,7 +9244,7 @@
       <c r="C58" s="3" t="n"/>
       <c r="F58" s="3" t="n"/>
       <c r="G58" s="3" t="n"/>
-      <c r="H58" s="14" t="n"/>
+      <c r="H58" s="15" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n"/>
@@ -9234,7 +9252,7 @@
       <c r="C59" s="3" t="n"/>
       <c r="F59" s="3" t="n"/>
       <c r="G59" s="3" t="n"/>
-      <c r="H59" s="14" t="n"/>
+      <c r="H59" s="15" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n"/>
@@ -9242,7 +9260,7 @@
       <c r="C60" s="3" t="n"/>
       <c r="F60" s="3" t="n"/>
       <c r="G60" s="3" t="n"/>
-      <c r="H60" s="14" t="n"/>
+      <c r="H60" s="15" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n"/>
@@ -9250,7 +9268,7 @@
       <c r="C61" s="3" t="n"/>
       <c r="F61" s="3" t="n"/>
       <c r="G61" s="3" t="n"/>
-      <c r="H61" s="14" t="n"/>
+      <c r="H61" s="15" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n"/>
@@ -9258,7 +9276,7 @@
       <c r="C62" s="3" t="n"/>
       <c r="F62" s="3" t="n"/>
       <c r="G62" s="3" t="n"/>
-      <c r="H62" s="14" t="n"/>
+      <c r="H62" s="15" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n"/>
@@ -9266,7 +9284,7 @@
       <c r="C63" s="3" t="n"/>
       <c r="F63" s="3" t="n"/>
       <c r="G63" s="3" t="n"/>
-      <c r="H63" s="14" t="n"/>
+      <c r="H63" s="15" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n"/>
@@ -9274,7 +9292,7 @@
       <c r="C64" s="3" t="n"/>
       <c r="F64" s="3" t="n"/>
       <c r="G64" s="3" t="n"/>
-      <c r="H64" s="14" t="n"/>
+      <c r="H64" s="15" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n"/>
@@ -9282,7 +9300,7 @@
       <c r="C65" s="3" t="n"/>
       <c r="F65" s="3" t="n"/>
       <c r="G65" s="3" t="n"/>
-      <c r="H65" s="14" t="n"/>
+      <c r="H65" s="15" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n"/>
@@ -9290,7 +9308,7 @@
       <c r="C66" s="3" t="n"/>
       <c r="F66" s="3" t="n"/>
       <c r="G66" s="3" t="n"/>
-      <c r="H66" s="14" t="n"/>
+      <c r="H66" s="15" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n"/>
@@ -9298,7 +9316,7 @@
       <c r="C67" s="3" t="n"/>
       <c r="F67" s="3" t="n"/>
       <c r="G67" s="3" t="n"/>
-      <c r="H67" s="14" t="n"/>
+      <c r="H67" s="15" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n"/>
@@ -9306,7 +9324,7 @@
       <c r="C68" s="3" t="n"/>
       <c r="F68" s="3" t="n"/>
       <c r="G68" s="3" t="n"/>
-      <c r="H68" s="14" t="n"/>
+      <c r="H68" s="15" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n"/>
@@ -9314,7 +9332,7 @@
       <c r="C69" s="3" t="n"/>
       <c r="F69" s="3" t="n"/>
       <c r="G69" s="3" t="n"/>
-      <c r="H69" s="14" t="n"/>
+      <c r="H69" s="15" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n"/>
@@ -9322,7 +9340,7 @@
       <c r="C70" s="3" t="n"/>
       <c r="F70" s="3" t="n"/>
       <c r="G70" s="3" t="n"/>
-      <c r="H70" s="14" t="n"/>
+      <c r="H70" s="15" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n"/>
@@ -9330,7 +9348,7 @@
       <c r="C71" s="3" t="n"/>
       <c r="F71" s="3" t="n"/>
       <c r="G71" s="3" t="n"/>
-      <c r="H71" s="14" t="n"/>
+      <c r="H71" s="15" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n"/>
@@ -9338,7 +9356,7 @@
       <c r="C72" s="3" t="n"/>
       <c r="F72" s="3" t="n"/>
       <c r="G72" s="3" t="n"/>
-      <c r="H72" s="14" t="n"/>
+      <c r="H72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n"/>
@@ -9346,7 +9364,7 @@
       <c r="C73" s="3" t="n"/>
       <c r="F73" s="3" t="n"/>
       <c r="G73" s="3" t="n"/>
-      <c r="H73" s="14" t="n"/>
+      <c r="H73" s="15" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n"/>
@@ -9354,7 +9372,7 @@
       <c r="C74" s="3" t="n"/>
       <c r="F74" s="3" t="n"/>
       <c r="G74" s="3" t="n"/>
-      <c r="H74" s="14" t="n"/>
+      <c r="H74" s="15" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n"/>
@@ -9362,7 +9380,7 @@
       <c r="C75" s="3" t="n"/>
       <c r="F75" s="3" t="n"/>
       <c r="G75" s="3" t="n"/>
-      <c r="H75" s="14" t="n"/>
+      <c r="H75" s="15" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n"/>
@@ -9370,7 +9388,7 @@
       <c r="C76" s="3" t="n"/>
       <c r="F76" s="3" t="n"/>
       <c r="G76" s="3" t="n"/>
-      <c r="H76" s="14" t="n"/>
+      <c r="H76" s="15" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n"/>
@@ -9378,7 +9396,7 @@
       <c r="C77" s="3" t="n"/>
       <c r="F77" s="3" t="n"/>
       <c r="G77" s="3" t="n"/>
-      <c r="H77" s="14" t="n"/>
+      <c r="H77" s="15" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n"/>
@@ -9386,7 +9404,7 @@
       <c r="C78" s="3" t="n"/>
       <c r="F78" s="3" t="n"/>
       <c r="G78" s="3" t="n"/>
-      <c r="H78" s="14" t="n"/>
+      <c r="H78" s="15" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n"/>
@@ -9394,7 +9412,7 @@
       <c r="C79" s="3" t="n"/>
       <c r="F79" s="3" t="n"/>
       <c r="G79" s="3" t="n"/>
-      <c r="H79" s="14" t="n"/>
+      <c r="H79" s="15" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n"/>
@@ -9402,7 +9420,7 @@
       <c r="C80" s="3" t="n"/>
       <c r="F80" s="3" t="n"/>
       <c r="G80" s="3" t="n"/>
-      <c r="H80" s="14" t="n"/>
+      <c r="H80" s="15" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n"/>
@@ -9410,7 +9428,7 @@
       <c r="C81" s="3" t="n"/>
       <c r="F81" s="3" t="n"/>
       <c r="G81" s="3" t="n"/>
-      <c r="H81" s="14" t="n"/>
+      <c r="H81" s="15" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n"/>
@@ -9418,7 +9436,7 @@
       <c r="C82" s="3" t="n"/>
       <c r="F82" s="3" t="n"/>
       <c r="G82" s="3" t="n"/>
-      <c r="H82" s="14" t="n"/>
+      <c r="H82" s="15" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n"/>
@@ -9426,7 +9444,7 @@
       <c r="C83" s="3" t="n"/>
       <c r="F83" s="3" t="n"/>
       <c r="G83" s="3" t="n"/>
-      <c r="H83" s="14" t="n"/>
+      <c r="H83" s="15" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n"/>
@@ -9434,7 +9452,7 @@
       <c r="C84" s="3" t="n"/>
       <c r="F84" s="3" t="n"/>
       <c r="G84" s="3" t="n"/>
-      <c r="H84" s="14" t="n"/>
+      <c r="H84" s="15" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n"/>
@@ -9442,7 +9460,7 @@
       <c r="C85" s="3" t="n"/>
       <c r="F85" s="3" t="n"/>
       <c r="G85" s="3" t="n"/>
-      <c r="H85" s="14" t="n"/>
+      <c r="H85" s="15" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n"/>
@@ -9450,7 +9468,7 @@
       <c r="C86" s="3" t="n"/>
       <c r="F86" s="3" t="n"/>
       <c r="G86" s="3" t="n"/>
-      <c r="H86" s="14" t="n"/>
+      <c r="H86" s="15" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n"/>
@@ -9458,7 +9476,7 @@
       <c r="C87" s="3" t="n"/>
       <c r="F87" s="3" t="n"/>
       <c r="G87" s="3" t="n"/>
-      <c r="H87" s="14" t="n"/>
+      <c r="H87" s="15" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n"/>
@@ -9466,7 +9484,7 @@
       <c r="C88" s="3" t="n"/>
       <c r="F88" s="3" t="n"/>
       <c r="G88" s="3" t="n"/>
-      <c r="H88" s="14" t="n"/>
+      <c r="H88" s="15" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n"/>
@@ -9474,7 +9492,7 @@
       <c r="C89" s="3" t="n"/>
       <c r="F89" s="3" t="n"/>
       <c r="G89" s="3" t="n"/>
-      <c r="H89" s="14" t="n"/>
+      <c r="H89" s="15" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n"/>
@@ -9482,7 +9500,7 @@
       <c r="C90" s="3" t="n"/>
       <c r="F90" s="3" t="n"/>
       <c r="G90" s="3" t="n"/>
-      <c r="H90" s="14" t="n"/>
+      <c r="H90" s="15" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n"/>
@@ -9490,7 +9508,7 @@
       <c r="C91" s="3" t="n"/>
       <c r="F91" s="3" t="n"/>
       <c r="G91" s="3" t="n"/>
-      <c r="H91" s="14" t="n"/>
+      <c r="H91" s="15" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n"/>
@@ -9498,7 +9516,7 @@
       <c r="C92" s="3" t="n"/>
       <c r="F92" s="3" t="n"/>
       <c r="G92" s="3" t="n"/>
-      <c r="H92" s="14" t="n"/>
+      <c r="H92" s="15" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n"/>
@@ -9506,7 +9524,7 @@
       <c r="C93" s="3" t="n"/>
       <c r="F93" s="3" t="n"/>
       <c r="G93" s="3" t="n"/>
-      <c r="H93" s="14" t="n"/>
+      <c r="H93" s="15" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n"/>
@@ -9514,7 +9532,7 @@
       <c r="C94" s="3" t="n"/>
       <c r="F94" s="3" t="n"/>
       <c r="G94" s="3" t="n"/>
-      <c r="H94" s="14" t="n"/>
+      <c r="H94" s="15" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n"/>
@@ -9522,7 +9540,7 @@
       <c r="C95" s="3" t="n"/>
       <c r="F95" s="3" t="n"/>
       <c r="G95" s="3" t="n"/>
-      <c r="H95" s="14" t="n"/>
+      <c r="H95" s="15" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n"/>
@@ -9530,7 +9548,7 @@
       <c r="C96" s="3" t="n"/>
       <c r="F96" s="3" t="n"/>
       <c r="G96" s="3" t="n"/>
-      <c r="H96" s="14" t="n"/>
+      <c r="H96" s="15" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n"/>
@@ -9538,7 +9556,7 @@
       <c r="C97" s="3" t="n"/>
       <c r="F97" s="3" t="n"/>
       <c r="G97" s="3" t="n"/>
-      <c r="H97" s="14" t="n"/>
+      <c r="H97" s="15" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n"/>
@@ -9546,7 +9564,7 @@
       <c r="C98" s="3" t="n"/>
       <c r="F98" s="3" t="n"/>
       <c r="G98" s="3" t="n"/>
-      <c r="H98" s="14" t="n"/>
+      <c r="H98" s="15" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n"/>
@@ -9554,7 +9572,7 @@
       <c r="C99" s="3" t="n"/>
       <c r="F99" s="3" t="n"/>
       <c r="G99" s="3" t="n"/>
-      <c r="H99" s="14" t="n"/>
+      <c r="H99" s="15" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n"/>
@@ -9562,7 +9580,7 @@
       <c r="C100" s="3" t="n"/>
       <c r="F100" s="3" t="n"/>
       <c r="G100" s="3" t="n"/>
-      <c r="H100" s="14" t="n"/>
+      <c r="H100" s="15" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n"/>
@@ -9570,7 +9588,7 @@
       <c r="C101" s="3" t="n"/>
       <c r="F101" s="3" t="n"/>
       <c r="G101" s="3" t="n"/>
-      <c r="H101" s="14" t="n"/>
+      <c r="H101" s="15" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n"/>
@@ -9578,7 +9596,7 @@
       <c r="C102" s="3" t="n"/>
       <c r="F102" s="3" t="n"/>
       <c r="G102" s="3" t="n"/>
-      <c r="H102" s="14" t="n"/>
+      <c r="H102" s="15" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n"/>
@@ -9586,7 +9604,7 @@
       <c r="C103" s="3" t="n"/>
       <c r="F103" s="3" t="n"/>
       <c r="G103" s="3" t="n"/>
-      <c r="H103" s="14" t="n"/>
+      <c r="H103" s="15" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n"/>
@@ -9594,7 +9612,7 @@
       <c r="C104" s="3" t="n"/>
       <c r="F104" s="3" t="n"/>
       <c r="G104" s="3" t="n"/>
-      <c r="H104" s="14" t="n"/>
+      <c r="H104" s="15" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n"/>
@@ -9602,7 +9620,7 @@
       <c r="C105" s="3" t="n"/>
       <c r="F105" s="3" t="n"/>
       <c r="G105" s="3" t="n"/>
-      <c r="H105" s="14" t="n"/>
+      <c r="H105" s="15" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n"/>
@@ -9610,7 +9628,7 @@
       <c r="C106" s="3" t="n"/>
       <c r="F106" s="3" t="n"/>
       <c r="G106" s="3" t="n"/>
-      <c r="H106" s="14" t="n"/>
+      <c r="H106" s="15" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n"/>
@@ -9618,7 +9636,7 @@
       <c r="C107" s="3" t="n"/>
       <c r="F107" s="3" t="n"/>
       <c r="G107" s="3" t="n"/>
-      <c r="H107" s="14" t="n"/>
+      <c r="H107" s="15" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n"/>
@@ -9626,7 +9644,7 @@
       <c r="C108" s="3" t="n"/>
       <c r="F108" s="3" t="n"/>
       <c r="G108" s="3" t="n"/>
-      <c r="H108" s="14" t="n"/>
+      <c r="H108" s="15" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n"/>
@@ -9634,7 +9652,7 @@
       <c r="C109" s="3" t="n"/>
       <c r="F109" s="3" t="n"/>
       <c r="G109" s="3" t="n"/>
-      <c r="H109" s="14" t="n"/>
+      <c r="H109" s="15" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n"/>
@@ -9642,7 +9660,7 @@
       <c r="C110" s="3" t="n"/>
       <c r="F110" s="3" t="n"/>
       <c r="G110" s="3" t="n"/>
-      <c r="H110" s="14" t="n"/>
+      <c r="H110" s="15" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n"/>
@@ -9650,7 +9668,7 @@
       <c r="C111" s="3" t="n"/>
       <c r="F111" s="3" t="n"/>
       <c r="G111" s="3" t="n"/>
-      <c r="H111" s="14" t="n"/>
+      <c r="H111" s="15" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n"/>
@@ -9658,7 +9676,7 @@
       <c r="C112" s="3" t="n"/>
       <c r="F112" s="3" t="n"/>
       <c r="G112" s="3" t="n"/>
-      <c r="H112" s="14" t="n"/>
+      <c r="H112" s="15" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n"/>
@@ -9666,7 +9684,7 @@
       <c r="C113" s="3" t="n"/>
       <c r="F113" s="3" t="n"/>
       <c r="G113" s="3" t="n"/>
-      <c r="H113" s="14" t="n"/>
+      <c r="H113" s="15" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n"/>
@@ -9674,7 +9692,7 @@
       <c r="C114" s="3" t="n"/>
       <c r="F114" s="3" t="n"/>
       <c r="G114" s="3" t="n"/>
-      <c r="H114" s="14" t="n"/>
+      <c r="H114" s="15" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n"/>
@@ -9682,7 +9700,7 @@
       <c r="C115" s="3" t="n"/>
       <c r="F115" s="3" t="n"/>
       <c r="G115" s="3" t="n"/>
-      <c r="H115" s="14" t="n"/>
+      <c r="H115" s="15" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n"/>
@@ -9690,7 +9708,7 @@
       <c r="C116" s="3" t="n"/>
       <c r="F116" s="3" t="n"/>
       <c r="G116" s="3" t="n"/>
-      <c r="H116" s="14" t="n"/>
+      <c r="H116" s="15" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n"/>
@@ -9698,7 +9716,7 @@
       <c r="C117" s="3" t="n"/>
       <c r="F117" s="3" t="n"/>
       <c r="G117" s="3" t="n"/>
-      <c r="H117" s="14" t="n"/>
+      <c r="H117" s="15" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n"/>
@@ -9706,7 +9724,7 @@
       <c r="C118" s="3" t="n"/>
       <c r="F118" s="3" t="n"/>
       <c r="G118" s="3" t="n"/>
-      <c r="H118" s="14" t="n"/>
+      <c r="H118" s="15" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n"/>
@@ -9714,7 +9732,7 @@
       <c r="C119" s="3" t="n"/>
       <c r="F119" s="3" t="n"/>
       <c r="G119" s="3" t="n"/>
-      <c r="H119" s="14" t="n"/>
+      <c r="H119" s="15" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n"/>
@@ -9722,7 +9740,7 @@
       <c r="C120" s="3" t="n"/>
       <c r="F120" s="3" t="n"/>
       <c r="G120" s="3" t="n"/>
-      <c r="H120" s="14" t="n"/>
+      <c r="H120" s="15" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n"/>
@@ -9730,7 +9748,7 @@
       <c r="C121" s="3" t="n"/>
       <c r="F121" s="3" t="n"/>
       <c r="G121" s="3" t="n"/>
-      <c r="H121" s="14" t="n"/>
+      <c r="H121" s="15" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n"/>
@@ -9738,7 +9756,7 @@
       <c r="C122" s="3" t="n"/>
       <c r="F122" s="3" t="n"/>
       <c r="G122" s="3" t="n"/>
-      <c r="H122" s="14" t="n"/>
+      <c r="H122" s="15" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n"/>
@@ -9746,7 +9764,7 @@
       <c r="C123" s="3" t="n"/>
       <c r="F123" s="3" t="n"/>
       <c r="G123" s="3" t="n"/>
-      <c r="H123" s="14" t="n"/>
+      <c r="H123" s="15" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n"/>
@@ -9754,7 +9772,7 @@
       <c r="C124" s="3" t="n"/>
       <c r="F124" s="3" t="n"/>
       <c r="G124" s="3" t="n"/>
-      <c r="H124" s="14" t="n"/>
+      <c r="H124" s="15" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n"/>
@@ -9762,7 +9780,7 @@
       <c r="C125" s="3" t="n"/>
       <c r="F125" s="3" t="n"/>
       <c r="G125" s="3" t="n"/>
-      <c r="H125" s="14" t="n"/>
+      <c r="H125" s="15" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n"/>
@@ -9770,7 +9788,7 @@
       <c r="C126" s="3" t="n"/>
       <c r="F126" s="3" t="n"/>
       <c r="G126" s="3" t="n"/>
-      <c r="H126" s="14" t="n"/>
+      <c r="H126" s="15" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n"/>
@@ -9778,7 +9796,7 @@
       <c r="C127" s="3" t="n"/>
       <c r="F127" s="3" t="n"/>
       <c r="G127" s="3" t="n"/>
-      <c r="H127" s="14" t="n"/>
+      <c r="H127" s="15" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n"/>
@@ -9786,7 +9804,7 @@
       <c r="C128" s="3" t="n"/>
       <c r="F128" s="3" t="n"/>
       <c r="G128" s="3" t="n"/>
-      <c r="H128" s="14" t="n"/>
+      <c r="H128" s="15" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n"/>
@@ -9794,7 +9812,7 @@
       <c r="C129" s="3" t="n"/>
       <c r="F129" s="3" t="n"/>
       <c r="G129" s="3" t="n"/>
-      <c r="H129" s="14" t="n"/>
+      <c r="H129" s="15" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n"/>
@@ -9802,7 +9820,7 @@
       <c r="C130" s="3" t="n"/>
       <c r="F130" s="3" t="n"/>
       <c r="G130" s="3" t="n"/>
-      <c r="H130" s="14" t="n"/>
+      <c r="H130" s="15" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n"/>
@@ -9810,7 +9828,7 @@
       <c r="C131" s="3" t="n"/>
       <c r="F131" s="3" t="n"/>
       <c r="G131" s="3" t="n"/>
-      <c r="H131" s="14" t="n"/>
+      <c r="H131" s="15" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n"/>
@@ -9818,7 +9836,7 @@
       <c r="C132" s="3" t="n"/>
       <c r="F132" s="3" t="n"/>
       <c r="G132" s="3" t="n"/>
-      <c r="H132" s="14" t="n"/>
+      <c r="H132" s="15" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n"/>
@@ -9826,7 +9844,7 @@
       <c r="C133" s="3" t="n"/>
       <c r="F133" s="3" t="n"/>
       <c r="G133" s="3" t="n"/>
-      <c r="H133" s="14" t="n"/>
+      <c r="H133" s="15" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n"/>
@@ -9834,7 +9852,7 @@
       <c r="C134" s="3" t="n"/>
       <c r="F134" s="3" t="n"/>
       <c r="G134" s="3" t="n"/>
-      <c r="H134" s="14" t="n"/>
+      <c r="H134" s="15" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n"/>
@@ -9842,7 +9860,7 @@
       <c r="C135" s="3" t="n"/>
       <c r="F135" s="3" t="n"/>
       <c r="G135" s="3" t="n"/>
-      <c r="H135" s="14" t="n"/>
+      <c r="H135" s="15" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n"/>
@@ -9850,7 +9868,7 @@
       <c r="C136" s="3" t="n"/>
       <c r="F136" s="3" t="n"/>
       <c r="G136" s="3" t="n"/>
-      <c r="H136" s="14" t="n"/>
+      <c r="H136" s="15" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n"/>
@@ -9858,7 +9876,7 @@
       <c r="C137" s="3" t="n"/>
       <c r="F137" s="3" t="n"/>
       <c r="G137" s="3" t="n"/>
-      <c r="H137" s="14" t="n"/>
+      <c r="H137" s="15" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n"/>
@@ -9866,7 +9884,7 @@
       <c r="C138" s="3" t="n"/>
       <c r="F138" s="3" t="n"/>
       <c r="G138" s="3" t="n"/>
-      <c r="H138" s="14" t="n"/>
+      <c r="H138" s="15" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n"/>
@@ -9874,7 +9892,7 @@
       <c r="C139" s="3" t="n"/>
       <c r="F139" s="3" t="n"/>
       <c r="G139" s="3" t="n"/>
-      <c r="H139" s="14" t="n"/>
+      <c r="H139" s="15" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n"/>
@@ -9882,7 +9900,7 @@
       <c r="C140" s="3" t="n"/>
       <c r="F140" s="3" t="n"/>
       <c r="G140" s="3" t="n"/>
-      <c r="H140" s="14" t="n"/>
+      <c r="H140" s="15" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n"/>
@@ -9890,7 +9908,7 @@
       <c r="C141" s="3" t="n"/>
       <c r="F141" s="3" t="n"/>
       <c r="G141" s="3" t="n"/>
-      <c r="H141" s="14" t="n"/>
+      <c r="H141" s="15" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n"/>
@@ -9898,7 +9916,7 @@
       <c r="C142" s="3" t="n"/>
       <c r="F142" s="3" t="n"/>
       <c r="G142" s="3" t="n"/>
-      <c r="H142" s="14" t="n"/>
+      <c r="H142" s="15" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n"/>
@@ -9906,7 +9924,7 @@
       <c r="C143" s="3" t="n"/>
       <c r="F143" s="3" t="n"/>
       <c r="G143" s="3" t="n"/>
-      <c r="H143" s="14" t="n"/>
+      <c r="H143" s="15" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n"/>
@@ -9914,7 +9932,7 @@
       <c r="C144" s="3" t="n"/>
       <c r="F144" s="3" t="n"/>
       <c r="G144" s="3" t="n"/>
-      <c r="H144" s="14" t="n"/>
+      <c r="H144" s="15" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n"/>
@@ -9922,7 +9940,7 @@
       <c r="C145" s="3" t="n"/>
       <c r="F145" s="3" t="n"/>
       <c r="G145" s="3" t="n"/>
-      <c r="H145" s="14" t="n"/>
+      <c r="H145" s="15" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n"/>
@@ -9930,7 +9948,7 @@
       <c r="C146" s="3" t="n"/>
       <c r="F146" s="3" t="n"/>
       <c r="G146" s="3" t="n"/>
-      <c r="H146" s="14" t="n"/>
+      <c r="H146" s="15" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n"/>
@@ -9938,7 +9956,7 @@
       <c r="C147" s="3" t="n"/>
       <c r="F147" s="3" t="n"/>
       <c r="G147" s="3" t="n"/>
-      <c r="H147" s="14" t="n"/>
+      <c r="H147" s="15" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n"/>
@@ -9946,7 +9964,7 @@
       <c r="C148" s="3" t="n"/>
       <c r="F148" s="3" t="n"/>
       <c r="G148" s="3" t="n"/>
-      <c r="H148" s="14" t="n"/>
+      <c r="H148" s="15" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n"/>
@@ -9954,7 +9972,7 @@
       <c r="C149" s="3" t="n"/>
       <c r="F149" s="3" t="n"/>
       <c r="G149" s="3" t="n"/>
-      <c r="H149" s="14" t="n"/>
+      <c r="H149" s="15" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n"/>
@@ -9962,7 +9980,7 @@
       <c r="C150" s="3" t="n"/>
       <c r="F150" s="3" t="n"/>
       <c r="G150" s="3" t="n"/>
-      <c r="H150" s="14" t="n"/>
+      <c r="H150" s="15" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n"/>
@@ -9970,7 +9988,7 @@
       <c r="C151" s="3" t="n"/>
       <c r="F151" s="3" t="n"/>
       <c r="G151" s="3" t="n"/>
-      <c r="H151" s="14" t="n"/>
+      <c r="H151" s="15" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n"/>
@@ -9978,7 +9996,7 @@
       <c r="C152" s="3" t="n"/>
       <c r="F152" s="3" t="n"/>
       <c r="G152" s="3" t="n"/>
-      <c r="H152" s="14" t="n"/>
+      <c r="H152" s="15" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n"/>
@@ -9986,7 +10004,7 @@
       <c r="C153" s="3" t="n"/>
       <c r="F153" s="3" t="n"/>
       <c r="G153" s="3" t="n"/>
-      <c r="H153" s="14" t="n"/>
+      <c r="H153" s="15" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n"/>
@@ -9994,7 +10012,7 @@
       <c r="C154" s="3" t="n"/>
       <c r="F154" s="3" t="n"/>
       <c r="G154" s="3" t="n"/>
-      <c r="H154" s="14" t="n"/>
+      <c r="H154" s="15" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n"/>
@@ -10002,7 +10020,7 @@
       <c r="C155" s="3" t="n"/>
       <c r="F155" s="3" t="n"/>
       <c r="G155" s="3" t="n"/>
-      <c r="H155" s="14" t="n"/>
+      <c r="H155" s="15" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n"/>
@@ -10010,7 +10028,7 @@
       <c r="C156" s="3" t="n"/>
       <c r="F156" s="3" t="n"/>
       <c r="G156" s="3" t="n"/>
-      <c r="H156" s="14" t="n"/>
+      <c r="H156" s="15" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n"/>
@@ -10018,7 +10036,7 @@
       <c r="C157" s="3" t="n"/>
       <c r="F157" s="3" t="n"/>
       <c r="G157" s="3" t="n"/>
-      <c r="H157" s="14" t="n"/>
+      <c r="H157" s="15" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n"/>
@@ -10026,7 +10044,7 @@
       <c r="C158" s="3" t="n"/>
       <c r="F158" s="3" t="n"/>
       <c r="G158" s="3" t="n"/>
-      <c r="H158" s="14" t="n"/>
+      <c r="H158" s="15" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n"/>
@@ -10034,7 +10052,7 @@
       <c r="C159" s="3" t="n"/>
       <c r="F159" s="3" t="n"/>
       <c r="G159" s="3" t="n"/>
-      <c r="H159" s="14" t="n"/>
+      <c r="H159" s="15" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n"/>
@@ -10042,7 +10060,7 @@
       <c r="C160" s="3" t="n"/>
       <c r="F160" s="3" t="n"/>
       <c r="G160" s="3" t="n"/>
-      <c r="H160" s="14" t="n"/>
+      <c r="H160" s="15" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n"/>
@@ -10050,7 +10068,7 @@
       <c r="C161" s="3" t="n"/>
       <c r="F161" s="3" t="n"/>
       <c r="G161" s="3" t="n"/>
-      <c r="H161" s="14" t="n"/>
+      <c r="H161" s="15" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n"/>
@@ -10058,7 +10076,7 @@
       <c r="C162" s="3" t="n"/>
       <c r="F162" s="3" t="n"/>
       <c r="G162" s="3" t="n"/>
-      <c r="H162" s="14" t="n"/>
+      <c r="H162" s="15" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n"/>
@@ -10066,7 +10084,7 @@
       <c r="C163" s="3" t="n"/>
       <c r="F163" s="3" t="n"/>
       <c r="G163" s="3" t="n"/>
-      <c r="H163" s="14" t="n"/>
+      <c r="H163" s="15" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n"/>
@@ -10074,7 +10092,7 @@
       <c r="C164" s="3" t="n"/>
       <c r="F164" s="3" t="n"/>
       <c r="G164" s="3" t="n"/>
-      <c r="H164" s="14" t="n"/>
+      <c r="H164" s="15" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n"/>
@@ -10082,7 +10100,7 @@
       <c r="C165" s="3" t="n"/>
       <c r="F165" s="3" t="n"/>
       <c r="G165" s="3" t="n"/>
-      <c r="H165" s="14" t="n"/>
+      <c r="H165" s="15" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n"/>
@@ -10090,7 +10108,7 @@
       <c r="C166" s="3" t="n"/>
       <c r="F166" s="3" t="n"/>
       <c r="G166" s="3" t="n"/>
-      <c r="H166" s="14" t="n"/>
+      <c r="H166" s="15" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n"/>
@@ -10098,7 +10116,7 @@
       <c r="C167" s="3" t="n"/>
       <c r="F167" s="3" t="n"/>
       <c r="G167" s="3" t="n"/>
-      <c r="H167" s="14" t="n"/>
+      <c r="H167" s="15" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n"/>
@@ -10106,7 +10124,7 @@
       <c r="C168" s="3" t="n"/>
       <c r="F168" s="3" t="n"/>
       <c r="G168" s="3" t="n"/>
-      <c r="H168" s="14" t="n"/>
+      <c r="H168" s="15" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n"/>
@@ -10114,7 +10132,7 @@
       <c r="C169" s="3" t="n"/>
       <c r="F169" s="3" t="n"/>
       <c r="G169" s="3" t="n"/>
-      <c r="H169" s="14" t="n"/>
+      <c r="H169" s="15" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n"/>
@@ -10122,7 +10140,7 @@
       <c r="C170" s="3" t="n"/>
       <c r="F170" s="3" t="n"/>
       <c r="G170" s="3" t="n"/>
-      <c r="H170" s="14" t="n"/>
+      <c r="H170" s="15" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n"/>
@@ -10130,7 +10148,7 @@
       <c r="C171" s="3" t="n"/>
       <c r="F171" s="3" t="n"/>
       <c r="G171" s="3" t="n"/>
-      <c r="H171" s="14" t="n"/>
+      <c r="H171" s="15" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n"/>
@@ -10138,7 +10156,7 @@
       <c r="C172" s="3" t="n"/>
       <c r="F172" s="3" t="n"/>
       <c r="G172" s="3" t="n"/>
-      <c r="H172" s="14" t="n"/>
+      <c r="H172" s="15" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n"/>
@@ -10146,7 +10164,7 @@
       <c r="C173" s="3" t="n"/>
       <c r="F173" s="3" t="n"/>
       <c r="G173" s="3" t="n"/>
-      <c r="H173" s="14" t="n"/>
+      <c r="H173" s="15" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n"/>
@@ -10154,7 +10172,7 @@
       <c r="C174" s="3" t="n"/>
       <c r="F174" s="3" t="n"/>
       <c r="G174" s="3" t="n"/>
-      <c r="H174" s="14" t="n"/>
+      <c r="H174" s="15" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n"/>
@@ -10162,7 +10180,7 @@
       <c r="C175" s="3" t="n"/>
       <c r="F175" s="3" t="n"/>
       <c r="G175" s="3" t="n"/>
-      <c r="H175" s="14" t="n"/>
+      <c r="H175" s="15" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n"/>
@@ -10170,7 +10188,7 @@
       <c r="C176" s="3" t="n"/>
       <c r="F176" s="3" t="n"/>
       <c r="G176" s="3" t="n"/>
-      <c r="H176" s="14" t="n"/>
+      <c r="H176" s="15" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n"/>
@@ -10178,7 +10196,7 @@
       <c r="C177" s="3" t="n"/>
       <c r="F177" s="3" t="n"/>
       <c r="G177" s="3" t="n"/>
-      <c r="H177" s="14" t="n"/>
+      <c r="H177" s="15" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n"/>
@@ -10186,7 +10204,7 @@
       <c r="C178" s="3" t="n"/>
       <c r="F178" s="3" t="n"/>
       <c r="G178" s="3" t="n"/>
-      <c r="H178" s="14" t="n"/>
+      <c r="H178" s="15" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n"/>
@@ -10194,7 +10212,7 @@
       <c r="C179" s="3" t="n"/>
       <c r="F179" s="3" t="n"/>
       <c r="G179" s="3" t="n"/>
-      <c r="H179" s="14" t="n"/>
+      <c r="H179" s="15" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="n"/>
@@ -10202,7 +10220,7 @@
       <c r="C180" s="3" t="n"/>
       <c r="F180" s="3" t="n"/>
       <c r="G180" s="3" t="n"/>
-      <c r="H180" s="14" t="n"/>
+      <c r="H180" s="15" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="n"/>
@@ -10210,7 +10228,7 @@
       <c r="C181" s="3" t="n"/>
       <c r="F181" s="3" t="n"/>
       <c r="G181" s="3" t="n"/>
-      <c r="H181" s="14" t="n"/>
+      <c r="H181" s="15" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n"/>
@@ -10218,7 +10236,7 @@
       <c r="C182" s="3" t="n"/>
       <c r="F182" s="3" t="n"/>
       <c r="G182" s="3" t="n"/>
-      <c r="H182" s="14" t="n"/>
+      <c r="H182" s="15" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="n"/>
@@ -10226,7 +10244,7 @@
       <c r="C183" s="3" t="n"/>
       <c r="F183" s="3" t="n"/>
       <c r="G183" s="3" t="n"/>
-      <c r="H183" s="14" t="n"/>
+      <c r="H183" s="15" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="n"/>
@@ -10234,7 +10252,7 @@
       <c r="C184" s="3" t="n"/>
       <c r="F184" s="3" t="n"/>
       <c r="G184" s="3" t="n"/>
-      <c r="H184" s="14" t="n"/>
+      <c r="H184" s="15" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="n"/>
@@ -10242,7 +10260,7 @@
       <c r="C185" s="3" t="n"/>
       <c r="F185" s="3" t="n"/>
       <c r="G185" s="3" t="n"/>
-      <c r="H185" s="14" t="n"/>
+      <c r="H185" s="15" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="n"/>
@@ -10250,7 +10268,7 @@
       <c r="C186" s="3" t="n"/>
       <c r="F186" s="3" t="n"/>
       <c r="G186" s="3" t="n"/>
-      <c r="H186" s="14" t="n"/>
+      <c r="H186" s="15" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="n"/>
@@ -10258,7 +10276,7 @@
       <c r="C187" s="3" t="n"/>
       <c r="F187" s="3" t="n"/>
       <c r="G187" s="3" t="n"/>
-      <c r="H187" s="14" t="n"/>
+      <c r="H187" s="15" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="n"/>
@@ -10266,7 +10284,7 @@
       <c r="C188" s="3" t="n"/>
       <c r="F188" s="3" t="n"/>
       <c r="G188" s="3" t="n"/>
-      <c r="H188" s="14" t="n"/>
+      <c r="H188" s="15" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="n"/>
@@ -10274,7 +10292,7 @@
       <c r="C189" s="3" t="n"/>
       <c r="F189" s="3" t="n"/>
       <c r="G189" s="3" t="n"/>
-      <c r="H189" s="14" t="n"/>
+      <c r="H189" s="15" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="n"/>
@@ -10282,7 +10300,7 @@
       <c r="C190" s="3" t="n"/>
       <c r="F190" s="3" t="n"/>
       <c r="G190" s="3" t="n"/>
-      <c r="H190" s="14" t="n"/>
+      <c r="H190" s="15" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="n"/>
@@ -10290,7 +10308,7 @@
       <c r="C191" s="3" t="n"/>
       <c r="F191" s="3" t="n"/>
       <c r="G191" s="3" t="n"/>
-      <c r="H191" s="14" t="n"/>
+      <c r="H191" s="15" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="n"/>
@@ -10298,7 +10316,7 @@
       <c r="C192" s="3" t="n"/>
       <c r="F192" s="3" t="n"/>
       <c r="G192" s="3" t="n"/>
-      <c r="H192" s="14" t="n"/>
+      <c r="H192" s="15" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="n"/>
@@ -10306,7 +10324,7 @@
       <c r="C193" s="3" t="n"/>
       <c r="F193" s="3" t="n"/>
       <c r="G193" s="3" t="n"/>
-      <c r="H193" s="14" t="n"/>
+      <c r="H193" s="15" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="n"/>
@@ -10314,7 +10332,7 @@
       <c r="C194" s="3" t="n"/>
       <c r="F194" s="3" t="n"/>
       <c r="G194" s="3" t="n"/>
-      <c r="H194" s="14" t="n"/>
+      <c r="H194" s="15" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="n"/>
@@ -10322,7 +10340,7 @@
       <c r="C195" s="3" t="n"/>
       <c r="F195" s="3" t="n"/>
       <c r="G195" s="3" t="n"/>
-      <c r="H195" s="14" t="n"/>
+      <c r="H195" s="15" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="n"/>
@@ -10330,7 +10348,7 @@
       <c r="C196" s="3" t="n"/>
       <c r="F196" s="3" t="n"/>
       <c r="G196" s="3" t="n"/>
-      <c r="H196" s="14" t="n"/>
+      <c r="H196" s="15" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="n"/>
@@ -10338,7 +10356,7 @@
       <c r="C197" s="3" t="n"/>
       <c r="F197" s="3" t="n"/>
       <c r="G197" s="3" t="n"/>
-      <c r="H197" s="14" t="n"/>
+      <c r="H197" s="15" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="n"/>
@@ -10346,7 +10364,7 @@
       <c r="C198" s="3" t="n"/>
       <c r="F198" s="3" t="n"/>
       <c r="G198" s="3" t="n"/>
-      <c r="H198" s="14" t="n"/>
+      <c r="H198" s="15" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="n"/>
@@ -10354,7 +10372,7 @@
       <c r="C199" s="3" t="n"/>
       <c r="F199" s="3" t="n"/>
       <c r="G199" s="3" t="n"/>
-      <c r="H199" s="14" t="n"/>
+      <c r="H199" s="15" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="n"/>
@@ -10362,7 +10380,7 @@
       <c r="C200" s="3" t="n"/>
       <c r="F200" s="3" t="n"/>
       <c r="G200" s="3" t="n"/>
-      <c r="H200" s="14" t="n"/>
+      <c r="H200" s="15" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="n"/>
@@ -10370,7 +10388,7 @@
       <c r="C201" s="3" t="n"/>
       <c r="F201" s="3" t="n"/>
       <c r="G201" s="3" t="n"/>
-      <c r="H201" s="14" t="n"/>
+      <c r="H201" s="15" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="n"/>
@@ -10378,7 +10396,7 @@
       <c r="C202" s="3" t="n"/>
       <c r="F202" s="3" t="n"/>
       <c r="G202" s="3" t="n"/>
-      <c r="H202" s="14" t="n"/>
+      <c r="H202" s="15" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="n"/>
@@ -10386,7 +10404,7 @@
       <c r="C203" s="3" t="n"/>
       <c r="F203" s="3" t="n"/>
       <c r="G203" s="3" t="n"/>
-      <c r="H203" s="14" t="n"/>
+      <c r="H203" s="15" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="n"/>
@@ -10394,7 +10412,7 @@
       <c r="C204" s="3" t="n"/>
       <c r="F204" s="3" t="n"/>
       <c r="G204" s="3" t="n"/>
-      <c r="H204" s="14" t="n"/>
+      <c r="H204" s="15" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="n"/>
@@ -10402,7 +10420,7 @@
       <c r="C205" s="3" t="n"/>
       <c r="F205" s="3" t="n"/>
       <c r="G205" s="3" t="n"/>
-      <c r="H205" s="14" t="n"/>
+      <c r="H205" s="15" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="n"/>
@@ -10410,7 +10428,7 @@
       <c r="C206" s="3" t="n"/>
       <c r="F206" s="3" t="n"/>
       <c r="G206" s="3" t="n"/>
-      <c r="H206" s="14" t="n"/>
+      <c r="H206" s="15" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="n"/>
@@ -10418,7 +10436,7 @@
       <c r="C207" s="3" t="n"/>
       <c r="F207" s="3" t="n"/>
       <c r="G207" s="3" t="n"/>
-      <c r="H207" s="14" t="n"/>
+      <c r="H207" s="15" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="n"/>
@@ -10426,7 +10444,7 @@
       <c r="C208" s="3" t="n"/>
       <c r="F208" s="3" t="n"/>
       <c r="G208" s="3" t="n"/>
-      <c r="H208" s="14" t="n"/>
+      <c r="H208" s="15" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="n"/>
@@ -10434,7 +10452,7 @@
       <c r="C209" s="3" t="n"/>
       <c r="F209" s="3" t="n"/>
       <c r="G209" s="3" t="n"/>
-      <c r="H209" s="14" t="n"/>
+      <c r="H209" s="15" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="3" t="n"/>
@@ -10442,7 +10460,7 @@
       <c r="C210" s="3" t="n"/>
       <c r="F210" s="3" t="n"/>
       <c r="G210" s="3" t="n"/>
-      <c r="H210" s="14" t="n"/>
+      <c r="H210" s="15" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="3" t="n"/>
@@ -10450,7 +10468,7 @@
       <c r="C211" s="3" t="n"/>
       <c r="F211" s="3" t="n"/>
       <c r="G211" s="3" t="n"/>
-      <c r="H211" s="14" t="n"/>
+      <c r="H211" s="15" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="n"/>
@@ -10458,7 +10476,7 @@
       <c r="C212" s="3" t="n"/>
       <c r="F212" s="3" t="n"/>
       <c r="G212" s="3" t="n"/>
-      <c r="H212" s="14" t="n"/>
+      <c r="H212" s="15" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="n"/>
@@ -10466,7 +10484,7 @@
       <c r="C213" s="3" t="n"/>
       <c r="F213" s="3" t="n"/>
       <c r="G213" s="3" t="n"/>
-      <c r="H213" s="14" t="n"/>
+      <c r="H213" s="15" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="n"/>
@@ -10474,7 +10492,7 @@
       <c r="C214" s="3" t="n"/>
       <c r="F214" s="3" t="n"/>
       <c r="G214" s="3" t="n"/>
-      <c r="H214" s="14" t="n"/>
+      <c r="H214" s="15" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="n"/>
@@ -10482,7 +10500,7 @@
       <c r="C215" s="3" t="n"/>
       <c r="F215" s="3" t="n"/>
       <c r="G215" s="3" t="n"/>
-      <c r="H215" s="14" t="n"/>
+      <c r="H215" s="15" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="n"/>
@@ -10490,7 +10508,7 @@
       <c r="C216" s="3" t="n"/>
       <c r="F216" s="3" t="n"/>
       <c r="G216" s="3" t="n"/>
-      <c r="H216" s="14" t="n"/>
+      <c r="H216" s="15" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="3" t="n"/>
@@ -10498,7 +10516,7 @@
       <c r="C217" s="3" t="n"/>
       <c r="F217" s="3" t="n"/>
       <c r="G217" s="3" t="n"/>
-      <c r="H217" s="14" t="n"/>
+      <c r="H217" s="15" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="3" t="n"/>
@@ -10506,7 +10524,7 @@
       <c r="C218" s="3" t="n"/>
       <c r="F218" s="3" t="n"/>
       <c r="G218" s="3" t="n"/>
-      <c r="H218" s="14" t="n"/>
+      <c r="H218" s="15" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="n"/>
@@ -10514,7 +10532,7 @@
       <c r="C219" s="3" t="n"/>
       <c r="F219" s="3" t="n"/>
       <c r="G219" s="3" t="n"/>
-      <c r="H219" s="14" t="n"/>
+      <c r="H219" s="15" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="n"/>
@@ -10522,7 +10540,7 @@
       <c r="C220" s="3" t="n"/>
       <c r="F220" s="3" t="n"/>
       <c r="G220" s="3" t="n"/>
-      <c r="H220" s="14" t="n"/>
+      <c r="H220" s="15" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="n"/>
@@ -10530,7 +10548,7 @@
       <c r="C221" s="3" t="n"/>
       <c r="F221" s="3" t="n"/>
       <c r="G221" s="3" t="n"/>
-      <c r="H221" s="14" t="n"/>
+      <c r="H221" s="15" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="n"/>
@@ -10538,7 +10556,7 @@
       <c r="C222" s="3" t="n"/>
       <c r="F222" s="3" t="n"/>
       <c r="G222" s="3" t="n"/>
-      <c r="H222" s="14" t="n"/>
+      <c r="H222" s="15" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="n"/>
@@ -10546,7 +10564,7 @@
       <c r="C223" s="3" t="n"/>
       <c r="F223" s="3" t="n"/>
       <c r="G223" s="3" t="n"/>
-      <c r="H223" s="14" t="n"/>
+      <c r="H223" s="15" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="3" t="n"/>
@@ -10554,7 +10572,7 @@
       <c r="C224" s="3" t="n"/>
       <c r="F224" s="3" t="n"/>
       <c r="G224" s="3" t="n"/>
-      <c r="H224" s="14" t="n"/>
+      <c r="H224" s="15" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="3" t="n"/>
@@ -10562,7 +10580,7 @@
       <c r="C225" s="3" t="n"/>
       <c r="F225" s="3" t="n"/>
       <c r="G225" s="3" t="n"/>
-      <c r="H225" s="14" t="n"/>
+      <c r="H225" s="15" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="n"/>
@@ -10570,7 +10588,7 @@
       <c r="C226" s="3" t="n"/>
       <c r="F226" s="3" t="n"/>
       <c r="G226" s="3" t="n"/>
-      <c r="H226" s="14" t="n"/>
+      <c r="H226" s="15" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="n"/>
@@ -10578,7 +10596,7 @@
       <c r="C227" s="3" t="n"/>
       <c r="F227" s="3" t="n"/>
       <c r="G227" s="3" t="n"/>
-      <c r="H227" s="14" t="n"/>
+      <c r="H227" s="15" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="n"/>
@@ -10586,7 +10604,7 @@
       <c r="C228" s="3" t="n"/>
       <c r="F228" s="3" t="n"/>
       <c r="G228" s="3" t="n"/>
-      <c r="H228" s="14" t="n"/>
+      <c r="H228" s="15" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="n"/>
@@ -10594,7 +10612,7 @@
       <c r="C229" s="3" t="n"/>
       <c r="F229" s="3" t="n"/>
       <c r="G229" s="3" t="n"/>
-      <c r="H229" s="14" t="n"/>
+      <c r="H229" s="15" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="n"/>
@@ -10602,7 +10620,7 @@
       <c r="C230" s="3" t="n"/>
       <c r="F230" s="3" t="n"/>
       <c r="G230" s="3" t="n"/>
-      <c r="H230" s="14" t="n"/>
+      <c r="H230" s="15" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="3" t="n"/>
@@ -10610,7 +10628,7 @@
       <c r="C231" s="3" t="n"/>
       <c r="F231" s="3" t="n"/>
       <c r="G231" s="3" t="n"/>
-      <c r="H231" s="14" t="n"/>
+      <c r="H231" s="15" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="3" t="n"/>
@@ -10618,7 +10636,7 @@
       <c r="C232" s="3" t="n"/>
       <c r="F232" s="3" t="n"/>
       <c r="G232" s="3" t="n"/>
-      <c r="H232" s="14" t="n"/>
+      <c r="H232" s="15" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="n"/>
@@ -10626,7 +10644,7 @@
       <c r="C233" s="3" t="n"/>
       <c r="F233" s="3" t="n"/>
       <c r="G233" s="3" t="n"/>
-      <c r="H233" s="14" t="n"/>
+      <c r="H233" s="15" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="n"/>
@@ -10634,7 +10652,7 @@
       <c r="C234" s="3" t="n"/>
       <c r="F234" s="3" t="n"/>
       <c r="G234" s="3" t="n"/>
-      <c r="H234" s="14" t="n"/>
+      <c r="H234" s="15" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="n"/>
@@ -10642,7 +10660,7 @@
       <c r="C235" s="3" t="n"/>
       <c r="F235" s="3" t="n"/>
       <c r="G235" s="3" t="n"/>
-      <c r="H235" s="14" t="n"/>
+      <c r="H235" s="15" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="n"/>
@@ -10650,7 +10668,7 @@
       <c r="C236" s="3" t="n"/>
       <c r="F236" s="3" t="n"/>
       <c r="G236" s="3" t="n"/>
-      <c r="H236" s="14" t="n"/>
+      <c r="H236" s="15" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="n"/>
@@ -10658,7 +10676,7 @@
       <c r="C237" s="3" t="n"/>
       <c r="F237" s="3" t="n"/>
       <c r="G237" s="3" t="n"/>
-      <c r="H237" s="14" t="n"/>
+      <c r="H237" s="15" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="3" t="n"/>
@@ -10666,7 +10684,7 @@
       <c r="C238" s="3" t="n"/>
       <c r="F238" s="3" t="n"/>
       <c r="G238" s="3" t="n"/>
-      <c r="H238" s="14" t="n"/>
+      <c r="H238" s="15" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="3" t="n"/>
@@ -10674,7 +10692,7 @@
       <c r="C239" s="3" t="n"/>
       <c r="F239" s="3" t="n"/>
       <c r="G239" s="3" t="n"/>
-      <c r="H239" s="14" t="n"/>
+      <c r="H239" s="15" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="n"/>
@@ -10682,7 +10700,7 @@
       <c r="C240" s="3" t="n"/>
       <c r="F240" s="3" t="n"/>
       <c r="G240" s="3" t="n"/>
-      <c r="H240" s="14" t="n"/>
+      <c r="H240" s="15" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="n"/>
@@ -10690,7 +10708,7 @@
       <c r="C241" s="3" t="n"/>
       <c r="F241" s="3" t="n"/>
       <c r="G241" s="3" t="n"/>
-      <c r="H241" s="14" t="n"/>
+      <c r="H241" s="15" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="n"/>
@@ -10698,7 +10716,7 @@
       <c r="C242" s="3" t="n"/>
       <c r="F242" s="3" t="n"/>
       <c r="G242" s="3" t="n"/>
-      <c r="H242" s="14" t="n"/>
+      <c r="H242" s="15" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="n"/>
@@ -10706,7 +10724,7 @@
       <c r="C243" s="3" t="n"/>
       <c r="F243" s="3" t="n"/>
       <c r="G243" s="3" t="n"/>
-      <c r="H243" s="14" t="n"/>
+      <c r="H243" s="15" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="n"/>
@@ -10714,7 +10732,7 @@
       <c r="C244" s="3" t="n"/>
       <c r="F244" s="3" t="n"/>
       <c r="G244" s="3" t="n"/>
-      <c r="H244" s="14" t="n"/>
+      <c r="H244" s="15" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="3" t="n"/>
@@ -10722,7 +10740,7 @@
       <c r="C245" s="3" t="n"/>
       <c r="F245" s="3" t="n"/>
       <c r="G245" s="3" t="n"/>
-      <c r="H245" s="14" t="n"/>
+      <c r="H245" s="15" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="3" t="n"/>
@@ -10730,7 +10748,7 @@
       <c r="C246" s="3" t="n"/>
       <c r="F246" s="3" t="n"/>
       <c r="G246" s="3" t="n"/>
-      <c r="H246" s="14" t="n"/>
+      <c r="H246" s="15" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="n"/>
@@ -10738,7 +10756,7 @@
       <c r="C247" s="3" t="n"/>
       <c r="F247" s="3" t="n"/>
       <c r="G247" s="3" t="n"/>
-      <c r="H247" s="14" t="n"/>
+      <c r="H247" s="15" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="n"/>
@@ -10746,7 +10764,7 @@
       <c r="C248" s="3" t="n"/>
       <c r="F248" s="3" t="n"/>
       <c r="G248" s="3" t="n"/>
-      <c r="H248" s="14" t="n"/>
+      <c r="H248" s="15" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="3" t="n"/>
@@ -10754,7 +10772,7 @@
       <c r="C249" s="3" t="n"/>
       <c r="F249" s="3" t="n"/>
       <c r="G249" s="3" t="n"/>
-      <c r="H249" s="14" t="n"/>
+      <c r="H249" s="15" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="3" t="n"/>
@@ -10762,7 +10780,7 @@
       <c r="C250" s="3" t="n"/>
       <c r="F250" s="3" t="n"/>
       <c r="G250" s="3" t="n"/>
-      <c r="H250" s="14" t="n"/>
+      <c r="H250" s="15" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="3" t="n"/>
@@ -10770,7 +10788,7 @@
       <c r="C251" s="3" t="n"/>
       <c r="F251" s="3" t="n"/>
       <c r="G251" s="3" t="n"/>
-      <c r="H251" s="14" t="n"/>
+      <c r="H251" s="15" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="3" t="n"/>
@@ -10778,7 +10796,7 @@
       <c r="C252" s="3" t="n"/>
       <c r="F252" s="3" t="n"/>
       <c r="G252" s="3" t="n"/>
-      <c r="H252" s="14" t="n"/>
+      <c r="H252" s="15" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="3" t="n"/>
@@ -10786,7 +10804,7 @@
       <c r="C253" s="3" t="n"/>
       <c r="F253" s="3" t="n"/>
       <c r="G253" s="3" t="n"/>
-      <c r="H253" s="14" t="n"/>
+      <c r="H253" s="15" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="3" t="n"/>
@@ -10794,7 +10812,7 @@
       <c r="C254" s="3" t="n"/>
       <c r="F254" s="3" t="n"/>
       <c r="G254" s="3" t="n"/>
-      <c r="H254" s="14" t="n"/>
+      <c r="H254" s="15" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="3" t="n"/>
@@ -10802,7 +10820,7 @@
       <c r="C255" s="3" t="n"/>
       <c r="F255" s="3" t="n"/>
       <c r="G255" s="3" t="n"/>
-      <c r="H255" s="14" t="n"/>
+      <c r="H255" s="15" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="3" t="n"/>
@@ -10810,7 +10828,7 @@
       <c r="C256" s="3" t="n"/>
       <c r="F256" s="3" t="n"/>
       <c r="G256" s="3" t="n"/>
-      <c r="H256" s="14" t="n"/>
+      <c r="H256" s="15" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="3" t="n"/>
@@ -10818,7 +10836,7 @@
       <c r="C257" s="3" t="n"/>
       <c r="F257" s="3" t="n"/>
       <c r="G257" s="3" t="n"/>
-      <c r="H257" s="14" t="n"/>
+      <c r="H257" s="15" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="3" t="n"/>
@@ -10826,7 +10844,7 @@
       <c r="C258" s="3" t="n"/>
       <c r="F258" s="3" t="n"/>
       <c r="G258" s="3" t="n"/>
-      <c r="H258" s="14" t="n"/>
+      <c r="H258" s="15" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="3" t="n"/>
@@ -10834,7 +10852,7 @@
       <c r="C259" s="3" t="n"/>
       <c r="F259" s="3" t="n"/>
       <c r="G259" s="3" t="n"/>
-      <c r="H259" s="14" t="n"/>
+      <c r="H259" s="15" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="3" t="n"/>
@@ -10842,7 +10860,7 @@
       <c r="C260" s="3" t="n"/>
       <c r="F260" s="3" t="n"/>
       <c r="G260" s="3" t="n"/>
-      <c r="H260" s="14" t="n"/>
+      <c r="H260" s="15" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="3" t="n"/>
@@ -10850,7 +10868,7 @@
       <c r="C261" s="3" t="n"/>
       <c r="F261" s="3" t="n"/>
       <c r="G261" s="3" t="n"/>
-      <c r="H261" s="14" t="n"/>
+      <c r="H261" s="15" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="n"/>
@@ -10858,7 +10876,7 @@
       <c r="C262" s="3" t="n"/>
       <c r="F262" s="3" t="n"/>
       <c r="G262" s="3" t="n"/>
-      <c r="H262" s="14" t="n"/>
+      <c r="H262" s="15" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="3" t="n"/>
@@ -10866,7 +10884,7 @@
       <c r="C263" s="3" t="n"/>
       <c r="F263" s="3" t="n"/>
       <c r="G263" s="3" t="n"/>
-      <c r="H263" s="14" t="n"/>
+      <c r="H263" s="15" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="3" t="n"/>
@@ -10874,7 +10892,7 @@
       <c r="C264" s="3" t="n"/>
       <c r="F264" s="3" t="n"/>
       <c r="G264" s="3" t="n"/>
-      <c r="H264" s="14" t="n"/>
+      <c r="H264" s="15" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="3" t="n"/>
@@ -10882,7 +10900,7 @@
       <c r="C265" s="3" t="n"/>
       <c r="F265" s="3" t="n"/>
       <c r="G265" s="3" t="n"/>
-      <c r="H265" s="14" t="n"/>
+      <c r="H265" s="15" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="3" t="n"/>
@@ -10890,7 +10908,7 @@
       <c r="C266" s="3" t="n"/>
       <c r="F266" s="3" t="n"/>
       <c r="G266" s="3" t="n"/>
-      <c r="H266" s="14" t="n"/>
+      <c r="H266" s="15" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="3" t="n"/>
@@ -10898,7 +10916,7 @@
       <c r="C267" s="3" t="n"/>
       <c r="F267" s="3" t="n"/>
       <c r="G267" s="3" t="n"/>
-      <c r="H267" s="14" t="n"/>
+      <c r="H267" s="15" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="3" t="n"/>
@@ -10906,7 +10924,7 @@
       <c r="C268" s="3" t="n"/>
       <c r="F268" s="3" t="n"/>
       <c r="G268" s="3" t="n"/>
-      <c r="H268" s="14" t="n"/>
+      <c r="H268" s="15" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="3" t="n"/>
@@ -10914,7 +10932,7 @@
       <c r="C269" s="3" t="n"/>
       <c r="F269" s="3" t="n"/>
       <c r="G269" s="3" t="n"/>
-      <c r="H269" s="14" t="n"/>
+      <c r="H269" s="15" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="3" t="n"/>
@@ -10922,7 +10940,7 @@
       <c r="C270" s="3" t="n"/>
       <c r="F270" s="3" t="n"/>
       <c r="G270" s="3" t="n"/>
-      <c r="H270" s="14" t="n"/>
+      <c r="H270" s="15" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="3" t="n"/>
@@ -10930,7 +10948,7 @@
       <c r="C271" s="3" t="n"/>
       <c r="F271" s="3" t="n"/>
       <c r="G271" s="3" t="n"/>
-      <c r="H271" s="14" t="n"/>
+      <c r="H271" s="15" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="3" t="n"/>
@@ -10938,7 +10956,7 @@
       <c r="C272" s="3" t="n"/>
       <c r="F272" s="3" t="n"/>
       <c r="G272" s="3" t="n"/>
-      <c r="H272" s="14" t="n"/>
+      <c r="H272" s="15" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="3" t="n"/>
@@ -10946,7 +10964,7 @@
       <c r="C273" s="3" t="n"/>
       <c r="F273" s="3" t="n"/>
       <c r="G273" s="3" t="n"/>
-      <c r="H273" s="14" t="n"/>
+      <c r="H273" s="15" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="3" t="n"/>
@@ -10954,7 +10972,7 @@
       <c r="C274" s="3" t="n"/>
       <c r="F274" s="3" t="n"/>
       <c r="G274" s="3" t="n"/>
-      <c r="H274" s="14" t="n"/>
+      <c r="H274" s="15" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="3" t="n"/>
@@ -10962,7 +10980,7 @@
       <c r="C275" s="3" t="n"/>
       <c r="F275" s="3" t="n"/>
       <c r="G275" s="3" t="n"/>
-      <c r="H275" s="14" t="n"/>
+      <c r="H275" s="15" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="3" t="n"/>
@@ -10970,7 +10988,7 @@
       <c r="C276" s="3" t="n"/>
       <c r="F276" s="3" t="n"/>
       <c r="G276" s="3" t="n"/>
-      <c r="H276" s="14" t="n"/>
+      <c r="H276" s="15" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="3" t="n"/>
@@ -10978,7 +10996,7 @@
       <c r="C277" s="3" t="n"/>
       <c r="F277" s="3" t="n"/>
       <c r="G277" s="3" t="n"/>
-      <c r="H277" s="14" t="n"/>
+      <c r="H277" s="15" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="3" t="n"/>
@@ -10986,7 +11004,7 @@
       <c r="C278" s="3" t="n"/>
       <c r="F278" s="3" t="n"/>
       <c r="G278" s="3" t="n"/>
-      <c r="H278" s="14" t="n"/>
+      <c r="H278" s="15" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="3" t="n"/>
@@ -10994,7 +11012,7 @@
       <c r="C279" s="3" t="n"/>
       <c r="F279" s="3" t="n"/>
       <c r="G279" s="3" t="n"/>
-      <c r="H279" s="14" t="n"/>
+      <c r="H279" s="15" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="3" t="n"/>
@@ -11002,7 +11020,7 @@
       <c r="C280" s="3" t="n"/>
       <c r="F280" s="3" t="n"/>
       <c r="G280" s="3" t="n"/>
-      <c r="H280" s="14" t="n"/>
+      <c r="H280" s="15" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="3" t="n"/>
@@ -11010,7 +11028,7 @@
       <c r="C281" s="3" t="n"/>
       <c r="F281" s="3" t="n"/>
       <c r="G281" s="3" t="n"/>
-      <c r="H281" s="14" t="n"/>
+      <c r="H281" s="15" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="3" t="n"/>
@@ -11018,7 +11036,7 @@
       <c r="C282" s="3" t="n"/>
       <c r="F282" s="3" t="n"/>
       <c r="G282" s="3" t="n"/>
-      <c r="H282" s="14" t="n"/>
+      <c r="H282" s="15" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="3" t="n"/>
@@ -11026,7 +11044,7 @@
       <c r="C283" s="3" t="n"/>
       <c r="F283" s="3" t="n"/>
       <c r="G283" s="3" t="n"/>
-      <c r="H283" s="14" t="n"/>
+      <c r="H283" s="15" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="3" t="n"/>
@@ -11034,7 +11052,7 @@
       <c r="C284" s="3" t="n"/>
       <c r="F284" s="3" t="n"/>
       <c r="G284" s="3" t="n"/>
-      <c r="H284" s="14" t="n"/>
+      <c r="H284" s="15" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="3" t="n"/>
@@ -11042,7 +11060,7 @@
       <c r="C285" s="3" t="n"/>
       <c r="F285" s="3" t="n"/>
       <c r="G285" s="3" t="n"/>
-      <c r="H285" s="14" t="n"/>
+      <c r="H285" s="15" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="3" t="n"/>
@@ -11050,7 +11068,7 @@
       <c r="C286" s="3" t="n"/>
       <c r="F286" s="3" t="n"/>
       <c r="G286" s="3" t="n"/>
-      <c r="H286" s="14" t="n"/>
+      <c r="H286" s="15" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="3" t="n"/>
@@ -11058,7 +11076,7 @@
       <c r="C287" s="3" t="n"/>
       <c r="F287" s="3" t="n"/>
       <c r="G287" s="3" t="n"/>
-      <c r="H287" s="14" t="n"/>
+      <c r="H287" s="15" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="3" t="n"/>
@@ -11066,7 +11084,7 @@
       <c r="C288" s="3" t="n"/>
       <c r="F288" s="3" t="n"/>
       <c r="G288" s="3" t="n"/>
-      <c r="H288" s="14" t="n"/>
+      <c r="H288" s="15" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="3" t="n"/>
@@ -11074,7 +11092,7 @@
       <c r="C289" s="3" t="n"/>
       <c r="F289" s="3" t="n"/>
       <c r="G289" s="3" t="n"/>
-      <c r="H289" s="14" t="n"/>
+      <c r="H289" s="15" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="3" t="n"/>
@@ -11082,7 +11100,7 @@
       <c r="C290" s="3" t="n"/>
       <c r="F290" s="3" t="n"/>
       <c r="G290" s="3" t="n"/>
-      <c r="H290" s="14" t="n"/>
+      <c r="H290" s="15" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="3" t="n"/>
@@ -11090,7 +11108,7 @@
       <c r="C291" s="3" t="n"/>
       <c r="F291" s="3" t="n"/>
       <c r="G291" s="3" t="n"/>
-      <c r="H291" s="14" t="n"/>
+      <c r="H291" s="15" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="3" t="n"/>
@@ -11098,7 +11116,7 @@
       <c r="C292" s="3" t="n"/>
       <c r="F292" s="3" t="n"/>
       <c r="G292" s="3" t="n"/>
-      <c r="H292" s="14" t="n"/>
+      <c r="H292" s="15" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="3" t="n"/>
@@ -11106,7 +11124,7 @@
       <c r="C293" s="3" t="n"/>
       <c r="F293" s="3" t="n"/>
       <c r="G293" s="3" t="n"/>
-      <c r="H293" s="14" t="n"/>
+      <c r="H293" s="15" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="3" t="n"/>
@@ -11114,7 +11132,7 @@
       <c r="C294" s="3" t="n"/>
       <c r="F294" s="3" t="n"/>
       <c r="G294" s="3" t="n"/>
-      <c r="H294" s="14" t="n"/>
+      <c r="H294" s="15" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="3" t="n"/>
@@ -11122,7 +11140,7 @@
       <c r="C295" s="3" t="n"/>
       <c r="F295" s="3" t="n"/>
       <c r="G295" s="3" t="n"/>
-      <c r="H295" s="14" t="n"/>
+      <c r="H295" s="15" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="3" t="n"/>
@@ -11130,7 +11148,7 @@
       <c r="C296" s="3" t="n"/>
       <c r="F296" s="3" t="n"/>
       <c r="G296" s="3" t="n"/>
-      <c r="H296" s="14" t="n"/>
+      <c r="H296" s="15" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="3" t="n"/>
@@ -11138,7 +11156,7 @@
       <c r="C297" s="3" t="n"/>
       <c r="F297" s="3" t="n"/>
       <c r="G297" s="3" t="n"/>
-      <c r="H297" s="14" t="n"/>
+      <c r="H297" s="15" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="3" t="n"/>
@@ -11146,7 +11164,7 @@
       <c r="C298" s="3" t="n"/>
       <c r="F298" s="3" t="n"/>
       <c r="G298" s="3" t="n"/>
-      <c r="H298" s="14" t="n"/>
+      <c r="H298" s="15" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="3" t="n"/>
@@ -11154,7 +11172,7 @@
       <c r="C299" s="3" t="n"/>
       <c r="F299" s="3" t="n"/>
       <c r="G299" s="3" t="n"/>
-      <c r="H299" s="14" t="n"/>
+      <c r="H299" s="15" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="3" t="n"/>
@@ -11162,7 +11180,7 @@
       <c r="C300" s="3" t="n"/>
       <c r="F300" s="3" t="n"/>
       <c r="G300" s="3" t="n"/>
-      <c r="H300" s="14" t="n"/>
+      <c r="H300" s="15" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="3" t="n"/>
@@ -11170,7 +11188,7 @@
       <c r="C301" s="3" t="n"/>
       <c r="F301" s="3" t="n"/>
       <c r="G301" s="3" t="n"/>
-      <c r="H301" s="14" t="n"/>
+      <c r="H301" s="15" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="3" t="n"/>
@@ -11178,7 +11196,7 @@
       <c r="C302" s="3" t="n"/>
       <c r="F302" s="3" t="n"/>
       <c r="G302" s="3" t="n"/>
-      <c r="H302" s="14" t="n"/>
+      <c r="H302" s="15" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="3" t="n"/>
@@ -11186,7 +11204,7 @@
       <c r="C303" s="3" t="n"/>
       <c r="F303" s="3" t="n"/>
       <c r="G303" s="3" t="n"/>
-      <c r="H303" s="14" t="n"/>
+      <c r="H303" s="15" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="3" t="n"/>
@@ -11194,7 +11212,7 @@
       <c r="C304" s="3" t="n"/>
       <c r="F304" s="3" t="n"/>
       <c r="G304" s="3" t="n"/>
-      <c r="H304" s="14" t="n"/>
+      <c r="H304" s="15" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="3" t="n"/>
@@ -11202,7 +11220,7 @@
       <c r="C305" s="3" t="n"/>
       <c r="F305" s="3" t="n"/>
       <c r="G305" s="3" t="n"/>
-      <c r="H305" s="14" t="n"/>
+      <c r="H305" s="15" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="3" t="n"/>
@@ -11210,7 +11228,7 @@
       <c r="C306" s="3" t="n"/>
       <c r="F306" s="3" t="n"/>
       <c r="G306" s="3" t="n"/>
-      <c r="H306" s="14" t="n"/>
+      <c r="H306" s="15" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="3" t="n"/>
@@ -11218,7 +11236,7 @@
       <c r="C307" s="3" t="n"/>
       <c r="F307" s="3" t="n"/>
       <c r="G307" s="3" t="n"/>
-      <c r="H307" s="14" t="n"/>
+      <c r="H307" s="15" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="3" t="n"/>
@@ -11226,7 +11244,7 @@
       <c r="C308" s="3" t="n"/>
       <c r="F308" s="3" t="n"/>
       <c r="G308" s="3" t="n"/>
-      <c r="H308" s="14" t="n"/>
+      <c r="H308" s="15" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="3" t="n"/>
@@ -11234,7 +11252,7 @@
       <c r="C309" s="3" t="n"/>
       <c r="F309" s="3" t="n"/>
       <c r="G309" s="3" t="n"/>
-      <c r="H309" s="14" t="n"/>
+      <c r="H309" s="15" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="3" t="n"/>
@@ -11242,7 +11260,7 @@
       <c r="C310" s="3" t="n"/>
       <c r="F310" s="3" t="n"/>
       <c r="G310" s="3" t="n"/>
-      <c r="H310" s="14" t="n"/>
+      <c r="H310" s="15" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="3" t="n"/>
@@ -11250,7 +11268,7 @@
       <c r="C311" s="3" t="n"/>
       <c r="F311" s="3" t="n"/>
       <c r="G311" s="3" t="n"/>
-      <c r="H311" s="14" t="n"/>
+      <c r="H311" s="15" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="3" t="n"/>
@@ -11258,7 +11276,7 @@
       <c r="C312" s="3" t="n"/>
       <c r="F312" s="3" t="n"/>
       <c r="G312" s="3" t="n"/>
-      <c r="H312" s="14" t="n"/>
+      <c r="H312" s="15" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="3" t="n"/>
@@ -11266,7 +11284,7 @@
       <c r="C313" s="3" t="n"/>
       <c r="F313" s="3" t="n"/>
       <c r="G313" s="3" t="n"/>
-      <c r="H313" s="14" t="n"/>
+      <c r="H313" s="15" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="3" t="n"/>
@@ -11274,7 +11292,7 @@
       <c r="C314" s="3" t="n"/>
       <c r="F314" s="3" t="n"/>
       <c r="G314" s="3" t="n"/>
-      <c r="H314" s="14" t="n"/>
+      <c r="H314" s="15" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="3" t="n"/>
@@ -11282,7 +11300,7 @@
       <c r="C315" s="3" t="n"/>
       <c r="F315" s="3" t="n"/>
       <c r="G315" s="3" t="n"/>
-      <c r="H315" s="14" t="n"/>
+      <c r="H315" s="15" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="3" t="n"/>
@@ -11290,7 +11308,7 @@
       <c r="C316" s="3" t="n"/>
       <c r="F316" s="3" t="n"/>
       <c r="G316" s="3" t="n"/>
-      <c r="H316" s="14" t="n"/>
+      <c r="H316" s="15" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="3" t="n"/>
@@ -11298,7 +11316,7 @@
       <c r="C317" s="3" t="n"/>
       <c r="F317" s="3" t="n"/>
       <c r="G317" s="3" t="n"/>
-      <c r="H317" s="14" t="n"/>
+      <c r="H317" s="15" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="3" t="n"/>
@@ -11306,7 +11324,7 @@
       <c r="C318" s="3" t="n"/>
       <c r="F318" s="3" t="n"/>
       <c r="G318" s="3" t="n"/>
-      <c r="H318" s="14" t="n"/>
+      <c r="H318" s="15" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="3" t="n"/>
@@ -11314,7 +11332,7 @@
       <c r="C319" s="3" t="n"/>
       <c r="F319" s="3" t="n"/>
       <c r="G319" s="3" t="n"/>
-      <c r="H319" s="14" t="n"/>
+      <c r="H319" s="15" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="3" t="n"/>
@@ -11322,7 +11340,7 @@
       <c r="C320" s="3" t="n"/>
       <c r="F320" s="3" t="n"/>
       <c r="G320" s="3" t="n"/>
-      <c r="H320" s="14" t="n"/>
+      <c r="H320" s="15" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="3" t="n"/>
@@ -11330,7 +11348,7 @@
       <c r="C321" s="3" t="n"/>
       <c r="F321" s="3" t="n"/>
       <c r="G321" s="3" t="n"/>
-      <c r="H321" s="14" t="n"/>
+      <c r="H321" s="15" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="3" t="n"/>
@@ -11338,7 +11356,7 @@
       <c r="C322" s="3" t="n"/>
       <c r="F322" s="3" t="n"/>
       <c r="G322" s="3" t="n"/>
-      <c r="H322" s="14" t="n"/>
+      <c r="H322" s="15" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="3" t="n"/>
@@ -11346,7 +11364,7 @@
       <c r="C323" s="3" t="n"/>
       <c r="F323" s="3" t="n"/>
       <c r="G323" s="3" t="n"/>
-      <c r="H323" s="14" t="n"/>
+      <c r="H323" s="15" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="3" t="n"/>
@@ -11354,7 +11372,7 @@
       <c r="C324" s="3" t="n"/>
       <c r="F324" s="3" t="n"/>
       <c r="G324" s="3" t="n"/>
-      <c r="H324" s="14" t="n"/>
+      <c r="H324" s="15" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="3" t="n"/>
@@ -11362,7 +11380,7 @@
       <c r="C325" s="3" t="n"/>
       <c r="F325" s="3" t="n"/>
       <c r="G325" s="3" t="n"/>
-      <c r="H325" s="14" t="n"/>
+      <c r="H325" s="15" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="3" t="n"/>
@@ -11370,7 +11388,7 @@
       <c r="C326" s="3" t="n"/>
       <c r="F326" s="3" t="n"/>
       <c r="G326" s="3" t="n"/>
-      <c r="H326" s="14" t="n"/>
+      <c r="H326" s="15" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="3" t="n"/>
@@ -11378,7 +11396,7 @@
       <c r="C327" s="3" t="n"/>
       <c r="F327" s="3" t="n"/>
       <c r="G327" s="3" t="n"/>
-      <c r="H327" s="14" t="n"/>
+      <c r="H327" s="15" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="3" t="n"/>
@@ -11386,7 +11404,7 @@
       <c r="C328" s="3" t="n"/>
       <c r="F328" s="3" t="n"/>
       <c r="G328" s="3" t="n"/>
-      <c r="H328" s="14" t="n"/>
+      <c r="H328" s="15" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="3" t="n"/>
@@ -11394,7 +11412,7 @@
       <c r="C329" s="3" t="n"/>
       <c r="F329" s="3" t="n"/>
       <c r="G329" s="3" t="n"/>
-      <c r="H329" s="14" t="n"/>
+      <c r="H329" s="15" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="3" t="n"/>
@@ -11402,7 +11420,7 @@
       <c r="C330" s="3" t="n"/>
       <c r="F330" s="3" t="n"/>
       <c r="G330" s="3" t="n"/>
-      <c r="H330" s="14" t="n"/>
+      <c r="H330" s="15" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="3" t="n"/>
@@ -11410,7 +11428,7 @@
       <c r="C331" s="3" t="n"/>
       <c r="F331" s="3" t="n"/>
       <c r="G331" s="3" t="n"/>
-      <c r="H331" s="14" t="n"/>
+      <c r="H331" s="15" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="3" t="n"/>
@@ -11418,7 +11436,7 @@
       <c r="C332" s="3" t="n"/>
       <c r="F332" s="3" t="n"/>
       <c r="G332" s="3" t="n"/>
-      <c r="H332" s="14" t="n"/>
+      <c r="H332" s="15" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="3" t="n"/>
@@ -11426,7 +11444,7 @@
       <c r="C333" s="3" t="n"/>
       <c r="F333" s="3" t="n"/>
       <c r="G333" s="3" t="n"/>
-      <c r="H333" s="14" t="n"/>
+      <c r="H333" s="15" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="3" t="n"/>
@@ -11434,7 +11452,7 @@
       <c r="C334" s="3" t="n"/>
       <c r="F334" s="3" t="n"/>
       <c r="G334" s="3" t="n"/>
-      <c r="H334" s="14" t="n"/>
+      <c r="H334" s="15" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="3" t="n"/>
@@ -11442,7 +11460,7 @@
       <c r="C335" s="3" t="n"/>
       <c r="F335" s="3" t="n"/>
       <c r="G335" s="3" t="n"/>
-      <c r="H335" s="14" t="n"/>
+      <c r="H335" s="15" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="3" t="n"/>
@@ -11450,7 +11468,7 @@
       <c r="C336" s="3" t="n"/>
       <c r="F336" s="3" t="n"/>
       <c r="G336" s="3" t="n"/>
-      <c r="H336" s="14" t="n"/>
+      <c r="H336" s="15" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="3" t="n"/>
@@ -11458,7 +11476,7 @@
       <c r="C337" s="3" t="n"/>
       <c r="F337" s="3" t="n"/>
       <c r="G337" s="3" t="n"/>
-      <c r="H337" s="14" t="n"/>
+      <c r="H337" s="15" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="3" t="n"/>
@@ -11466,7 +11484,7 @@
       <c r="C338" s="3" t="n"/>
       <c r="F338" s="3" t="n"/>
       <c r="G338" s="3" t="n"/>
-      <c r="H338" s="14" t="n"/>
+      <c r="H338" s="15" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="3" t="n"/>
@@ -11474,7 +11492,7 @@
       <c r="C339" s="3" t="n"/>
       <c r="F339" s="3" t="n"/>
       <c r="G339" s="3" t="n"/>
-      <c r="H339" s="14" t="n"/>
+      <c r="H339" s="15" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="3" t="n"/>
@@ -11482,7 +11500,7 @@
       <c r="C340" s="3" t="n"/>
       <c r="F340" s="3" t="n"/>
       <c r="G340" s="3" t="n"/>
-      <c r="H340" s="14" t="n"/>
+      <c r="H340" s="15" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="3" t="n"/>
@@ -11490,7 +11508,7 @@
       <c r="C341" s="3" t="n"/>
       <c r="F341" s="3" t="n"/>
       <c r="G341" s="3" t="n"/>
-      <c r="H341" s="14" t="n"/>
+      <c r="H341" s="15" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="3" t="n"/>
@@ -11498,7 +11516,7 @@
       <c r="C342" s="3" t="n"/>
       <c r="F342" s="3" t="n"/>
       <c r="G342" s="3" t="n"/>
-      <c r="H342" s="14" t="n"/>
+      <c r="H342" s="15" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="3" t="n"/>
@@ -11506,7 +11524,7 @@
       <c r="C343" s="3" t="n"/>
       <c r="F343" s="3" t="n"/>
       <c r="G343" s="3" t="n"/>
-      <c r="H343" s="14" t="n"/>
+      <c r="H343" s="15" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="3" t="n"/>
@@ -11514,7 +11532,7 @@
       <c r="C344" s="3" t="n"/>
       <c r="F344" s="3" t="n"/>
       <c r="G344" s="3" t="n"/>
-      <c r="H344" s="14" t="n"/>
+      <c r="H344" s="15" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="3" t="n"/>
@@ -11522,7 +11540,7 @@
       <c r="C345" s="3" t="n"/>
       <c r="F345" s="3" t="n"/>
       <c r="G345" s="3" t="n"/>
-      <c r="H345" s="14" t="n"/>
+      <c r="H345" s="15" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="3" t="n"/>
@@ -11530,7 +11548,7 @@
       <c r="C346" s="3" t="n"/>
       <c r="F346" s="3" t="n"/>
       <c r="G346" s="3" t="n"/>
-      <c r="H346" s="14" t="n"/>
+      <c r="H346" s="15" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="3" t="n"/>
@@ -11538,7 +11556,7 @@
       <c r="C347" s="3" t="n"/>
       <c r="F347" s="3" t="n"/>
       <c r="G347" s="3" t="n"/>
-      <c r="H347" s="14" t="n"/>
+      <c r="H347" s="15" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="3" t="n"/>
@@ -11546,7 +11564,7 @@
       <c r="C348" s="3" t="n"/>
       <c r="F348" s="3" t="n"/>
       <c r="G348" s="3" t="n"/>
-      <c r="H348" s="14" t="n"/>
+      <c r="H348" s="15" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="3" t="n"/>
@@ -11554,7 +11572,7 @@
       <c r="C349" s="3" t="n"/>
       <c r="F349" s="3" t="n"/>
       <c r="G349" s="3" t="n"/>
-      <c r="H349" s="14" t="n"/>
+      <c r="H349" s="15" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="3" t="n"/>
@@ -11562,7 +11580,7 @@
       <c r="C350" s="3" t="n"/>
       <c r="F350" s="3" t="n"/>
       <c r="G350" s="3" t="n"/>
-      <c r="H350" s="14" t="n"/>
+      <c r="H350" s="15" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="3" t="n"/>
@@ -11570,7 +11588,7 @@
       <c r="C351" s="3" t="n"/>
       <c r="F351" s="3" t="n"/>
       <c r="G351" s="3" t="n"/>
-      <c r="H351" s="14" t="n"/>
+      <c r="H351" s="15" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="3" t="n"/>
@@ -11578,7 +11596,7 @@
       <c r="C352" s="3" t="n"/>
       <c r="F352" s="3" t="n"/>
       <c r="G352" s="3" t="n"/>
-      <c r="H352" s="14" t="n"/>
+      <c r="H352" s="15" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="3" t="n"/>
@@ -11586,7 +11604,7 @@
       <c r="C353" s="3" t="n"/>
       <c r="F353" s="3" t="n"/>
       <c r="G353" s="3" t="n"/>
-      <c r="H353" s="14" t="n"/>
+      <c r="H353" s="15" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="3" t="n"/>
@@ -11594,7 +11612,7 @@
       <c r="C354" s="3" t="n"/>
       <c r="F354" s="3" t="n"/>
       <c r="G354" s="3" t="n"/>
-      <c r="H354" s="14" t="n"/>
+      <c r="H354" s="15" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="3" t="n"/>
@@ -11602,7 +11620,7 @@
       <c r="C355" s="3" t="n"/>
       <c r="F355" s="3" t="n"/>
       <c r="G355" s="3" t="n"/>
-      <c r="H355" s="14" t="n"/>
+      <c r="H355" s="15" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="3" t="n"/>
@@ -11610,7 +11628,7 @@
       <c r="C356" s="3" t="n"/>
       <c r="F356" s="3" t="n"/>
       <c r="G356" s="3" t="n"/>
-      <c r="H356" s="14" t="n"/>
+      <c r="H356" s="15" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="3" t="n"/>
@@ -11618,7 +11636,7 @@
       <c r="C357" s="3" t="n"/>
       <c r="F357" s="3" t="n"/>
       <c r="G357" s="3" t="n"/>
-      <c r="H357" s="14" t="n"/>
+      <c r="H357" s="15" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="3" t="n"/>
@@ -11626,7 +11644,7 @@
       <c r="C358" s="3" t="n"/>
       <c r="F358" s="3" t="n"/>
       <c r="G358" s="3" t="n"/>
-      <c r="H358" s="14" t="n"/>
+      <c r="H358" s="15" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="3" t="n"/>
@@ -11634,7 +11652,7 @@
       <c r="C359" s="3" t="n"/>
       <c r="F359" s="3" t="n"/>
       <c r="G359" s="3" t="n"/>
-      <c r="H359" s="14" t="n"/>
+      <c r="H359" s="15" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="3" t="n"/>
@@ -11642,7 +11660,7 @@
       <c r="C360" s="3" t="n"/>
       <c r="F360" s="3" t="n"/>
       <c r="G360" s="3" t="n"/>
-      <c r="H360" s="14" t="n"/>
+      <c r="H360" s="15" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="3" t="n"/>
@@ -11650,7 +11668,7 @@
       <c r="C361" s="3" t="n"/>
       <c r="F361" s="3" t="n"/>
       <c r="G361" s="3" t="n"/>
-      <c r="H361" s="14" t="n"/>
+      <c r="H361" s="15" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="3" t="n"/>
@@ -11658,7 +11676,7 @@
       <c r="C362" s="3" t="n"/>
       <c r="F362" s="3" t="n"/>
       <c r="G362" s="3" t="n"/>
-      <c r="H362" s="14" t="n"/>
+      <c r="H362" s="15" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="3" t="n"/>
@@ -11666,7 +11684,7 @@
       <c r="C363" s="3" t="n"/>
       <c r="F363" s="3" t="n"/>
       <c r="G363" s="3" t="n"/>
-      <c r="H363" s="14" t="n"/>
+      <c r="H363" s="15" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="3" t="n"/>
@@ -11674,7 +11692,7 @@
       <c r="C364" s="3" t="n"/>
       <c r="F364" s="3" t="n"/>
       <c r="G364" s="3" t="n"/>
-      <c r="H364" s="14" t="n"/>
+      <c r="H364" s="15" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="3" t="n"/>
@@ -11682,7 +11700,7 @@
       <c r="C365" s="3" t="n"/>
       <c r="F365" s="3" t="n"/>
       <c r="G365" s="3" t="n"/>
-      <c r="H365" s="14" t="n"/>
+      <c r="H365" s="15" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="3" t="n"/>
@@ -11690,7 +11708,7 @@
       <c r="C366" s="3" t="n"/>
       <c r="F366" s="3" t="n"/>
       <c r="G366" s="3" t="n"/>
-      <c r="H366" s="14" t="n"/>
+      <c r="H366" s="15" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="3" t="n"/>
@@ -11698,7 +11716,7 @@
       <c r="C367" s="3" t="n"/>
       <c r="F367" s="3" t="n"/>
       <c r="G367" s="3" t="n"/>
-      <c r="H367" s="14" t="n"/>
+      <c r="H367" s="15" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="3" t="n"/>
@@ -11706,7 +11724,7 @@
       <c r="C368" s="3" t="n"/>
       <c r="F368" s="3" t="n"/>
       <c r="G368" s="3" t="n"/>
-      <c r="H368" s="14" t="n"/>
+      <c r="H368" s="15" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="3" t="n"/>
@@ -11714,7 +11732,7 @@
       <c r="C369" s="3" t="n"/>
       <c r="F369" s="3" t="n"/>
       <c r="G369" s="3" t="n"/>
-      <c r="H369" s="14" t="n"/>
+      <c r="H369" s="15" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="3" t="n"/>
@@ -11722,7 +11740,7 @@
       <c r="C370" s="3" t="n"/>
       <c r="F370" s="3" t="n"/>
       <c r="G370" s="3" t="n"/>
-      <c r="H370" s="14" t="n"/>
+      <c r="H370" s="15" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="3" t="n"/>
@@ -11730,7 +11748,7 @@
       <c r="C371" s="3" t="n"/>
       <c r="F371" s="3" t="n"/>
       <c r="G371" s="3" t="n"/>
-      <c r="H371" s="14" t="n"/>
+      <c r="H371" s="15" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="3" t="n"/>
@@ -11738,7 +11756,7 @@
       <c r="C372" s="3" t="n"/>
       <c r="F372" s="3" t="n"/>
       <c r="G372" s="3" t="n"/>
-      <c r="H372" s="14" t="n"/>
+      <c r="H372" s="15" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="3" t="n"/>
@@ -11746,7 +11764,7 @@
       <c r="C373" s="3" t="n"/>
       <c r="F373" s="3" t="n"/>
       <c r="G373" s="3" t="n"/>
-      <c r="H373" s="14" t="n"/>
+      <c r="H373" s="15" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="3" t="n"/>
@@ -11754,7 +11772,7 @@
       <c r="C374" s="3" t="n"/>
       <c r="F374" s="3" t="n"/>
       <c r="G374" s="3" t="n"/>
-      <c r="H374" s="14" t="n"/>
+      <c r="H374" s="15" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="3" t="n"/>
@@ -11762,7 +11780,7 @@
       <c r="C375" s="3" t="n"/>
       <c r="F375" s="3" t="n"/>
       <c r="G375" s="3" t="n"/>
-      <c r="H375" s="14" t="n"/>
+      <c r="H375" s="15" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="3" t="n"/>
@@ -11770,7 +11788,7 @@
       <c r="C376" s="3" t="n"/>
       <c r="F376" s="3" t="n"/>
       <c r="G376" s="3" t="n"/>
-      <c r="H376" s="14" t="n"/>
+      <c r="H376" s="15" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="3" t="n"/>
@@ -11778,7 +11796,7 @@
       <c r="C377" s="3" t="n"/>
       <c r="F377" s="3" t="n"/>
       <c r="G377" s="3" t="n"/>
-      <c r="H377" s="14" t="n"/>
+      <c r="H377" s="15" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="3" t="n"/>
@@ -11786,7 +11804,7 @@
       <c r="C378" s="3" t="n"/>
       <c r="F378" s="3" t="n"/>
       <c r="G378" s="3" t="n"/>
-      <c r="H378" s="14" t="n"/>
+      <c r="H378" s="15" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="3" t="n"/>
@@ -11794,7 +11812,7 @@
       <c r="C379" s="3" t="n"/>
       <c r="F379" s="3" t="n"/>
       <c r="G379" s="3" t="n"/>
-      <c r="H379" s="14" t="n"/>
+      <c r="H379" s="15" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="3" t="n"/>
@@ -11802,7 +11820,7 @@
       <c r="C380" s="3" t="n"/>
       <c r="F380" s="3" t="n"/>
       <c r="G380" s="3" t="n"/>
-      <c r="H380" s="14" t="n"/>
+      <c r="H380" s="15" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="3" t="n"/>
@@ -11810,7 +11828,7 @@
       <c r="C381" s="3" t="n"/>
       <c r="F381" s="3" t="n"/>
       <c r="G381" s="3" t="n"/>
-      <c r="H381" s="14" t="n"/>
+      <c r="H381" s="15" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="3" t="n"/>
@@ -11818,7 +11836,7 @@
       <c r="C382" s="3" t="n"/>
       <c r="F382" s="3" t="n"/>
       <c r="G382" s="3" t="n"/>
-      <c r="H382" s="14" t="n"/>
+      <c r="H382" s="15" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="3" t="n"/>
@@ -11826,7 +11844,7 @@
       <c r="C383" s="3" t="n"/>
       <c r="F383" s="3" t="n"/>
       <c r="G383" s="3" t="n"/>
-      <c r="H383" s="14" t="n"/>
+      <c r="H383" s="15" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="3" t="n"/>
@@ -11834,7 +11852,7 @@
       <c r="C384" s="3" t="n"/>
       <c r="F384" s="3" t="n"/>
       <c r="G384" s="3" t="n"/>
-      <c r="H384" s="14" t="n"/>
+      <c r="H384" s="15" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="3" t="n"/>
@@ -11842,7 +11860,7 @@
       <c r="C385" s="3" t="n"/>
       <c r="F385" s="3" t="n"/>
       <c r="G385" s="3" t="n"/>
-      <c r="H385" s="14" t="n"/>
+      <c r="H385" s="15" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="3" t="n"/>
@@ -11850,7 +11868,7 @@
       <c r="C386" s="3" t="n"/>
       <c r="F386" s="3" t="n"/>
       <c r="G386" s="3" t="n"/>
-      <c r="H386" s="14" t="n"/>
+      <c r="H386" s="15" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="3" t="n"/>
@@ -11858,7 +11876,7 @@
       <c r="C387" s="3" t="n"/>
       <c r="F387" s="3" t="n"/>
       <c r="G387" s="3" t="n"/>
-      <c r="H387" s="14" t="n"/>
+      <c r="H387" s="15" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="3" t="n"/>
@@ -11866,7 +11884,7 @@
       <c r="C388" s="3" t="n"/>
       <c r="F388" s="3" t="n"/>
       <c r="G388" s="3" t="n"/>
-      <c r="H388" s="14" t="n"/>
+      <c r="H388" s="15" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="3" t="n"/>
@@ -11874,7 +11892,7 @@
       <c r="C389" s="3" t="n"/>
       <c r="F389" s="3" t="n"/>
       <c r="G389" s="3" t="n"/>
-      <c r="H389" s="14" t="n"/>
+      <c r="H389" s="15" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="3" t="n"/>
@@ -11882,7 +11900,7 @@
       <c r="C390" s="3" t="n"/>
       <c r="F390" s="3" t="n"/>
       <c r="G390" s="3" t="n"/>
-      <c r="H390" s="14" t="n"/>
+      <c r="H390" s="15" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="3" t="n"/>
@@ -11890,7 +11908,7 @@
       <c r="C391" s="3" t="n"/>
       <c r="F391" s="3" t="n"/>
       <c r="G391" s="3" t="n"/>
-      <c r="H391" s="14" t="n"/>
+      <c r="H391" s="15" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="3" t="n"/>
@@ -11898,7 +11916,7 @@
       <c r="C392" s="3" t="n"/>
       <c r="F392" s="3" t="n"/>
       <c r="G392" s="3" t="n"/>
-      <c r="H392" s="14" t="n"/>
+      <c r="H392" s="15" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="3" t="n"/>
@@ -11906,7 +11924,7 @@
       <c r="C393" s="3" t="n"/>
       <c r="F393" s="3" t="n"/>
       <c r="G393" s="3" t="n"/>
-      <c r="H393" s="14" t="n"/>
+      <c r="H393" s="15" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="3" t="n"/>
@@ -11914,7 +11932,7 @@
       <c r="C394" s="3" t="n"/>
       <c r="F394" s="3" t="n"/>
       <c r="G394" s="3" t="n"/>
-      <c r="H394" s="14" t="n"/>
+      <c r="H394" s="15" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="3" t="n"/>
@@ -11922,7 +11940,7 @@
       <c r="C395" s="3" t="n"/>
       <c r="F395" s="3" t="n"/>
       <c r="G395" s="3" t="n"/>
-      <c r="H395" s="14" t="n"/>
+      <c r="H395" s="15" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="3" t="n"/>
@@ -11930,7 +11948,7 @@
       <c r="C396" s="3" t="n"/>
       <c r="F396" s="3" t="n"/>
       <c r="G396" s="3" t="n"/>
-      <c r="H396" s="14" t="n"/>
+      <c r="H396" s="15" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="3" t="n"/>
@@ -11938,7 +11956,7 @@
       <c r="C397" s="3" t="n"/>
       <c r="F397" s="3" t="n"/>
       <c r="G397" s="3" t="n"/>
-      <c r="H397" s="14" t="n"/>
+      <c r="H397" s="15" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="3" t="n"/>
@@ -11946,7 +11964,7 @@
       <c r="C398" s="3" t="n"/>
       <c r="F398" s="3" t="n"/>
       <c r="G398" s="3" t="n"/>
-      <c r="H398" s="14" t="n"/>
+      <c r="H398" s="15" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="3" t="n"/>
@@ -11954,7 +11972,7 @@
       <c r="C399" s="3" t="n"/>
       <c r="F399" s="3" t="n"/>
       <c r="G399" s="3" t="n"/>
-      <c r="H399" s="14" t="n"/>
+      <c r="H399" s="15" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="3" t="n"/>
@@ -11962,7 +11980,7 @@
       <c r="C400" s="3" t="n"/>
       <c r="F400" s="3" t="n"/>
       <c r="G400" s="3" t="n"/>
-      <c r="H400" s="14" t="n"/>
+      <c r="H400" s="15" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="3" t="n"/>
@@ -11970,7 +11988,7 @@
       <c r="C401" s="3" t="n"/>
       <c r="F401" s="3" t="n"/>
       <c r="G401" s="3" t="n"/>
-      <c r="H401" s="14" t="n"/>
+      <c r="H401" s="15" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="3" t="n"/>
@@ -11978,7 +11996,7 @@
       <c r="C402" s="3" t="n"/>
       <c r="F402" s="3" t="n"/>
       <c r="G402" s="3" t="n"/>
-      <c r="H402" s="14" t="n"/>
+      <c r="H402" s="15" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="3" t="n"/>
@@ -11986,7 +12004,7 @@
       <c r="C403" s="3" t="n"/>
       <c r="F403" s="3" t="n"/>
       <c r="G403" s="3" t="n"/>
-      <c r="H403" s="14" t="n"/>
+      <c r="H403" s="15" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="3" t="n"/>
@@ -11994,7 +12012,7 @@
       <c r="C404" s="3" t="n"/>
       <c r="F404" s="3" t="n"/>
       <c r="G404" s="3" t="n"/>
-      <c r="H404" s="14" t="n"/>
+      <c r="H404" s="15" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="3" t="n"/>
@@ -12002,7 +12020,7 @@
       <c r="C405" s="3" t="n"/>
       <c r="F405" s="3" t="n"/>
       <c r="G405" s="3" t="n"/>
-      <c r="H405" s="14" t="n"/>
+      <c r="H405" s="15" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="3" t="n"/>
@@ -12010,7 +12028,7 @@
       <c r="C406" s="3" t="n"/>
       <c r="F406" s="3" t="n"/>
       <c r="G406" s="3" t="n"/>
-      <c r="H406" s="14" t="n"/>
+      <c r="H406" s="15" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="3" t="n"/>
@@ -12018,7 +12036,7 @@
       <c r="C407" s="3" t="n"/>
       <c r="F407" s="3" t="n"/>
       <c r="G407" s="3" t="n"/>
-      <c r="H407" s="14" t="n"/>
+      <c r="H407" s="15" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="3" t="n"/>
@@ -12026,7 +12044,7 @@
       <c r="C408" s="3" t="n"/>
       <c r="F408" s="3" t="n"/>
       <c r="G408" s="3" t="n"/>
-      <c r="H408" s="14" t="n"/>
+      <c r="H408" s="15" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="3" t="n"/>
@@ -12034,7 +12052,7 @@
       <c r="C409" s="3" t="n"/>
       <c r="F409" s="3" t="n"/>
       <c r="G409" s="3" t="n"/>
-      <c r="H409" s="14" t="n"/>
+      <c r="H409" s="15" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="3" t="n"/>
@@ -12042,7 +12060,7 @@
       <c r="C410" s="3" t="n"/>
       <c r="F410" s="3" t="n"/>
       <c r="G410" s="3" t="n"/>
-      <c r="H410" s="14" t="n"/>
+      <c r="H410" s="15" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="3" t="n"/>
@@ -12050,7 +12068,7 @@
       <c r="C411" s="3" t="n"/>
       <c r="F411" s="3" t="n"/>
       <c r="G411" s="3" t="n"/>
-      <c r="H411" s="14" t="n"/>
+      <c r="H411" s="15" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="3" t="n"/>
@@ -12058,7 +12076,7 @@
       <c r="C412" s="3" t="n"/>
       <c r="F412" s="3" t="n"/>
       <c r="G412" s="3" t="n"/>
-      <c r="H412" s="14" t="n"/>
+      <c r="H412" s="15" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="3" t="n"/>
@@ -12066,7 +12084,7 @@
       <c r="C413" s="3" t="n"/>
       <c r="F413" s="3" t="n"/>
       <c r="G413" s="3" t="n"/>
-      <c r="H413" s="14" t="n"/>
+      <c r="H413" s="15" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="3" t="n"/>
@@ -12074,7 +12092,7 @@
       <c r="C414" s="3" t="n"/>
       <c r="F414" s="3" t="n"/>
       <c r="G414" s="3" t="n"/>
-      <c r="H414" s="14" t="n"/>
+      <c r="H414" s="15" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="3" t="n"/>
@@ -12082,7 +12100,7 @@
       <c r="C415" s="3" t="n"/>
       <c r="F415" s="3" t="n"/>
       <c r="G415" s="3" t="n"/>
-      <c r="H415" s="14" t="n"/>
+      <c r="H415" s="15" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="3" t="n"/>
@@ -12090,7 +12108,7 @@
       <c r="C416" s="3" t="n"/>
       <c r="F416" s="3" t="n"/>
       <c r="G416" s="3" t="n"/>
-      <c r="H416" s="14" t="n"/>
+      <c r="H416" s="15" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="3" t="n"/>
@@ -12098,7 +12116,7 @@
       <c r="C417" s="3" t="n"/>
       <c r="F417" s="3" t="n"/>
       <c r="G417" s="3" t="n"/>
-      <c r="H417" s="14" t="n"/>
+      <c r="H417" s="15" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="3" t="n"/>
@@ -12106,7 +12124,7 @@
       <c r="C418" s="3" t="n"/>
       <c r="F418" s="3" t="n"/>
       <c r="G418" s="3" t="n"/>
-      <c r="H418" s="14" t="n"/>
+      <c r="H418" s="15" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="3" t="n"/>
@@ -12114,7 +12132,7 @@
       <c r="C419" s="3" t="n"/>
       <c r="F419" s="3" t="n"/>
       <c r="G419" s="3" t="n"/>
-      <c r="H419" s="14" t="n"/>
+      <c r="H419" s="15" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="3" t="n"/>
@@ -12122,7 +12140,7 @@
       <c r="C420" s="3" t="n"/>
       <c r="F420" s="3" t="n"/>
       <c r="G420" s="3" t="n"/>
-      <c r="H420" s="14" t="n"/>
+      <c r="H420" s="15" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="3" t="n"/>
@@ -12130,7 +12148,7 @@
       <c r="C421" s="3" t="n"/>
       <c r="F421" s="3" t="n"/>
       <c r="G421" s="3" t="n"/>
-      <c r="H421" s="14" t="n"/>
+      <c r="H421" s="15" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="3" t="n"/>
@@ -12138,7 +12156,7 @@
       <c r="C422" s="3" t="n"/>
       <c r="F422" s="3" t="n"/>
       <c r="G422" s="3" t="n"/>
-      <c r="H422" s="14" t="n"/>
+      <c r="H422" s="15" t="n"/>
     </row>
     <row r="423">
       <c r="A423" s="3" t="n"/>
@@ -12146,7 +12164,7 @@
       <c r="C423" s="3" t="n"/>
       <c r="F423" s="3" t="n"/>
       <c r="G423" s="3" t="n"/>
-      <c r="H423" s="14" t="n"/>
+      <c r="H423" s="15" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="3" t="n"/>
@@ -12154,7 +12172,7 @@
       <c r="C424" s="3" t="n"/>
       <c r="F424" s="3" t="n"/>
       <c r="G424" s="3" t="n"/>
-      <c r="H424" s="14" t="n"/>
+      <c r="H424" s="15" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="3" t="n"/>
@@ -12162,7 +12180,7 @@
       <c r="C425" s="3" t="n"/>
       <c r="F425" s="3" t="n"/>
       <c r="G425" s="3" t="n"/>
-      <c r="H425" s="14" t="n"/>
+      <c r="H425" s="15" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="3" t="n"/>
@@ -12170,7 +12188,7 @@
       <c r="C426" s="3" t="n"/>
       <c r="F426" s="3" t="n"/>
       <c r="G426" s="3" t="n"/>
-      <c r="H426" s="14" t="n"/>
+      <c r="H426" s="15" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="3" t="n"/>
@@ -12178,7 +12196,7 @@
       <c r="C427" s="3" t="n"/>
       <c r="F427" s="3" t="n"/>
       <c r="G427" s="3" t="n"/>
-      <c r="H427" s="14" t="n"/>
+      <c r="H427" s="15" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="3" t="n"/>
@@ -12186,7 +12204,7 @@
       <c r="C428" s="3" t="n"/>
       <c r="F428" s="3" t="n"/>
       <c r="G428" s="3" t="n"/>
-      <c r="H428" s="14" t="n"/>
+      <c r="H428" s="15" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="3" t="n"/>
@@ -12194,7 +12212,7 @@
       <c r="C429" s="3" t="n"/>
       <c r="F429" s="3" t="n"/>
       <c r="G429" s="3" t="n"/>
-      <c r="H429" s="14" t="n"/>
+      <c r="H429" s="15" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="3" t="n"/>
@@ -12202,7 +12220,7 @@
       <c r="C430" s="3" t="n"/>
       <c r="F430" s="3" t="n"/>
       <c r="G430" s="3" t="n"/>
-      <c r="H430" s="14" t="n"/>
+      <c r="H430" s="15" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="3" t="n"/>
@@ -12210,7 +12228,7 @@
       <c r="C431" s="3" t="n"/>
       <c r="F431" s="3" t="n"/>
       <c r="G431" s="3" t="n"/>
-      <c r="H431" s="14" t="n"/>
+      <c r="H431" s="15" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="3" t="n"/>
@@ -12218,7 +12236,7 @@
       <c r="C432" s="3" t="n"/>
       <c r="F432" s="3" t="n"/>
       <c r="G432" s="3" t="n"/>
-      <c r="H432" s="14" t="n"/>
+      <c r="H432" s="15" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="3" t="n"/>
@@ -12226,7 +12244,7 @@
       <c r="C433" s="3" t="n"/>
       <c r="F433" s="3" t="n"/>
       <c r="G433" s="3" t="n"/>
-      <c r="H433" s="14" t="n"/>
+      <c r="H433" s="15" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="3" t="n"/>
@@ -12234,7 +12252,7 @@
       <c r="C434" s="3" t="n"/>
       <c r="F434" s="3" t="n"/>
       <c r="G434" s="3" t="n"/>
-      <c r="H434" s="14" t="n"/>
+      <c r="H434" s="15" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="3" t="n"/>
@@ -12242,7 +12260,7 @@
       <c r="C435" s="3" t="n"/>
       <c r="F435" s="3" t="n"/>
       <c r="G435" s="3" t="n"/>
-      <c r="H435" s="14" t="n"/>
+      <c r="H435" s="15" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="3" t="n"/>
@@ -12250,7 +12268,7 @@
       <c r="C436" s="3" t="n"/>
       <c r="F436" s="3" t="n"/>
       <c r="G436" s="3" t="n"/>
-      <c r="H436" s="14" t="n"/>
+      <c r="H436" s="15" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="3" t="n"/>
@@ -12258,7 +12276,7 @@
       <c r="C437" s="3" t="n"/>
       <c r="F437" s="3" t="n"/>
       <c r="G437" s="3" t="n"/>
-      <c r="H437" s="14" t="n"/>
+      <c r="H437" s="15" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="3" t="n"/>
@@ -12266,7 +12284,7 @@
       <c r="C438" s="3" t="n"/>
       <c r="F438" s="3" t="n"/>
       <c r="G438" s="3" t="n"/>
-      <c r="H438" s="14" t="n"/>
+      <c r="H438" s="15" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="3" t="n"/>
@@ -12274,7 +12292,7 @@
       <c r="C439" s="3" t="n"/>
       <c r="F439" s="3" t="n"/>
       <c r="G439" s="3" t="n"/>
-      <c r="H439" s="14" t="n"/>
+      <c r="H439" s="15" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="3" t="n"/>
@@ -12282,7 +12300,7 @@
       <c r="C440" s="3" t="n"/>
       <c r="F440" s="3" t="n"/>
       <c r="G440" s="3" t="n"/>
-      <c r="H440" s="14" t="n"/>
+      <c r="H440" s="15" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="3" t="n"/>
@@ -12290,7 +12308,7 @@
       <c r="C441" s="3" t="n"/>
       <c r="F441" s="3" t="n"/>
       <c r="G441" s="3" t="n"/>
-      <c r="H441" s="14" t="n"/>
+      <c r="H441" s="15" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="3" t="n"/>
@@ -12298,7 +12316,7 @@
       <c r="C442" s="3" t="n"/>
       <c r="F442" s="3" t="n"/>
       <c r="G442" s="3" t="n"/>
-      <c r="H442" s="14" t="n"/>
+      <c r="H442" s="15" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="3" t="n"/>
@@ -12306,7 +12324,7 @@
       <c r="C443" s="3" t="n"/>
       <c r="F443" s="3" t="n"/>
       <c r="G443" s="3" t="n"/>
-      <c r="H443" s="14" t="n"/>
+      <c r="H443" s="15" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="3" t="n"/>
@@ -12314,7 +12332,7 @@
       <c r="C444" s="3" t="n"/>
       <c r="F444" s="3" t="n"/>
       <c r="G444" s="3" t="n"/>
-      <c r="H444" s="14" t="n"/>
+      <c r="H444" s="15" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="3" t="n"/>
@@ -12322,7 +12340,7 @@
       <c r="C445" s="3" t="n"/>
       <c r="F445" s="3" t="n"/>
       <c r="G445" s="3" t="n"/>
-      <c r="H445" s="14" t="n"/>
+      <c r="H445" s="15" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="3" t="n"/>
@@ -12330,7 +12348,7 @@
       <c r="C446" s="3" t="n"/>
       <c r="F446" s="3" t="n"/>
       <c r="G446" s="3" t="n"/>
-      <c r="H446" s="14" t="n"/>
+      <c r="H446" s="15" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="3" t="n"/>
@@ -12338,7 +12356,7 @@
       <c r="C447" s="3" t="n"/>
       <c r="F447" s="3" t="n"/>
       <c r="G447" s="3" t="n"/>
-      <c r="H447" s="14" t="n"/>
+      <c r="H447" s="15" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="3" t="n"/>
@@ -12346,7 +12364,7 @@
       <c r="C448" s="3" t="n"/>
       <c r="F448" s="3" t="n"/>
       <c r="G448" s="3" t="n"/>
-      <c r="H448" s="14" t="n"/>
+      <c r="H448" s="15" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="3" t="n"/>
@@ -12354,7 +12372,7 @@
       <c r="C449" s="3" t="n"/>
       <c r="F449" s="3" t="n"/>
       <c r="G449" s="3" t="n"/>
-      <c r="H449" s="14" t="n"/>
+      <c r="H449" s="15" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="3" t="n"/>
@@ -12362,7 +12380,7 @@
       <c r="C450" s="3" t="n"/>
       <c r="F450" s="3" t="n"/>
       <c r="G450" s="3" t="n"/>
-      <c r="H450" s="14" t="n"/>
+      <c r="H450" s="15" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="3" t="n"/>
@@ -12370,7 +12388,7 @@
       <c r="C451" s="3" t="n"/>
       <c r="F451" s="3" t="n"/>
       <c r="G451" s="3" t="n"/>
-      <c r="H451" s="14" t="n"/>
+      <c r="H451" s="15" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="3" t="n"/>
@@ -12378,7 +12396,7 @@
       <c r="C452" s="3" t="n"/>
       <c r="F452" s="3" t="n"/>
       <c r="G452" s="3" t="n"/>
-      <c r="H452" s="14" t="n"/>
+      <c r="H452" s="15" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="3" t="n"/>
@@ -12386,7 +12404,7 @@
       <c r="C453" s="3" t="n"/>
       <c r="F453" s="3" t="n"/>
       <c r="G453" s="3" t="n"/>
-      <c r="H453" s="14" t="n"/>
+      <c r="H453" s="15" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="3" t="n"/>
@@ -12394,7 +12412,7 @@
       <c r="C454" s="3" t="n"/>
       <c r="F454" s="3" t="n"/>
       <c r="G454" s="3" t="n"/>
-      <c r="H454" s="14" t="n"/>
+      <c r="H454" s="15" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="3" t="n"/>
@@ -12402,7 +12420,7 @@
       <c r="C455" s="3" t="n"/>
       <c r="F455" s="3" t="n"/>
       <c r="G455" s="3" t="n"/>
-      <c r="H455" s="14" t="n"/>
+      <c r="H455" s="15" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="3" t="n"/>
@@ -12410,7 +12428,7 @@
       <c r="C456" s="3" t="n"/>
       <c r="F456" s="3" t="n"/>
       <c r="G456" s="3" t="n"/>
-      <c r="H456" s="14" t="n"/>
+      <c r="H456" s="15" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="3" t="n"/>
@@ -12418,7 +12436,7 @@
       <c r="C457" s="3" t="n"/>
       <c r="F457" s="3" t="n"/>
       <c r="G457" s="3" t="n"/>
-      <c r="H457" s="14" t="n"/>
+      <c r="H457" s="15" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="3" t="n"/>
@@ -12426,7 +12444,7 @@
       <c r="C458" s="3" t="n"/>
       <c r="F458" s="3" t="n"/>
       <c r="G458" s="3" t="n"/>
-      <c r="H458" s="14" t="n"/>
+      <c r="H458" s="15" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="3" t="n"/>
@@ -12434,7 +12452,7 @@
       <c r="C459" s="3" t="n"/>
       <c r="F459" s="3" t="n"/>
       <c r="G459" s="3" t="n"/>
-      <c r="H459" s="14" t="n"/>
+      <c r="H459" s="15" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="3" t="n"/>
@@ -12442,7 +12460,7 @@
       <c r="C460" s="3" t="n"/>
       <c r="F460" s="3" t="n"/>
       <c r="G460" s="3" t="n"/>
-      <c r="H460" s="14" t="n"/>
+      <c r="H460" s="15" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="3" t="n"/>
@@ -12450,7 +12468,7 @@
       <c r="C461" s="3" t="n"/>
       <c r="F461" s="3" t="n"/>
       <c r="G461" s="3" t="n"/>
-      <c r="H461" s="14" t="n"/>
+      <c r="H461" s="15" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="3" t="n"/>
@@ -12458,7 +12476,7 @@
       <c r="C462" s="3" t="n"/>
       <c r="F462" s="3" t="n"/>
       <c r="G462" s="3" t="n"/>
-      <c r="H462" s="14" t="n"/>
+      <c r="H462" s="15" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="3" t="n"/>
@@ -12466,7 +12484,7 @@
       <c r="C463" s="3" t="n"/>
       <c r="F463" s="3" t="n"/>
       <c r="G463" s="3" t="n"/>
-      <c r="H463" s="14" t="n"/>
+      <c r="H463" s="15" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="3" t="n"/>
@@ -12474,7 +12492,7 @@
       <c r="C464" s="3" t="n"/>
       <c r="F464" s="3" t="n"/>
       <c r="G464" s="3" t="n"/>
-      <c r="H464" s="14" t="n"/>
+      <c r="H464" s="15" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="3" t="n"/>
@@ -12482,7 +12500,7 @@
       <c r="C465" s="3" t="n"/>
       <c r="F465" s="3" t="n"/>
       <c r="G465" s="3" t="n"/>
-      <c r="H465" s="14" t="n"/>
+      <c r="H465" s="15" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="3" t="n"/>
@@ -12490,7 +12508,7 @@
       <c r="C466" s="3" t="n"/>
       <c r="F466" s="3" t="n"/>
       <c r="G466" s="3" t="n"/>
-      <c r="H466" s="14" t="n"/>
+      <c r="H466" s="15" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="3" t="n"/>
@@ -12498,7 +12516,7 @@
       <c r="C467" s="3" t="n"/>
       <c r="F467" s="3" t="n"/>
       <c r="G467" s="3" t="n"/>
-      <c r="H467" s="14" t="n"/>
+      <c r="H467" s="15" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="3" t="n"/>
@@ -12506,7 +12524,7 @@
       <c r="C468" s="3" t="n"/>
       <c r="F468" s="3" t="n"/>
       <c r="G468" s="3" t="n"/>
-      <c r="H468" s="14" t="n"/>
+      <c r="H468" s="15" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="3" t="n"/>
@@ -12514,7 +12532,7 @@
       <c r="C469" s="3" t="n"/>
       <c r="F469" s="3" t="n"/>
       <c r="G469" s="3" t="n"/>
-      <c r="H469" s="14" t="n"/>
+      <c r="H469" s="15" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="3" t="n"/>
@@ -12522,7 +12540,7 @@
       <c r="C470" s="3" t="n"/>
       <c r="F470" s="3" t="n"/>
       <c r="G470" s="3" t="n"/>
-      <c r="H470" s="14" t="n"/>
+      <c r="H470" s="15" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="3" t="n"/>
@@ -12530,7 +12548,7 @@
       <c r="C471" s="3" t="n"/>
       <c r="F471" s="3" t="n"/>
       <c r="G471" s="3" t="n"/>
-      <c r="H471" s="14" t="n"/>
+      <c r="H471" s="15" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="3" t="n"/>
@@ -12538,7 +12556,7 @@
       <c r="C472" s="3" t="n"/>
       <c r="F472" s="3" t="n"/>
       <c r="G472" s="3" t="n"/>
-      <c r="H472" s="14" t="n"/>
+      <c r="H472" s="15" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="3" t="n"/>
@@ -12546,7 +12564,7 @@
       <c r="C473" s="3" t="n"/>
       <c r="F473" s="3" t="n"/>
       <c r="G473" s="3" t="n"/>
-      <c r="H473" s="14" t="n"/>
+      <c r="H473" s="15" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="3" t="n"/>
@@ -12554,7 +12572,7 @@
       <c r="C474" s="3" t="n"/>
       <c r="F474" s="3" t="n"/>
       <c r="G474" s="3" t="n"/>
-      <c r="H474" s="14" t="n"/>
+      <c r="H474" s="15" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="3" t="n"/>
@@ -12562,7 +12580,7 @@
       <c r="C475" s="3" t="n"/>
       <c r="F475" s="3" t="n"/>
       <c r="G475" s="3" t="n"/>
-      <c r="H475" s="14" t="n"/>
+      <c r="H475" s="15" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="3" t="n"/>
@@ -12570,7 +12588,7 @@
       <c r="C476" s="3" t="n"/>
       <c r="F476" s="3" t="n"/>
       <c r="G476" s="3" t="n"/>
-      <c r="H476" s="14" t="n"/>
+      <c r="H476" s="15" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="3" t="n"/>
@@ -12578,7 +12596,7 @@
       <c r="C477" s="3" t="n"/>
       <c r="F477" s="3" t="n"/>
       <c r="G477" s="3" t="n"/>
-      <c r="H477" s="14" t="n"/>
+      <c r="H477" s="15" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="3" t="n"/>
@@ -12586,7 +12604,7 @@
       <c r="C478" s="3" t="n"/>
       <c r="F478" s="3" t="n"/>
       <c r="G478" s="3" t="n"/>
-      <c r="H478" s="14" t="n"/>
+      <c r="H478" s="15" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="3" t="n"/>
@@ -12594,7 +12612,7 @@
       <c r="C479" s="3" t="n"/>
       <c r="F479" s="3" t="n"/>
       <c r="G479" s="3" t="n"/>
-      <c r="H479" s="14" t="n"/>
+      <c r="H479" s="15" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="3" t="n"/>
@@ -12602,7 +12620,7 @@
       <c r="C480" s="3" t="n"/>
       <c r="F480" s="3" t="n"/>
       <c r="G480" s="3" t="n"/>
-      <c r="H480" s="14" t="n"/>
+      <c r="H480" s="15" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="3" t="n"/>
@@ -12610,7 +12628,7 @@
       <c r="C481" s="3" t="n"/>
       <c r="F481" s="3" t="n"/>
       <c r="G481" s="3" t="n"/>
-      <c r="H481" s="14" t="n"/>
+      <c r="H481" s="15" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="3" t="n"/>
@@ -12618,7 +12636,7 @@
       <c r="C482" s="3" t="n"/>
       <c r="F482" s="3" t="n"/>
       <c r="G482" s="3" t="n"/>
-      <c r="H482" s="14" t="n"/>
+      <c r="H482" s="15" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="3" t="n"/>
@@ -12626,7 +12644,7 @@
       <c r="C483" s="3" t="n"/>
       <c r="F483" s="3" t="n"/>
       <c r="G483" s="3" t="n"/>
-      <c r="H483" s="14" t="n"/>
+      <c r="H483" s="15" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="3" t="n"/>
@@ -12634,7 +12652,7 @@
       <c r="C484" s="3" t="n"/>
       <c r="F484" s="3" t="n"/>
       <c r="G484" s="3" t="n"/>
-      <c r="H484" s="14" t="n"/>
+      <c r="H484" s="15" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="3" t="n"/>
@@ -12642,7 +12660,7 @@
       <c r="C485" s="3" t="n"/>
       <c r="F485" s="3" t="n"/>
       <c r="G485" s="3" t="n"/>
-      <c r="H485" s="14" t="n"/>
+      <c r="H485" s="15" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="3" t="n"/>
@@ -12650,7 +12668,7 @@
       <c r="C486" s="3" t="n"/>
       <c r="F486" s="3" t="n"/>
       <c r="G486" s="3" t="n"/>
-      <c r="H486" s="14" t="n"/>
+      <c r="H486" s="15" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="3" t="n"/>
@@ -12658,7 +12676,7 @@
       <c r="C487" s="3" t="n"/>
       <c r="F487" s="3" t="n"/>
       <c r="G487" s="3" t="n"/>
-      <c r="H487" s="14" t="n"/>
+      <c r="H487" s="15" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="3" t="n"/>
@@ -12666,7 +12684,7 @@
       <c r="C488" s="3" t="n"/>
       <c r="F488" s="3" t="n"/>
       <c r="G488" s="3" t="n"/>
-      <c r="H488" s="14" t="n"/>
+      <c r="H488" s="15" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="3" t="n"/>
@@ -12674,7 +12692,7 @@
       <c r="C489" s="3" t="n"/>
       <c r="F489" s="3" t="n"/>
       <c r="G489" s="3" t="n"/>
-      <c r="H489" s="14" t="n"/>
+      <c r="H489" s="15" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="3" t="n"/>
@@ -12682,7 +12700,7 @@
       <c r="C490" s="3" t="n"/>
       <c r="F490" s="3" t="n"/>
       <c r="G490" s="3" t="n"/>
-      <c r="H490" s="14" t="n"/>
+      <c r="H490" s="15" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="3" t="n"/>
@@ -12690,7 +12708,7 @@
       <c r="C491" s="3" t="n"/>
       <c r="F491" s="3" t="n"/>
       <c r="G491" s="3" t="n"/>
-      <c r="H491" s="14" t="n"/>
+      <c r="H491" s="15" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="3" t="n"/>
@@ -12698,7 +12716,7 @@
       <c r="C492" s="3" t="n"/>
       <c r="F492" s="3" t="n"/>
       <c r="G492" s="3" t="n"/>
-      <c r="H492" s="14" t="n"/>
+      <c r="H492" s="15" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="3" t="n"/>
@@ -12706,7 +12724,7 @@
       <c r="C493" s="3" t="n"/>
       <c r="F493" s="3" t="n"/>
       <c r="G493" s="3" t="n"/>
-      <c r="H493" s="14" t="n"/>
+      <c r="H493" s="15" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="3" t="n"/>
@@ -12714,7 +12732,7 @@
       <c r="C494" s="3" t="n"/>
       <c r="F494" s="3" t="n"/>
       <c r="G494" s="3" t="n"/>
-      <c r="H494" s="14" t="n"/>
+      <c r="H494" s="15" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="3" t="n"/>
@@ -12722,7 +12740,7 @@
       <c r="C495" s="3" t="n"/>
       <c r="F495" s="3" t="n"/>
       <c r="G495" s="3" t="n"/>
-      <c r="H495" s="14" t="n"/>
+      <c r="H495" s="15" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="3" t="n"/>
@@ -12730,7 +12748,7 @@
       <c r="C496" s="3" t="n"/>
       <c r="F496" s="3" t="n"/>
       <c r="G496" s="3" t="n"/>
-      <c r="H496" s="14" t="n"/>
+      <c r="H496" s="15" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="3" t="n"/>
@@ -12738,7 +12756,7 @@
       <c r="C497" s="3" t="n"/>
       <c r="F497" s="3" t="n"/>
       <c r="G497" s="3" t="n"/>
-      <c r="H497" s="14" t="n"/>
+      <c r="H497" s="15" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="3" t="n"/>
@@ -12746,7 +12764,7 @@
       <c r="C498" s="3" t="n"/>
       <c r="F498" s="3" t="n"/>
       <c r="G498" s="3" t="n"/>
-      <c r="H498" s="14" t="n"/>
+      <c r="H498" s="15" t="n"/>
     </row>
     <row r="499">
       <c r="A499" s="3" t="n"/>
@@ -12754,7 +12772,7 @@
       <c r="C499" s="3" t="n"/>
       <c r="F499" s="3" t="n"/>
       <c r="G499" s="3" t="n"/>
-      <c r="H499" s="14" t="n"/>
+      <c r="H499" s="15" t="n"/>
     </row>
     <row r="500">
       <c r="A500" s="3" t="n"/>
@@ -12762,7 +12780,7 @@
       <c r="C500" s="3" t="n"/>
       <c r="F500" s="3" t="n"/>
       <c r="G500" s="3" t="n"/>
-      <c r="H500" s="14" t="n"/>
+      <c r="H500" s="15" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="3" t="n"/>
@@ -12770,7 +12788,7 @@
       <c r="C501" s="3" t="n"/>
       <c r="F501" s="3" t="n"/>
       <c r="G501" s="3" t="n"/>
-      <c r="H501" s="14" t="n"/>
+      <c r="H501" s="15" t="n"/>
     </row>
     <row r="502">
       <c r="A502" s="3" t="n"/>
@@ -12778,7 +12796,7 @@
       <c r="C502" s="3" t="n"/>
       <c r="F502" s="3" t="n"/>
       <c r="G502" s="3" t="n"/>
-      <c r="H502" s="14" t="n"/>
+      <c r="H502" s="15" t="n"/>
     </row>
     <row r="503">
       <c r="A503" s="3" t="n"/>
@@ -12786,7 +12804,7 @@
       <c r="C503" s="3" t="n"/>
       <c r="F503" s="3" t="n"/>
       <c r="G503" s="3" t="n"/>
-      <c r="H503" s="14" t="n"/>
+      <c r="H503" s="15" t="n"/>
     </row>
     <row r="504">
       <c r="A504" s="3" t="n"/>
@@ -12794,7 +12812,7 @@
       <c r="C504" s="3" t="n"/>
       <c r="F504" s="3" t="n"/>
       <c r="G504" s="3" t="n"/>
-      <c r="H504" s="14" t="n"/>
+      <c r="H504" s="15" t="n"/>
     </row>
     <row r="505">
       <c r="A505" s="3" t="n"/>
@@ -12802,7 +12820,7 @@
       <c r="C505" s="3" t="n"/>
       <c r="F505" s="3" t="n"/>
       <c r="G505" s="3" t="n"/>
-      <c r="H505" s="14" t="n"/>
+      <c r="H505" s="15" t="n"/>
     </row>
     <row r="506">
       <c r="A506" s="3" t="n"/>
@@ -12810,7 +12828,7 @@
       <c r="C506" s="3" t="n"/>
       <c r="F506" s="3" t="n"/>
       <c r="G506" s="3" t="n"/>
-      <c r="H506" s="14" t="n"/>
+      <c r="H506" s="15" t="n"/>
     </row>
     <row r="507">
       <c r="A507" s="3" t="n"/>
@@ -12818,7 +12836,7 @@
       <c r="C507" s="3" t="n"/>
       <c r="F507" s="3" t="n"/>
       <c r="G507" s="3" t="n"/>
-      <c r="H507" s="14" t="n"/>
+      <c r="H507" s="15" t="n"/>
     </row>
     <row r="508">
       <c r="A508" s="3" t="n"/>
@@ -12826,7 +12844,7 @@
       <c r="C508" s="3" t="n"/>
       <c r="F508" s="3" t="n"/>
       <c r="G508" s="3" t="n"/>
-      <c r="H508" s="14" t="n"/>
+      <c r="H508" s="15" t="n"/>
     </row>
     <row r="509">
       <c r="A509" s="3" t="n"/>
@@ -12834,7 +12852,7 @@
       <c r="C509" s="3" t="n"/>
       <c r="F509" s="3" t="n"/>
       <c r="G509" s="3" t="n"/>
-      <c r="H509" s="14" t="n"/>
+      <c r="H509" s="15" t="n"/>
     </row>
     <row r="510">
       <c r="A510" s="3" t="n"/>
@@ -12842,7 +12860,7 @@
       <c r="C510" s="3" t="n"/>
       <c r="F510" s="3" t="n"/>
       <c r="G510" s="3" t="n"/>
-      <c r="H510" s="14" t="n"/>
+      <c r="H510" s="15" t="n"/>
     </row>
     <row r="511">
       <c r="A511" s="3" t="n"/>
@@ -12850,7 +12868,7 @@
       <c r="C511" s="3" t="n"/>
       <c r="F511" s="3" t="n"/>
       <c r="G511" s="3" t="n"/>
-      <c r="H511" s="14" t="n"/>
+      <c r="H511" s="15" t="n"/>
     </row>
     <row r="512">
       <c r="A512" s="3" t="n"/>
@@ -12858,7 +12876,7 @@
       <c r="C512" s="3" t="n"/>
       <c r="F512" s="3" t="n"/>
       <c r="G512" s="3" t="n"/>
-      <c r="H512" s="14" t="n"/>
+      <c r="H512" s="15" t="n"/>
     </row>
     <row r="513">
       <c r="A513" s="3" t="n"/>
@@ -12866,7 +12884,7 @@
       <c r="C513" s="3" t="n"/>
       <c r="F513" s="3" t="n"/>
       <c r="G513" s="3" t="n"/>
-      <c r="H513" s="14" t="n"/>
+      <c r="H513" s="15" t="n"/>
     </row>
     <row r="514">
       <c r="A514" s="3" t="n"/>
@@ -12874,7 +12892,7 @@
       <c r="C514" s="3" t="n"/>
       <c r="F514" s="3" t="n"/>
       <c r="G514" s="3" t="n"/>
-      <c r="H514" s="14" t="n"/>
+      <c r="H514" s="15" t="n"/>
     </row>
     <row r="515">
       <c r="A515" s="3" t="n"/>
@@ -12882,7 +12900,7 @@
       <c r="C515" s="3" t="n"/>
       <c r="F515" s="3" t="n"/>
       <c r="G515" s="3" t="n"/>
-      <c r="H515" s="14" t="n"/>
+      <c r="H515" s="15" t="n"/>
     </row>
     <row r="516">
       <c r="A516" s="3" t="n"/>
@@ -12890,7 +12908,7 @@
       <c r="C516" s="3" t="n"/>
       <c r="F516" s="3" t="n"/>
       <c r="G516" s="3" t="n"/>
-      <c r="H516" s="14" t="n"/>
+      <c r="H516" s="15" t="n"/>
     </row>
     <row r="517">
       <c r="A517" s="3" t="n"/>
@@ -12898,7 +12916,7 @@
       <c r="C517" s="3" t="n"/>
       <c r="F517" s="3" t="n"/>
       <c r="G517" s="3" t="n"/>
-      <c r="H517" s="14" t="n"/>
+      <c r="H517" s="15" t="n"/>
     </row>
     <row r="518">
       <c r="A518" s="3" t="n"/>
@@ -12906,7 +12924,7 @@
       <c r="C518" s="3" t="n"/>
       <c r="F518" s="3" t="n"/>
       <c r="G518" s="3" t="n"/>
-      <c r="H518" s="14" t="n"/>
+      <c r="H518" s="15" t="n"/>
     </row>
     <row r="519">
       <c r="A519" s="3" t="n"/>
@@ -12914,7 +12932,7 @@
       <c r="C519" s="3" t="n"/>
       <c r="F519" s="3" t="n"/>
       <c r="G519" s="3" t="n"/>
-      <c r="H519" s="14" t="n"/>
+      <c r="H519" s="15" t="n"/>
     </row>
     <row r="520">
       <c r="A520" s="3" t="n"/>
@@ -12922,7 +12940,7 @@
       <c r="C520" s="3" t="n"/>
       <c r="F520" s="3" t="n"/>
       <c r="G520" s="3" t="n"/>
-      <c r="H520" s="14" t="n"/>
+      <c r="H520" s="15" t="n"/>
     </row>
     <row r="521">
       <c r="A521" s="3" t="n"/>
@@ -12930,7 +12948,7 @@
       <c r="C521" s="3" t="n"/>
       <c r="F521" s="3" t="n"/>
       <c r="G521" s="3" t="n"/>
-      <c r="H521" s="14" t="n"/>
+      <c r="H521" s="15" t="n"/>
     </row>
     <row r="522">
       <c r="A522" s="3" t="n"/>
@@ -12938,7 +12956,7 @@
       <c r="C522" s="3" t="n"/>
       <c r="F522" s="3" t="n"/>
       <c r="G522" s="3" t="n"/>
-      <c r="H522" s="14" t="n"/>
+      <c r="H522" s="15" t="n"/>
     </row>
     <row r="523">
       <c r="A523" s="3" t="n"/>
@@ -12946,7 +12964,7 @@
       <c r="C523" s="3" t="n"/>
       <c r="F523" s="3" t="n"/>
       <c r="G523" s="3" t="n"/>
-      <c r="H523" s="14" t="n"/>
+      <c r="H523" s="15" t="n"/>
     </row>
     <row r="524">
       <c r="A524" s="3" t="n"/>
@@ -12954,7 +12972,7 @@
       <c r="C524" s="3" t="n"/>
       <c r="F524" s="3" t="n"/>
       <c r="G524" s="3" t="n"/>
-      <c r="H524" s="14" t="n"/>
+      <c r="H524" s="15" t="n"/>
     </row>
     <row r="525">
       <c r="A525" s="3" t="n"/>
@@ -12962,7 +12980,7 @@
       <c r="C525" s="3" t="n"/>
       <c r="F525" s="3" t="n"/>
       <c r="G525" s="3" t="n"/>
-      <c r="H525" s="14" t="n"/>
+      <c r="H525" s="15" t="n"/>
     </row>
     <row r="526">
       <c r="A526" s="3" t="n"/>
@@ -12970,7 +12988,7 @@
       <c r="C526" s="3" t="n"/>
       <c r="F526" s="3" t="n"/>
       <c r="G526" s="3" t="n"/>
-      <c r="H526" s="14" t="n"/>
+      <c r="H526" s="15" t="n"/>
     </row>
     <row r="527">
       <c r="A527" s="3" t="n"/>
@@ -12978,7 +12996,7 @@
       <c r="C527" s="3" t="n"/>
       <c r="F527" s="3" t="n"/>
       <c r="G527" s="3" t="n"/>
-      <c r="H527" s="14" t="n"/>
+      <c r="H527" s="15" t="n"/>
     </row>
     <row r="528">
       <c r="A528" s="3" t="n"/>
@@ -12986,7 +13004,7 @@
       <c r="C528" s="3" t="n"/>
       <c r="F528" s="3" t="n"/>
       <c r="G528" s="3" t="n"/>
-      <c r="H528" s="14" t="n"/>
+      <c r="H528" s="15" t="n"/>
     </row>
     <row r="529">
       <c r="A529" s="3" t="n"/>
@@ -12994,7 +13012,7 @@
       <c r="C529" s="3" t="n"/>
       <c r="F529" s="3" t="n"/>
       <c r="G529" s="3" t="n"/>
-      <c r="H529" s="14" t="n"/>
+      <c r="H529" s="15" t="n"/>
     </row>
     <row r="530">
       <c r="A530" s="3" t="n"/>
@@ -13002,7 +13020,7 @@
       <c r="C530" s="3" t="n"/>
       <c r="F530" s="3" t="n"/>
       <c r="G530" s="3" t="n"/>
-      <c r="H530" s="14" t="n"/>
+      <c r="H530" s="15" t="n"/>
     </row>
     <row r="531">
       <c r="A531" s="3" t="n"/>
@@ -13010,7 +13028,7 @@
       <c r="C531" s="3" t="n"/>
       <c r="F531" s="3" t="n"/>
       <c r="G531" s="3" t="n"/>
-      <c r="H531" s="14" t="n"/>
+      <c r="H531" s="15" t="n"/>
     </row>
     <row r="532">
       <c r="A532" s="3" t="n"/>
@@ -13018,7 +13036,7 @@
       <c r="C532" s="3" t="n"/>
       <c r="F532" s="3" t="n"/>
       <c r="G532" s="3" t="n"/>
-      <c r="H532" s="14" t="n"/>
+      <c r="H532" s="15" t="n"/>
     </row>
     <row r="533">
       <c r="A533" s="3" t="n"/>
@@ -13026,7 +13044,7 @@
       <c r="C533" s="3" t="n"/>
       <c r="F533" s="3" t="n"/>
       <c r="G533" s="3" t="n"/>
-      <c r="H533" s="14" t="n"/>
+      <c r="H533" s="15" t="n"/>
     </row>
     <row r="534">
       <c r="A534" s="3" t="n"/>
@@ -13034,7 +13052,7 @@
       <c r="C534" s="3" t="n"/>
       <c r="F534" s="3" t="n"/>
       <c r="G534" s="3" t="n"/>
-      <c r="H534" s="14" t="n"/>
+      <c r="H534" s="15" t="n"/>
     </row>
     <row r="535">
       <c r="A535" s="3" t="n"/>
@@ -13042,7 +13060,7 @@
       <c r="C535" s="3" t="n"/>
       <c r="F535" s="3" t="n"/>
       <c r="G535" s="3" t="n"/>
-      <c r="H535" s="14" t="n"/>
+      <c r="H535" s="15" t="n"/>
     </row>
     <row r="536">
       <c r="A536" s="3" t="n"/>
@@ -13050,7 +13068,7 @@
       <c r="C536" s="3" t="n"/>
       <c r="F536" s="3" t="n"/>
       <c r="G536" s="3" t="n"/>
-      <c r="H536" s="14" t="n"/>
+      <c r="H536" s="15" t="n"/>
     </row>
     <row r="537">
       <c r="A537" s="3" t="n"/>
@@ -13058,7 +13076,7 @@
       <c r="C537" s="3" t="n"/>
       <c r="F537" s="3" t="n"/>
       <c r="G537" s="3" t="n"/>
-      <c r="H537" s="14" t="n"/>
+      <c r="H537" s="15" t="n"/>
     </row>
     <row r="538">
       <c r="A538" s="3" t="n"/>
@@ -13066,7 +13084,7 @@
       <c r="C538" s="3" t="n"/>
       <c r="F538" s="3" t="n"/>
       <c r="G538" s="3" t="n"/>
-      <c r="H538" s="14" t="n"/>
+      <c r="H538" s="15" t="n"/>
     </row>
     <row r="539">
       <c r="A539" s="3" t="n"/>
@@ -13074,7 +13092,7 @@
       <c r="C539" s="3" t="n"/>
       <c r="F539" s="3" t="n"/>
       <c r="G539" s="3" t="n"/>
-      <c r="H539" s="14" t="n"/>
+      <c r="H539" s="15" t="n"/>
     </row>
     <row r="540">
       <c r="A540" s="3" t="n"/>
@@ -13082,7 +13100,7 @@
       <c r="C540" s="3" t="n"/>
       <c r="F540" s="3" t="n"/>
       <c r="G540" s="3" t="n"/>
-      <c r="H540" s="14" t="n"/>
+      <c r="H540" s="15" t="n"/>
     </row>
     <row r="541">
       <c r="A541" s="3" t="n"/>
@@ -13090,7 +13108,7 @@
       <c r="C541" s="3" t="n"/>
       <c r="F541" s="3" t="n"/>
       <c r="G541" s="3" t="n"/>
-      <c r="H541" s="14" t="n"/>
+      <c r="H541" s="15" t="n"/>
     </row>
     <row r="542">
       <c r="A542" s="3" t="n"/>
@@ -13098,7 +13116,7 @@
       <c r="C542" s="3" t="n"/>
       <c r="F542" s="3" t="n"/>
       <c r="G542" s="3" t="n"/>
-      <c r="H542" s="14" t="n"/>
+      <c r="H542" s="15" t="n"/>
     </row>
     <row r="543">
       <c r="A543" s="3" t="n"/>
@@ -13106,7 +13124,7 @@
       <c r="C543" s="3" t="n"/>
       <c r="F543" s="3" t="n"/>
       <c r="G543" s="3" t="n"/>
-      <c r="H543" s="14" t="n"/>
+      <c r="H543" s="15" t="n"/>
     </row>
     <row r="544">
       <c r="A544" s="3" t="n"/>
@@ -13114,7 +13132,7 @@
       <c r="C544" s="3" t="n"/>
       <c r="F544" s="3" t="n"/>
       <c r="G544" s="3" t="n"/>
-      <c r="H544" s="14" t="n"/>
+      <c r="H544" s="15" t="n"/>
     </row>
     <row r="545">
       <c r="A545" s="3" t="n"/>
@@ -13122,7 +13140,7 @@
       <c r="C545" s="3" t="n"/>
       <c r="F545" s="3" t="n"/>
       <c r="G545" s="3" t="n"/>
-      <c r="H545" s="14" t="n"/>
+      <c r="H545" s="15" t="n"/>
     </row>
     <row r="546">
       <c r="A546" s="3" t="n"/>
@@ -13130,7 +13148,7 @@
       <c r="C546" s="3" t="n"/>
       <c r="F546" s="3" t="n"/>
       <c r="G546" s="3" t="n"/>
-      <c r="H546" s="14" t="n"/>
+      <c r="H546" s="15" t="n"/>
     </row>
     <row r="547">
       <c r="A547" s="3" t="n"/>
@@ -13138,7 +13156,7 @@
       <c r="C547" s="3" t="n"/>
       <c r="F547" s="3" t="n"/>
       <c r="G547" s="3" t="n"/>
-      <c r="H547" s="14" t="n"/>
+      <c r="H547" s="15" t="n"/>
     </row>
     <row r="548">
       <c r="A548" s="3" t="n"/>
@@ -13146,7 +13164,7 @@
       <c r="C548" s="3" t="n"/>
       <c r="F548" s="3" t="n"/>
       <c r="G548" s="3" t="n"/>
-      <c r="H548" s="14" t="n"/>
+      <c r="H548" s="15" t="n"/>
     </row>
     <row r="549">
       <c r="A549" s="3" t="n"/>
@@ -13154,7 +13172,7 @@
       <c r="C549" s="3" t="n"/>
       <c r="F549" s="3" t="n"/>
       <c r="G549" s="3" t="n"/>
-      <c r="H549" s="14" t="n"/>
+      <c r="H549" s="15" t="n"/>
     </row>
     <row r="550">
       <c r="A550" s="3" t="n"/>
@@ -13162,7 +13180,7 @@
       <c r="C550" s="3" t="n"/>
       <c r="F550" s="3" t="n"/>
       <c r="G550" s="3" t="n"/>
-      <c r="H550" s="14" t="n"/>
+      <c r="H550" s="15" t="n"/>
     </row>
     <row r="551">
       <c r="A551" s="3" t="n"/>
@@ -13170,7 +13188,7 @@
       <c r="C551" s="3" t="n"/>
       <c r="F551" s="3" t="n"/>
       <c r="G551" s="3" t="n"/>
-      <c r="H551" s="14" t="n"/>
+      <c r="H551" s="15" t="n"/>
     </row>
     <row r="552">
       <c r="A552" s="3" t="n"/>
@@ -13178,7 +13196,7 @@
       <c r="C552" s="3" t="n"/>
       <c r="F552" s="3" t="n"/>
       <c r="G552" s="3" t="n"/>
-      <c r="H552" s="14" t="n"/>
+      <c r="H552" s="15" t="n"/>
     </row>
     <row r="553">
       <c r="A553" s="3" t="n"/>
@@ -13186,7 +13204,7 @@
       <c r="C553" s="3" t="n"/>
       <c r="F553" s="3" t="n"/>
       <c r="G553" s="3" t="n"/>
-      <c r="H553" s="14" t="n"/>
+      <c r="H553" s="15" t="n"/>
     </row>
     <row r="554">
       <c r="A554" s="3" t="n"/>
@@ -13194,7 +13212,7 @@
       <c r="C554" s="3" t="n"/>
       <c r="F554" s="3" t="n"/>
       <c r="G554" s="3" t="n"/>
-      <c r="H554" s="14" t="n"/>
+      <c r="H554" s="15" t="n"/>
     </row>
     <row r="555">
       <c r="A555" s="3" t="n"/>
@@ -13202,7 +13220,7 @@
       <c r="C555" s="3" t="n"/>
       <c r="F555" s="3" t="n"/>
       <c r="G555" s="3" t="n"/>
-      <c r="H555" s="14" t="n"/>
+      <c r="H555" s="15" t="n"/>
     </row>
     <row r="556">
       <c r="A556" s="3" t="n"/>
@@ -13210,7 +13228,7 @@
       <c r="C556" s="3" t="n"/>
       <c r="F556" s="3" t="n"/>
       <c r="G556" s="3" t="n"/>
-      <c r="H556" s="14" t="n"/>
+      <c r="H556" s="15" t="n"/>
     </row>
     <row r="557">
       <c r="A557" s="3" t="n"/>
@@ -13218,7 +13236,7 @@
       <c r="C557" s="3" t="n"/>
       <c r="F557" s="3" t="n"/>
       <c r="G557" s="3" t="n"/>
-      <c r="H557" s="14" t="n"/>
+      <c r="H557" s="15" t="n"/>
     </row>
     <row r="558">
       <c r="A558" s="3" t="n"/>
@@ -13226,7 +13244,7 @@
       <c r="C558" s="3" t="n"/>
       <c r="F558" s="3" t="n"/>
       <c r="G558" s="3" t="n"/>
-      <c r="H558" s="14" t="n"/>
+      <c r="H558" s="15" t="n"/>
     </row>
     <row r="559">
       <c r="A559" s="3" t="n"/>
@@ -13234,7 +13252,7 @@
       <c r="C559" s="3" t="n"/>
       <c r="F559" s="3" t="n"/>
       <c r="G559" s="3" t="n"/>
-      <c r="H559" s="14" t="n"/>
+      <c r="H559" s="15" t="n"/>
     </row>
     <row r="560">
       <c r="A560" s="3" t="n"/>
@@ -13242,7 +13260,7 @@
       <c r="C560" s="3" t="n"/>
       <c r="F560" s="3" t="n"/>
       <c r="G560" s="3" t="n"/>
-      <c r="H560" s="14" t="n"/>
+      <c r="H560" s="15" t="n"/>
     </row>
     <row r="561">
       <c r="A561" s="3" t="n"/>
@@ -13250,7 +13268,7 @@
       <c r="C561" s="3" t="n"/>
       <c r="F561" s="3" t="n"/>
       <c r="G561" s="3" t="n"/>
-      <c r="H561" s="14" t="n"/>
+      <c r="H561" s="15" t="n"/>
     </row>
     <row r="562">
       <c r="A562" s="3" t="n"/>
@@ -13258,7 +13276,7 @@
       <c r="C562" s="3" t="n"/>
       <c r="F562" s="3" t="n"/>
       <c r="G562" s="3" t="n"/>
-      <c r="H562" s="14" t="n"/>
+      <c r="H562" s="15" t="n"/>
     </row>
     <row r="563">
       <c r="A563" s="3" t="n"/>
@@ -13266,7 +13284,7 @@
       <c r="C563" s="3" t="n"/>
       <c r="F563" s="3" t="n"/>
       <c r="G563" s="3" t="n"/>
-      <c r="H563" s="14" t="n"/>
+      <c r="H563" s="15" t="n"/>
     </row>
     <row r="564">
       <c r="A564" s="3" t="n"/>
@@ -13274,7 +13292,7 @@
       <c r="C564" s="3" t="n"/>
       <c r="F564" s="3" t="n"/>
       <c r="G564" s="3" t="n"/>
-      <c r="H564" s="14" t="n"/>
+      <c r="H564" s="15" t="n"/>
     </row>
     <row r="565">
       <c r="A565" s="3" t="n"/>
@@ -13282,7 +13300,7 @@
       <c r="C565" s="3" t="n"/>
       <c r="F565" s="3" t="n"/>
       <c r="G565" s="3" t="n"/>
-      <c r="H565" s="14" t="n"/>
+      <c r="H565" s="15" t="n"/>
     </row>
     <row r="566">
       <c r="A566" s="3" t="n"/>
@@ -13290,7 +13308,7 @@
       <c r="C566" s="3" t="n"/>
       <c r="F566" s="3" t="n"/>
       <c r="G566" s="3" t="n"/>
-      <c r="H566" s="14" t="n"/>
+      <c r="H566" s="15" t="n"/>
     </row>
     <row r="567">
       <c r="A567" s="3" t="n"/>
@@ -13298,7 +13316,7 @@
       <c r="C567" s="3" t="n"/>
       <c r="F567" s="3" t="n"/>
       <c r="G567" s="3" t="n"/>
-      <c r="H567" s="14" t="n"/>
+      <c r="H567" s="15" t="n"/>
     </row>
     <row r="568">
       <c r="A568" s="3" t="n"/>
@@ -13306,7 +13324,7 @@
       <c r="C568" s="3" t="n"/>
       <c r="F568" s="3" t="n"/>
       <c r="G568" s="3" t="n"/>
-      <c r="H568" s="14" t="n"/>
+      <c r="H568" s="15" t="n"/>
     </row>
     <row r="569">
       <c r="A569" s="3" t="n"/>
@@ -13314,7 +13332,7 @@
       <c r="C569" s="3" t="n"/>
       <c r="F569" s="3" t="n"/>
       <c r="G569" s="3" t="n"/>
-      <c r="H569" s="14" t="n"/>
+      <c r="H569" s="15" t="n"/>
     </row>
     <row r="570">
       <c r="A570" s="3" t="n"/>
@@ -13322,7 +13340,7 @@
       <c r="C570" s="3" t="n"/>
       <c r="F570" s="3" t="n"/>
       <c r="G570" s="3" t="n"/>
-      <c r="H570" s="14" t="n"/>
+      <c r="H570" s="15" t="n"/>
     </row>
     <row r="571">
       <c r="A571" s="3" t="n"/>
@@ -13330,7 +13348,7 @@
       <c r="C571" s="3" t="n"/>
       <c r="F571" s="3" t="n"/>
       <c r="G571" s="3" t="n"/>
-      <c r="H571" s="14" t="n"/>
+      <c r="H571" s="15" t="n"/>
     </row>
     <row r="572">
       <c r="A572" s="3" t="n"/>
@@ -13338,7 +13356,7 @@
       <c r="C572" s="3" t="n"/>
       <c r="F572" s="3" t="n"/>
       <c r="G572" s="3" t="n"/>
-      <c r="H572" s="14" t="n"/>
+      <c r="H572" s="15" t="n"/>
     </row>
     <row r="573">
       <c r="A573" s="3" t="n"/>
@@ -13346,7 +13364,7 @@
       <c r="C573" s="3" t="n"/>
       <c r="F573" s="3" t="n"/>
       <c r="G573" s="3" t="n"/>
-      <c r="H573" s="14" t="n"/>
+      <c r="H573" s="15" t="n"/>
     </row>
     <row r="574">
       <c r="A574" s="3" t="n"/>
@@ -13354,7 +13372,7 @@
       <c r="C574" s="3" t="n"/>
       <c r="F574" s="3" t="n"/>
       <c r="G574" s="3" t="n"/>
-      <c r="H574" s="14" t="n"/>
+      <c r="H574" s="15" t="n"/>
     </row>
     <row r="575">
       <c r="A575" s="3" t="n"/>
@@ -13362,7 +13380,7 @@
       <c r="C575" s="3" t="n"/>
       <c r="F575" s="3" t="n"/>
       <c r="G575" s="3" t="n"/>
-      <c r="H575" s="14" t="n"/>
+      <c r="H575" s="15" t="n"/>
     </row>
     <row r="576">
       <c r="A576" s="3" t="n"/>
@@ -13370,7 +13388,7 @@
       <c r="C576" s="3" t="n"/>
       <c r="F576" s="3" t="n"/>
       <c r="G576" s="3" t="n"/>
-      <c r="H576" s="14" t="n"/>
+      <c r="H576" s="15" t="n"/>
     </row>
     <row r="577">
       <c r="A577" s="3" t="n"/>
@@ -13378,7 +13396,7 @@
       <c r="C577" s="3" t="n"/>
       <c r="F577" s="3" t="n"/>
       <c r="G577" s="3" t="n"/>
-      <c r="H577" s="14" t="n"/>
+      <c r="H577" s="15" t="n"/>
     </row>
     <row r="578">
       <c r="A578" s="3" t="n"/>
@@ -13386,7 +13404,7 @@
       <c r="C578" s="3" t="n"/>
       <c r="F578" s="3" t="n"/>
       <c r="G578" s="3" t="n"/>
-      <c r="H578" s="14" t="n"/>
+      <c r="H578" s="15" t="n"/>
     </row>
     <row r="579">
       <c r="A579" s="3" t="n"/>
@@ -13394,7 +13412,7 @@
       <c r="C579" s="3" t="n"/>
       <c r="F579" s="3" t="n"/>
       <c r="G579" s="3" t="n"/>
-      <c r="H579" s="14" t="n"/>
+      <c r="H579" s="15" t="n"/>
     </row>
     <row r="580">
       <c r="A580" s="3" t="n"/>
@@ -13402,7 +13420,7 @@
       <c r="C580" s="3" t="n"/>
       <c r="F580" s="3" t="n"/>
       <c r="G580" s="3" t="n"/>
-      <c r="H580" s="14" t="n"/>
+      <c r="H580" s="15" t="n"/>
     </row>
     <row r="581">
       <c r="A581" s="3" t="n"/>
@@ -13410,7 +13428,7 @@
       <c r="C581" s="3" t="n"/>
       <c r="F581" s="3" t="n"/>
       <c r="G581" s="3" t="n"/>
-      <c r="H581" s="14" t="n"/>
+      <c r="H581" s="15" t="n"/>
     </row>
     <row r="582">
       <c r="A582" s="3" t="n"/>
@@ -13418,7 +13436,7 @@
       <c r="C582" s="3" t="n"/>
       <c r="F582" s="3" t="n"/>
       <c r="G582" s="3" t="n"/>
-      <c r="H582" s="14" t="n"/>
+      <c r="H582" s="15" t="n"/>
     </row>
     <row r="583">
       <c r="A583" s="3" t="n"/>
@@ -13426,7 +13444,7 @@
       <c r="C583" s="3" t="n"/>
       <c r="F583" s="3" t="n"/>
       <c r="G583" s="3" t="n"/>
-      <c r="H583" s="14" t="n"/>
+      <c r="H583" s="15" t="n"/>
     </row>
     <row r="584">
       <c r="A584" s="3" t="n"/>
@@ -13434,7 +13452,7 @@
       <c r="C584" s="3" t="n"/>
       <c r="F584" s="3" t="n"/>
       <c r="G584" s="3" t="n"/>
-      <c r="H584" s="14" t="n"/>
+      <c r="H584" s="15" t="n"/>
     </row>
     <row r="585">
       <c r="A585" s="3" t="n"/>
@@ -13442,7 +13460,7 @@
       <c r="C585" s="3" t="n"/>
       <c r="F585" s="3" t="n"/>
       <c r="G585" s="3" t="n"/>
-      <c r="H585" s="14" t="n"/>
+      <c r="H585" s="15" t="n"/>
     </row>
     <row r="586">
       <c r="A586" s="3" t="n"/>
@@ -13450,7 +13468,7 @@
       <c r="C586" s="3" t="n"/>
       <c r="F586" s="3" t="n"/>
       <c r="G586" s="3" t="n"/>
-      <c r="H586" s="14" t="n"/>
+      <c r="H586" s="15" t="n"/>
     </row>
     <row r="587">
       <c r="A587" s="3" t="n"/>
@@ -13458,7 +13476,7 @@
       <c r="C587" s="3" t="n"/>
       <c r="F587" s="3" t="n"/>
       <c r="G587" s="3" t="n"/>
-      <c r="H587" s="14" t="n"/>
+      <c r="H587" s="15" t="n"/>
     </row>
     <row r="588">
       <c r="A588" s="3" t="n"/>
@@ -13466,7 +13484,7 @@
       <c r="C588" s="3" t="n"/>
       <c r="F588" s="3" t="n"/>
       <c r="G588" s="3" t="n"/>
-      <c r="H588" s="14" t="n"/>
+      <c r="H588" s="15" t="n"/>
     </row>
     <row r="589">
       <c r="A589" s="3" t="n"/>
@@ -13474,7 +13492,7 @@
       <c r="C589" s="3" t="n"/>
       <c r="F589" s="3" t="n"/>
       <c r="G589" s="3" t="n"/>
-      <c r="H589" s="14" t="n"/>
+      <c r="H589" s="15" t="n"/>
     </row>
     <row r="590">
       <c r="A590" s="3" t="n"/>
@@ -13482,7 +13500,7 @@
       <c r="C590" s="3" t="n"/>
       <c r="F590" s="3" t="n"/>
       <c r="G590" s="3" t="n"/>
-      <c r="H590" s="14" t="n"/>
+      <c r="H590" s="15" t="n"/>
     </row>
     <row r="591">
       <c r="A591" s="3" t="n"/>
@@ -13490,7 +13508,7 @@
       <c r="C591" s="3" t="n"/>
       <c r="F591" s="3" t="n"/>
       <c r="G591" s="3" t="n"/>
-      <c r="H591" s="14" t="n"/>
+      <c r="H591" s="15" t="n"/>
     </row>
     <row r="592">
       <c r="A592" s="3" t="n"/>
@@ -13498,7 +13516,7 @@
       <c r="C592" s="3" t="n"/>
       <c r="F592" s="3" t="n"/>
       <c r="G592" s="3" t="n"/>
-      <c r="H592" s="14" t="n"/>
+      <c r="H592" s="15" t="n"/>
     </row>
     <row r="593">
       <c r="A593" s="3" t="n"/>
@@ -13506,7 +13524,7 @@
       <c r="C593" s="3" t="n"/>
       <c r="F593" s="3" t="n"/>
       <c r="G593" s="3" t="n"/>
-      <c r="H593" s="14" t="n"/>
+      <c r="H593" s="15" t="n"/>
     </row>
     <row r="594">
       <c r="A594" s="3" t="n"/>
@@ -13514,7 +13532,7 @@
       <c r="C594" s="3" t="n"/>
       <c r="F594" s="3" t="n"/>
       <c r="G594" s="3" t="n"/>
-      <c r="H594" s="14" t="n"/>
+      <c r="H594" s="15" t="n"/>
     </row>
     <row r="595">
       <c r="A595" s="3" t="n"/>
@@ -13522,7 +13540,7 @@
       <c r="C595" s="3" t="n"/>
       <c r="F595" s="3" t="n"/>
       <c r="G595" s="3" t="n"/>
-      <c r="H595" s="14" t="n"/>
+      <c r="H595" s="15" t="n"/>
     </row>
     <row r="596">
       <c r="A596" s="3" t="n"/>
@@ -13530,7 +13548,7 @@
       <c r="C596" s="3" t="n"/>
       <c r="F596" s="3" t="n"/>
       <c r="G596" s="3" t="n"/>
-      <c r="H596" s="14" t="n"/>
+      <c r="H596" s="15" t="n"/>
     </row>
     <row r="597">
       <c r="A597" s="3" t="n"/>
@@ -13538,7 +13556,7 @@
       <c r="C597" s="3" t="n"/>
       <c r="F597" s="3" t="n"/>
       <c r="G597" s="3" t="n"/>
-      <c r="H597" s="14" t="n"/>
+      <c r="H597" s="15" t="n"/>
     </row>
     <row r="598">
       <c r="A598" s="3" t="n"/>
@@ -13546,7 +13564,7 @@
       <c r="C598" s="3" t="n"/>
       <c r="F598" s="3" t="n"/>
       <c r="G598" s="3" t="n"/>
-      <c r="H598" s="14" t="n"/>
+      <c r="H598" s="15" t="n"/>
     </row>
     <row r="599">
       <c r="A599" s="3" t="n"/>
@@ -13554,7 +13572,7 @@
       <c r="C599" s="3" t="n"/>
       <c r="F599" s="3" t="n"/>
       <c r="G599" s="3" t="n"/>
-      <c r="H599" s="14" t="n"/>
+      <c r="H599" s="15" t="n"/>
     </row>
     <row r="600">
       <c r="A600" s="3" t="n"/>
@@ -13562,7 +13580,7 @@
       <c r="C600" s="3" t="n"/>
       <c r="F600" s="3" t="n"/>
       <c r="G600" s="3" t="n"/>
-      <c r="H600" s="14" t="n"/>
+      <c r="H600" s="15" t="n"/>
     </row>
     <row r="601">
       <c r="A601" s="3" t="n"/>
@@ -13570,7 +13588,7 @@
       <c r="C601" s="3" t="n"/>
       <c r="F601" s="3" t="n"/>
       <c r="G601" s="3" t="n"/>
-      <c r="H601" s="14" t="n"/>
+      <c r="H601" s="15" t="n"/>
     </row>
     <row r="602">
       <c r="A602" s="3" t="n"/>
@@ -13578,7 +13596,7 @@
       <c r="C602" s="3" t="n"/>
       <c r="F602" s="3" t="n"/>
       <c r="G602" s="3" t="n"/>
-      <c r="H602" s="14" t="n"/>
+      <c r="H602" s="15" t="n"/>
     </row>
     <row r="603">
       <c r="A603" s="3" t="n"/>
@@ -13586,7 +13604,7 @@
       <c r="C603" s="3" t="n"/>
       <c r="F603" s="3" t="n"/>
       <c r="G603" s="3" t="n"/>
-      <c r="H603" s="14" t="n"/>
+      <c r="H603" s="15" t="n"/>
     </row>
     <row r="604">
       <c r="A604" s="3" t="n"/>
@@ -13594,7 +13612,7 @@
       <c r="C604" s="3" t="n"/>
       <c r="F604" s="3" t="n"/>
       <c r="G604" s="3" t="n"/>
-      <c r="H604" s="14" t="n"/>
+      <c r="H604" s="15" t="n"/>
     </row>
     <row r="605">
       <c r="A605" s="3" t="n"/>
@@ -13602,7 +13620,7 @@
       <c r="C605" s="3" t="n"/>
       <c r="F605" s="3" t="n"/>
       <c r="G605" s="3" t="n"/>
-      <c r="H605" s="14" t="n"/>
+      <c r="H605" s="15" t="n"/>
     </row>
     <row r="606">
       <c r="A606" s="3" t="n"/>
@@ -13610,7 +13628,7 @@
       <c r="C606" s="3" t="n"/>
       <c r="F606" s="3" t="n"/>
       <c r="G606" s="3" t="n"/>
-      <c r="H606" s="14" t="n"/>
+      <c r="H606" s="15" t="n"/>
     </row>
     <row r="607">
       <c r="A607" s="3" t="n"/>
@@ -13618,7 +13636,7 @@
       <c r="C607" s="3" t="n"/>
       <c r="F607" s="3" t="n"/>
       <c r="G607" s="3" t="n"/>
-      <c r="H607" s="14" t="n"/>
+      <c r="H607" s="15" t="n"/>
     </row>
     <row r="608">
       <c r="A608" s="3" t="n"/>
@@ -13626,7 +13644,7 @@
       <c r="C608" s="3" t="n"/>
       <c r="F608" s="3" t="n"/>
       <c r="G608" s="3" t="n"/>
-      <c r="H608" s="14" t="n"/>
+      <c r="H608" s="15" t="n"/>
     </row>
     <row r="609">
       <c r="A609" s="3" t="n"/>
@@ -13634,7 +13652,7 @@
       <c r="C609" s="3" t="n"/>
       <c r="F609" s="3" t="n"/>
       <c r="G609" s="3" t="n"/>
-      <c r="H609" s="14" t="n"/>
+      <c r="H609" s="15" t="n"/>
     </row>
     <row r="610">
       <c r="A610" s="3" t="n"/>
@@ -13642,7 +13660,7 @@
       <c r="C610" s="3" t="n"/>
       <c r="F610" s="3" t="n"/>
       <c r="G610" s="3" t="n"/>
-      <c r="H610" s="14" t="n"/>
+      <c r="H610" s="15" t="n"/>
     </row>
     <row r="611">
       <c r="A611" s="3" t="n"/>
@@ -13650,7 +13668,7 @@
       <c r="C611" s="3" t="n"/>
       <c r="F611" s="3" t="n"/>
       <c r="G611" s="3" t="n"/>
-      <c r="H611" s="14" t="n"/>
+      <c r="H611" s="15" t="n"/>
     </row>
     <row r="612">
       <c r="A612" s="3" t="n"/>
@@ -13658,7 +13676,7 @@
       <c r="C612" s="3" t="n"/>
       <c r="F612" s="3" t="n"/>
       <c r="G612" s="3" t="n"/>
-      <c r="H612" s="14" t="n"/>
+      <c r="H612" s="15" t="n"/>
     </row>
     <row r="613">
       <c r="A613" s="3" t="n"/>
@@ -13666,7 +13684,7 @@
       <c r="C613" s="3" t="n"/>
       <c r="F613" s="3" t="n"/>
       <c r="G613" s="3" t="n"/>
-      <c r="H613" s="14" t="n"/>
+      <c r="H613" s="15" t="n"/>
     </row>
     <row r="614">
       <c r="A614" s="3" t="n"/>
@@ -13674,7 +13692,7 @@
       <c r="C614" s="3" t="n"/>
       <c r="F614" s="3" t="n"/>
       <c r="G614" s="3" t="n"/>
-      <c r="H614" s="14" t="n"/>
+      <c r="H614" s="15" t="n"/>
     </row>
     <row r="615">
       <c r="A615" s="3" t="n"/>
@@ -13682,7 +13700,7 @@
       <c r="C615" s="3" t="n"/>
       <c r="F615" s="3" t="n"/>
       <c r="G615" s="3" t="n"/>
-      <c r="H615" s="14" t="n"/>
+      <c r="H615" s="15" t="n"/>
     </row>
     <row r="616">
       <c r="A616" s="3" t="n"/>
@@ -13690,7 +13708,7 @@
       <c r="C616" s="3" t="n"/>
       <c r="F616" s="3" t="n"/>
       <c r="G616" s="3" t="n"/>
-      <c r="H616" s="14" t="n"/>
+      <c r="H616" s="15" t="n"/>
     </row>
     <row r="617">
       <c r="A617" s="3" t="n"/>
@@ -13698,7 +13716,7 @@
       <c r="C617" s="3" t="n"/>
       <c r="F617" s="3" t="n"/>
       <c r="G617" s="3" t="n"/>
-      <c r="H617" s="14" t="n"/>
+      <c r="H617" s="15" t="n"/>
     </row>
     <row r="618">
       <c r="A618" s="3" t="n"/>
@@ -13706,7 +13724,7 @@
       <c r="C618" s="3" t="n"/>
       <c r="F618" s="3" t="n"/>
       <c r="G618" s="3" t="n"/>
-      <c r="H618" s="14" t="n"/>
+      <c r="H618" s="15" t="n"/>
     </row>
     <row r="619">
       <c r="A619" s="3" t="n"/>
@@ -13714,7 +13732,7 @@
       <c r="C619" s="3" t="n"/>
       <c r="F619" s="3" t="n"/>
       <c r="G619" s="3" t="n"/>
-      <c r="H619" s="14" t="n"/>
+      <c r="H619" s="15" t="n"/>
     </row>
     <row r="620">
       <c r="A620" s="3" t="n"/>
@@ -13722,7 +13740,7 @@
       <c r="C620" s="3" t="n"/>
       <c r="F620" s="3" t="n"/>
       <c r="G620" s="3" t="n"/>
-      <c r="H620" s="14" t="n"/>
+      <c r="H620" s="15" t="n"/>
     </row>
     <row r="621">
       <c r="A621" s="3" t="n"/>
@@ -13730,7 +13748,7 @@
       <c r="C621" s="3" t="n"/>
       <c r="F621" s="3" t="n"/>
       <c r="G621" s="3" t="n"/>
-      <c r="H621" s="14" t="n"/>
+      <c r="H621" s="15" t="n"/>
     </row>
     <row r="622">
       <c r="A622" s="3" t="n"/>
@@ -13738,7 +13756,7 @@
       <c r="C622" s="3" t="n"/>
       <c r="F622" s="3" t="n"/>
       <c r="G622" s="3" t="n"/>
-      <c r="H622" s="14" t="n"/>
+      <c r="H622" s="15" t="n"/>
     </row>
     <row r="623">
       <c r="A623" s="3" t="n"/>
@@ -13746,7 +13764,7 @@
       <c r="C623" s="3" t="n"/>
       <c r="F623" s="3" t="n"/>
       <c r="G623" s="3" t="n"/>
-      <c r="H623" s="14" t="n"/>
+      <c r="H623" s="15" t="n"/>
     </row>
     <row r="624">
       <c r="A624" s="3" t="n"/>
@@ -13754,7 +13772,7 @@
       <c r="C624" s="3" t="n"/>
       <c r="F624" s="3" t="n"/>
       <c r="G624" s="3" t="n"/>
-      <c r="H624" s="14" t="n"/>
+      <c r="H624" s="15" t="n"/>
     </row>
     <row r="625">
       <c r="A625" s="3" t="n"/>
@@ -13762,7 +13780,7 @@
       <c r="C625" s="3" t="n"/>
       <c r="F625" s="3" t="n"/>
       <c r="G625" s="3" t="n"/>
-      <c r="H625" s="14" t="n"/>
+      <c r="H625" s="15" t="n"/>
     </row>
     <row r="626">
       <c r="A626" s="3" t="n"/>
@@ -13770,7 +13788,7 @@
       <c r="C626" s="3" t="n"/>
       <c r="F626" s="3" t="n"/>
       <c r="G626" s="3" t="n"/>
-      <c r="H626" s="14" t="n"/>
+      <c r="H626" s="15" t="n"/>
     </row>
     <row r="627">
       <c r="A627" s="3" t="n"/>
@@ -13778,7 +13796,7 @@
       <c r="C627" s="3" t="n"/>
       <c r="F627" s="3" t="n"/>
       <c r="G627" s="3" t="n"/>
-      <c r="H627" s="14" t="n"/>
+      <c r="H627" s="15" t="n"/>
     </row>
     <row r="628">
       <c r="A628" s="3" t="n"/>
@@ -13786,7 +13804,7 @@
       <c r="C628" s="3" t="n"/>
       <c r="F628" s="3" t="n"/>
       <c r="G628" s="3" t="n"/>
-      <c r="H628" s="14" t="n"/>
+      <c r="H628" s="15" t="n"/>
     </row>
     <row r="629">
       <c r="A629" s="3" t="n"/>
@@ -13794,7 +13812,7 @@
       <c r="C629" s="3" t="n"/>
       <c r="F629" s="3" t="n"/>
       <c r="G629" s="3" t="n"/>
-      <c r="H629" s="14" t="n"/>
+      <c r="H629" s="15" t="n"/>
     </row>
     <row r="630">
       <c r="A630" s="3" t="n"/>
@@ -13802,7 +13820,7 @@
       <c r="C630" s="3" t="n"/>
       <c r="F630" s="3" t="n"/>
       <c r="G630" s="3" t="n"/>
-      <c r="H630" s="14" t="n"/>
+      <c r="H630" s="15" t="n"/>
     </row>
     <row r="631">
       <c r="A631" s="3" t="n"/>
@@ -13810,7 +13828,7 @@
       <c r="C631" s="3" t="n"/>
       <c r="F631" s="3" t="n"/>
       <c r="G631" s="3" t="n"/>
-      <c r="H631" s="14" t="n"/>
+      <c r="H631" s="15" t="n"/>
     </row>
     <row r="632">
       <c r="A632" s="3" t="n"/>
@@ -13818,7 +13836,7 @@
       <c r="C632" s="3" t="n"/>
       <c r="F632" s="3" t="n"/>
       <c r="G632" s="3" t="n"/>
-      <c r="H632" s="14" t="n"/>
+      <c r="H632" s="15" t="n"/>
     </row>
     <row r="633">
       <c r="A633" s="3" t="n"/>
@@ -13826,7 +13844,7 @@
       <c r="C633" s="3" t="n"/>
       <c r="F633" s="3" t="n"/>
       <c r="G633" s="3" t="n"/>
-      <c r="H633" s="14" t="n"/>
+      <c r="H633" s="15" t="n"/>
     </row>
     <row r="634">
       <c r="A634" s="3" t="n"/>
@@ -13834,7 +13852,7 @@
       <c r="C634" s="3" t="n"/>
       <c r="F634" s="3" t="n"/>
       <c r="G634" s="3" t="n"/>
-      <c r="H634" s="14" t="n"/>
+      <c r="H634" s="15" t="n"/>
     </row>
     <row r="635">
       <c r="A635" s="3" t="n"/>
@@ -13842,7 +13860,7 @@
       <c r="C635" s="3" t="n"/>
       <c r="F635" s="3" t="n"/>
       <c r="G635" s="3" t="n"/>
-      <c r="H635" s="14" t="n"/>
+      <c r="H635" s="15" t="n"/>
     </row>
     <row r="636">
       <c r="A636" s="3" t="n"/>
@@ -13850,7 +13868,7 @@
       <c r="C636" s="3" t="n"/>
       <c r="F636" s="3" t="n"/>
       <c r="G636" s="3" t="n"/>
-      <c r="H636" s="14" t="n"/>
+      <c r="H636" s="15" t="n"/>
     </row>
     <row r="637">
       <c r="A637" s="3" t="n"/>
@@ -13858,7 +13876,7 @@
       <c r="C637" s="3" t="n"/>
       <c r="F637" s="3" t="n"/>
       <c r="G637" s="3" t="n"/>
-      <c r="H637" s="14" t="n"/>
+      <c r="H637" s="15" t="n"/>
     </row>
     <row r="638">
       <c r="A638" s="3" t="n"/>
@@ -13866,7 +13884,7 @@
       <c r="C638" s="3" t="n"/>
       <c r="F638" s="3" t="n"/>
       <c r="G638" s="3" t="n"/>
-      <c r="H638" s="14" t="n"/>
+      <c r="H638" s="15" t="n"/>
     </row>
     <row r="639">
       <c r="A639" s="3" t="n"/>
@@ -13874,7 +13892,7 @@
       <c r="C639" s="3" t="n"/>
       <c r="F639" s="3" t="n"/>
       <c r="G639" s="3" t="n"/>
-      <c r="H639" s="14" t="n"/>
+      <c r="H639" s="15" t="n"/>
     </row>
     <row r="640">
       <c r="A640" s="3" t="n"/>
@@ -13882,7 +13900,7 @@
       <c r="C640" s="3" t="n"/>
       <c r="F640" s="3" t="n"/>
       <c r="G640" s="3" t="n"/>
-      <c r="H640" s="14" t="n"/>
+      <c r="H640" s="15" t="n"/>
     </row>
     <row r="641">
       <c r="A641" s="3" t="n"/>
@@ -13890,7 +13908,7 @@
       <c r="C641" s="3" t="n"/>
       <c r="F641" s="3" t="n"/>
       <c r="G641" s="3" t="n"/>
-      <c r="H641" s="14" t="n"/>
+      <c r="H641" s="15" t="n"/>
     </row>
     <row r="642">
       <c r="A642" s="3" t="n"/>
@@ -13898,7 +13916,7 @@
       <c r="C642" s="3" t="n"/>
       <c r="F642" s="3" t="n"/>
       <c r="G642" s="3" t="n"/>
-      <c r="H642" s="14" t="n"/>
+      <c r="H642" s="15" t="n"/>
     </row>
     <row r="643">
       <c r="A643" s="3" t="n"/>
@@ -13906,7 +13924,7 @@
       <c r="C643" s="3" t="n"/>
       <c r="F643" s="3" t="n"/>
       <c r="G643" s="3" t="n"/>
-      <c r="H643" s="14" t="n"/>
+      <c r="H643" s="15" t="n"/>
     </row>
     <row r="644">
       <c r="A644" s="3" t="n"/>
@@ -13914,7 +13932,7 @@
       <c r="C644" s="3" t="n"/>
       <c r="F644" s="3" t="n"/>
       <c r="G644" s="3" t="n"/>
-      <c r="H644" s="14" t="n"/>
+      <c r="H644" s="15" t="n"/>
     </row>
     <row r="645">
       <c r="A645" s="3" t="n"/>
@@ -13922,7 +13940,7 @@
       <c r="C645" s="3" t="n"/>
       <c r="F645" s="3" t="n"/>
       <c r="G645" s="3" t="n"/>
-      <c r="H645" s="14" t="n"/>
+      <c r="H645" s="15" t="n"/>
     </row>
     <row r="646">
       <c r="A646" s="3" t="n"/>
@@ -13930,7 +13948,7 @@
       <c r="C646" s="3" t="n"/>
       <c r="F646" s="3" t="n"/>
       <c r="G646" s="3" t="n"/>
-      <c r="H646" s="14" t="n"/>
+      <c r="H646" s="15" t="n"/>
     </row>
     <row r="647">
       <c r="A647" s="3" t="n"/>
@@ -13938,7 +13956,7 @@
       <c r="C647" s="3" t="n"/>
       <c r="F647" s="3" t="n"/>
       <c r="G647" s="3" t="n"/>
-      <c r="H647" s="14" t="n"/>
+      <c r="H647" s="15" t="n"/>
     </row>
     <row r="648">
       <c r="A648" s="3" t="n"/>
@@ -13946,7 +13964,7 @@
       <c r="C648" s="3" t="n"/>
       <c r="F648" s="3" t="n"/>
       <c r="G648" s="3" t="n"/>
-      <c r="H648" s="14" t="n"/>
+      <c r="H648" s="15" t="n"/>
     </row>
     <row r="649">
       <c r="A649" s="3" t="n"/>
@@ -13954,7 +13972,7 @@
       <c r="C649" s="3" t="n"/>
       <c r="F649" s="3" t="n"/>
       <c r="G649" s="3" t="n"/>
-      <c r="H649" s="14" t="n"/>
+      <c r="H649" s="15" t="n"/>
     </row>
     <row r="650">
       <c r="A650" s="3" t="n"/>
@@ -13962,7 +13980,7 @@
       <c r="C650" s="3" t="n"/>
       <c r="F650" s="3" t="n"/>
       <c r="G650" s="3" t="n"/>
-      <c r="H650" s="14" t="n"/>
+      <c r="H650" s="15" t="n"/>
     </row>
     <row r="651">
       <c r="A651" s="3" t="n"/>
@@ -13970,7 +13988,7 @@
       <c r="C651" s="3" t="n"/>
       <c r="F651" s="3" t="n"/>
       <c r="G651" s="3" t="n"/>
-      <c r="H651" s="14" t="n"/>
+      <c r="H651" s="15" t="n"/>
     </row>
     <row r="652">
       <c r="A652" s="3" t="n"/>
@@ -13978,7 +13996,7 @@
       <c r="C652" s="3" t="n"/>
       <c r="F652" s="3" t="n"/>
       <c r="G652" s="3" t="n"/>
-      <c r="H652" s="14" t="n"/>
+      <c r="H652" s="15" t="n"/>
     </row>
     <row r="653">
       <c r="A653" s="3" t="n"/>
@@ -13986,7 +14004,7 @@
       <c r="C653" s="3" t="n"/>
       <c r="F653" s="3" t="n"/>
       <c r="G653" s="3" t="n"/>
-      <c r="H653" s="14" t="n"/>
+      <c r="H653" s="15" t="n"/>
     </row>
     <row r="654">
       <c r="A654" s="3" t="n"/>
@@ -13994,7 +14012,7 @@
       <c r="C654" s="3" t="n"/>
       <c r="F654" s="3" t="n"/>
       <c r="G654" s="3" t="n"/>
-      <c r="H654" s="14" t="n"/>
+      <c r="H654" s="15" t="n"/>
     </row>
     <row r="655">
       <c r="A655" s="3" t="n"/>
@@ -14002,7 +14020,7 @@
       <c r="C655" s="3" t="n"/>
       <c r="F655" s="3" t="n"/>
       <c r="G655" s="3" t="n"/>
-      <c r="H655" s="14" t="n"/>
+      <c r="H655" s="15" t="n"/>
     </row>
     <row r="656">
       <c r="A656" s="3" t="n"/>
@@ -14010,7 +14028,7 @@
       <c r="C656" s="3" t="n"/>
       <c r="F656" s="3" t="n"/>
       <c r="G656" s="3" t="n"/>
-      <c r="H656" s="14" t="n"/>
+      <c r="H656" s="15" t="n"/>
     </row>
     <row r="657">
       <c r="A657" s="3" t="n"/>
@@ -14018,7 +14036,7 @@
       <c r="C657" s="3" t="n"/>
       <c r="F657" s="3" t="n"/>
       <c r="G657" s="3" t="n"/>
-      <c r="H657" s="14" t="n"/>
+      <c r="H657" s="15" t="n"/>
     </row>
     <row r="658">
       <c r="A658" s="3" t="n"/>
@@ -14026,7 +14044,7 @@
       <c r="C658" s="3" t="n"/>
       <c r="F658" s="3" t="n"/>
       <c r="G658" s="3" t="n"/>
-      <c r="H658" s="14" t="n"/>
+      <c r="H658" s="15" t="n"/>
     </row>
     <row r="659">
       <c r="A659" s="3" t="n"/>
@@ -14034,7 +14052,7 @@
       <c r="C659" s="3" t="n"/>
       <c r="F659" s="3" t="n"/>
       <c r="G659" s="3" t="n"/>
-      <c r="H659" s="14" t="n"/>
+      <c r="H659" s="15" t="n"/>
     </row>
     <row r="660">
       <c r="A660" s="3" t="n"/>
@@ -14042,7 +14060,7 @@
       <c r="C660" s="3" t="n"/>
       <c r="F660" s="3" t="n"/>
       <c r="G660" s="3" t="n"/>
-      <c r="H660" s="14" t="n"/>
+      <c r="H660" s="15" t="n"/>
     </row>
     <row r="661">
       <c r="A661" s="3" t="n"/>
@@ -14050,7 +14068,7 @@
       <c r="C661" s="3" t="n"/>
       <c r="F661" s="3" t="n"/>
       <c r="G661" s="3" t="n"/>
-      <c r="H661" s="14" t="n"/>
+      <c r="H661" s="15" t="n"/>
     </row>
     <row r="662">
       <c r="A662" s="3" t="n"/>
@@ -14058,7 +14076,7 @@
       <c r="C662" s="3" t="n"/>
       <c r="F662" s="3" t="n"/>
       <c r="G662" s="3" t="n"/>
-      <c r="H662" s="14" t="n"/>
+      <c r="H662" s="15" t="n"/>
     </row>
     <row r="663">
       <c r="A663" s="3" t="n"/>
@@ -14066,7 +14084,7 @@
       <c r="C663" s="3" t="n"/>
       <c r="F663" s="3" t="n"/>
       <c r="G663" s="3" t="n"/>
-      <c r="H663" s="14" t="n"/>
+      <c r="H663" s="15" t="n"/>
     </row>
     <row r="664">
       <c r="A664" s="3" t="n"/>
@@ -14074,7 +14092,7 @@
       <c r="C664" s="3" t="n"/>
       <c r="F664" s="3" t="n"/>
       <c r="G664" s="3" t="n"/>
-      <c r="H664" s="14" t="n"/>
+      <c r="H664" s="15" t="n"/>
     </row>
     <row r="665">
       <c r="A665" s="3" t="n"/>
@@ -14082,7 +14100,7 @@
       <c r="C665" s="3" t="n"/>
       <c r="F665" s="3" t="n"/>
       <c r="G665" s="3" t="n"/>
-      <c r="H665" s="14" t="n"/>
+      <c r="H665" s="15" t="n"/>
     </row>
     <row r="666">
       <c r="A666" s="3" t="n"/>
@@ -14090,7 +14108,7 @@
       <c r="C666" s="3" t="n"/>
       <c r="F666" s="3" t="n"/>
       <c r="G666" s="3" t="n"/>
-      <c r="H666" s="14" t="n"/>
+      <c r="H666" s="15" t="n"/>
     </row>
     <row r="667">
       <c r="A667" s="3" t="n"/>
@@ -14098,7 +14116,7 @@
       <c r="C667" s="3" t="n"/>
       <c r="F667" s="3" t="n"/>
       <c r="G667" s="3" t="n"/>
-      <c r="H667" s="14" t="n"/>
+      <c r="H667" s="15" t="n"/>
     </row>
     <row r="668">
       <c r="A668" s="3" t="n"/>
@@ -14106,7 +14124,7 @@
       <c r="C668" s="3" t="n"/>
       <c r="F668" s="3" t="n"/>
       <c r="G668" s="3" t="n"/>
-      <c r="H668" s="14" t="n"/>
+      <c r="H668" s="15" t="n"/>
     </row>
     <row r="669">
       <c r="A669" s="3" t="n"/>
@@ -14114,7 +14132,7 @@
       <c r="C669" s="3" t="n"/>
       <c r="F669" s="3" t="n"/>
       <c r="G669" s="3" t="n"/>
-      <c r="H669" s="14" t="n"/>
+      <c r="H669" s="15" t="n"/>
     </row>
     <row r="670">
       <c r="A670" s="3" t="n"/>
@@ -14122,7 +14140,7 @@
       <c r="C670" s="3" t="n"/>
       <c r="F670" s="3" t="n"/>
       <c r="G670" s="3" t="n"/>
-      <c r="H670" s="14" t="n"/>
+      <c r="H670" s="15" t="n"/>
     </row>
     <row r="671">
       <c r="A671" s="3" t="n"/>
@@ -14130,7 +14148,7 @@
       <c r="C671" s="3" t="n"/>
       <c r="F671" s="3" t="n"/>
       <c r="G671" s="3" t="n"/>
-      <c r="H671" s="14" t="n"/>
+      <c r="H671" s="15" t="n"/>
     </row>
     <row r="672">
       <c r="A672" s="3" t="n"/>
@@ -14138,7 +14156,7 @@
       <c r="C672" s="3" t="n"/>
       <c r="F672" s="3" t="n"/>
       <c r="G672" s="3" t="n"/>
-      <c r="H672" s="14" t="n"/>
+      <c r="H672" s="15" t="n"/>
     </row>
     <row r="673">
       <c r="A673" s="3" t="n"/>
@@ -14146,7 +14164,7 @@
       <c r="C673" s="3" t="n"/>
       <c r="F673" s="3" t="n"/>
       <c r="G673" s="3" t="n"/>
-      <c r="H673" s="14" t="n"/>
+      <c r="H673" s="15" t="n"/>
     </row>
     <row r="674">
       <c r="A674" s="3" t="n"/>
@@ -14154,7 +14172,7 @@
       <c r="C674" s="3" t="n"/>
       <c r="F674" s="3" t="n"/>
       <c r="G674" s="3" t="n"/>
-      <c r="H674" s="14" t="n"/>
+      <c r="H674" s="15" t="n"/>
     </row>
     <row r="675">
       <c r="A675" s="3" t="n"/>
@@ -14162,7 +14180,7 @@
       <c r="C675" s="3" t="n"/>
       <c r="F675" s="3" t="n"/>
       <c r="G675" s="3" t="n"/>
-      <c r="H675" s="14" t="n"/>
+      <c r="H675" s="15" t="n"/>
     </row>
     <row r="676">
       <c r="A676" s="3" t="n"/>
@@ -14170,7 +14188,7 @@
       <c r="C676" s="3" t="n"/>
       <c r="F676" s="3" t="n"/>
       <c r="G676" s="3" t="n"/>
-      <c r="H676" s="14" t="n"/>
+      <c r="H676" s="15" t="n"/>
     </row>
     <row r="677">
       <c r="A677" s="3" t="n"/>
@@ -14178,7 +14196,7 @@
       <c r="C677" s="3" t="n"/>
       <c r="F677" s="3" t="n"/>
       <c r="G677" s="3" t="n"/>
-      <c r="H677" s="14" t="n"/>
+      <c r="H677" s="15" t="n"/>
     </row>
     <row r="678">
       <c r="A678" s="3" t="n"/>
@@ -14186,7 +14204,7 @@
       <c r="C678" s="3" t="n"/>
       <c r="F678" s="3" t="n"/>
       <c r="G678" s="3" t="n"/>
-      <c r="H678" s="14" t="n"/>
+      <c r="H678" s="15" t="n"/>
     </row>
     <row r="679">
       <c r="A679" s="3" t="n"/>
@@ -14194,7 +14212,7 @@
       <c r="C679" s="3" t="n"/>
       <c r="F679" s="3" t="n"/>
       <c r="G679" s="3" t="n"/>
-      <c r="H679" s="14" t="n"/>
+      <c r="H679" s="15" t="n"/>
     </row>
     <row r="680">
       <c r="A680" s="3" t="n"/>
@@ -14202,7 +14220,7 @@
       <c r="C680" s="3" t="n"/>
       <c r="F680" s="3" t="n"/>
       <c r="G680" s="3" t="n"/>
-      <c r="H680" s="14" t="n"/>
+      <c r="H680" s="15" t="n"/>
     </row>
     <row r="681">
       <c r="A681" s="3" t="n"/>
@@ -14210,7 +14228,7 @@
       <c r="C681" s="3" t="n"/>
       <c r="F681" s="3" t="n"/>
       <c r="G681" s="3" t="n"/>
-      <c r="H681" s="14" t="n"/>
+      <c r="H681" s="15" t="n"/>
     </row>
     <row r="682">
       <c r="A682" s="3" t="n"/>
@@ -14218,7 +14236,7 @@
       <c r="C682" s="3" t="n"/>
       <c r="F682" s="3" t="n"/>
       <c r="G682" s="3" t="n"/>
-      <c r="H682" s="14" t="n"/>
+      <c r="H682" s="15" t="n"/>
     </row>
     <row r="683">
       <c r="A683" s="3" t="n"/>
@@ -14226,7 +14244,7 @@
       <c r="C683" s="3" t="n"/>
       <c r="F683" s="3" t="n"/>
       <c r="G683" s="3" t="n"/>
-      <c r="H683" s="14" t="n"/>
+      <c r="H683" s="15" t="n"/>
     </row>
     <row r="684">
       <c r="A684" s="3" t="n"/>
@@ -14234,7 +14252,7 @@
       <c r="C684" s="3" t="n"/>
       <c r="F684" s="3" t="n"/>
       <c r="G684" s="3" t="n"/>
-      <c r="H684" s="14" t="n"/>
+      <c r="H684" s="15" t="n"/>
     </row>
     <row r="685">
       <c r="A685" s="3" t="n"/>
@@ -14242,7 +14260,7 @@
       <c r="C685" s="3" t="n"/>
       <c r="F685" s="3" t="n"/>
       <c r="G685" s="3" t="n"/>
-      <c r="H685" s="14" t="n"/>
+      <c r="H685" s="15" t="n"/>
     </row>
     <row r="686">
       <c r="A686" s="3" t="n"/>
@@ -14250,7 +14268,7 @@
       <c r="C686" s="3" t="n"/>
       <c r="F686" s="3" t="n"/>
       <c r="G686" s="3" t="n"/>
-      <c r="H686" s="14" t="n"/>
+      <c r="H686" s="15" t="n"/>
     </row>
     <row r="687">
       <c r="A687" s="3" t="n"/>
@@ -14258,7 +14276,7 @@
       <c r="C687" s="3" t="n"/>
       <c r="F687" s="3" t="n"/>
       <c r="G687" s="3" t="n"/>
-      <c r="H687" s="14" t="n"/>
+      <c r="H687" s="15" t="n"/>
     </row>
     <row r="688">
       <c r="A688" s="3" t="n"/>
@@ -14266,7 +14284,7 @@
       <c r="C688" s="3" t="n"/>
       <c r="F688" s="3" t="n"/>
       <c r="G688" s="3" t="n"/>
-      <c r="H688" s="14" t="n"/>
+      <c r="H688" s="15" t="n"/>
     </row>
     <row r="689">
       <c r="A689" s="3" t="n"/>
@@ -14274,7 +14292,7 @@
       <c r="C689" s="3" t="n"/>
       <c r="F689" s="3" t="n"/>
       <c r="G689" s="3" t="n"/>
-      <c r="H689" s="14" t="n"/>
+      <c r="H689" s="15" t="n"/>
     </row>
     <row r="690">
       <c r="A690" s="3" t="n"/>
@@ -14282,7 +14300,7 @@
       <c r="C690" s="3" t="n"/>
       <c r="F690" s="3" t="n"/>
       <c r="G690" s="3" t="n"/>
-      <c r="H690" s="14" t="n"/>
+      <c r="H690" s="15" t="n"/>
     </row>
     <row r="691">
       <c r="A691" s="3" t="n"/>
@@ -14290,7 +14308,7 @@
       <c r="C691" s="3" t="n"/>
       <c r="F691" s="3" t="n"/>
       <c r="G691" s="3" t="n"/>
-      <c r="H691" s="14" t="n"/>
+      <c r="H691" s="15" t="n"/>
     </row>
     <row r="692">
       <c r="A692" s="3" t="n"/>
@@ -14298,7 +14316,7 @@
       <c r="C692" s="3" t="n"/>
       <c r="F692" s="3" t="n"/>
       <c r="G692" s="3" t="n"/>
-      <c r="H692" s="14" t="n"/>
+      <c r="H692" s="15" t="n"/>
     </row>
     <row r="693">
       <c r="A693" s="3" t="n"/>
@@ -14306,7 +14324,7 @@
       <c r="C693" s="3" t="n"/>
       <c r="F693" s="3" t="n"/>
       <c r="G693" s="3" t="n"/>
-      <c r="H693" s="14" t="n"/>
+      <c r="H693" s="15" t="n"/>
     </row>
     <row r="694">
       <c r="A694" s="3" t="n"/>
@@ -14314,7 +14332,7 @@
       <c r="C694" s="3" t="n"/>
       <c r="F694" s="3" t="n"/>
       <c r="G694" s="3" t="n"/>
-      <c r="H694" s="14" t="n"/>
+      <c r="H694" s="15" t="n"/>
     </row>
     <row r="695">
       <c r="A695" s="3" t="n"/>
@@ -14322,7 +14340,7 @@
       <c r="C695" s="3" t="n"/>
       <c r="F695" s="3" t="n"/>
       <c r="G695" s="3" t="n"/>
-      <c r="H695" s="14" t="n"/>
+      <c r="H695" s="15" t="n"/>
     </row>
     <row r="696">
       <c r="A696" s="3" t="n"/>
@@ -14330,7 +14348,7 @@
       <c r="C696" s="3" t="n"/>
       <c r="F696" s="3" t="n"/>
       <c r="G696" s="3" t="n"/>
-      <c r="H696" s="14" t="n"/>
+      <c r="H696" s="15" t="n"/>
     </row>
     <row r="697">
       <c r="A697" s="3" t="n"/>
@@ -14338,7 +14356,7 @@
       <c r="C697" s="3" t="n"/>
       <c r="F697" s="3" t="n"/>
       <c r="G697" s="3" t="n"/>
-      <c r="H697" s="14" t="n"/>
+      <c r="H697" s="15" t="n"/>
     </row>
     <row r="698">
       <c r="A698" s="3" t="n"/>
@@ -14346,7 +14364,7 @@
       <c r="C698" s="3" t="n"/>
       <c r="F698" s="3" t="n"/>
       <c r="G698" s="3" t="n"/>
-      <c r="H698" s="14" t="n"/>
+      <c r="H698" s="15" t="n"/>
     </row>
     <row r="699">
       <c r="A699" s="3" t="n"/>
@@ -14354,7 +14372,7 @@
       <c r="C699" s="3" t="n"/>
       <c r="F699" s="3" t="n"/>
       <c r="G699" s="3" t="n"/>
-      <c r="H699" s="14" t="n"/>
+      <c r="H699" s="15" t="n"/>
     </row>
     <row r="700">
       <c r="A700" s="3" t="n"/>
@@ -14362,7 +14380,7 @@
       <c r="C700" s="3" t="n"/>
       <c r="F700" s="3" t="n"/>
       <c r="G700" s="3" t="n"/>
-      <c r="H700" s="14" t="n"/>
+      <c r="H700" s="15" t="n"/>
     </row>
     <row r="701">
       <c r="A701" s="3" t="n"/>
@@ -14370,7 +14388,7 @@
       <c r="C701" s="3" t="n"/>
       <c r="F701" s="3" t="n"/>
       <c r="G701" s="3" t="n"/>
-      <c r="H701" s="14" t="n"/>
+      <c r="H701" s="15" t="n"/>
     </row>
     <row r="702">
       <c r="A702" s="3" t="n"/>
@@ -14378,7 +14396,7 @@
       <c r="C702" s="3" t="n"/>
       <c r="F702" s="3" t="n"/>
       <c r="G702" s="3" t="n"/>
-      <c r="H702" s="14" t="n"/>
+      <c r="H702" s="15" t="n"/>
     </row>
     <row r="703">
       <c r="A703" s="3" t="n"/>
@@ -14386,7 +14404,7 @@
       <c r="C703" s="3" t="n"/>
       <c r="F703" s="3" t="n"/>
       <c r="G703" s="3" t="n"/>
-      <c r="H703" s="14" t="n"/>
+      <c r="H703" s="15" t="n"/>
     </row>
     <row r="704">
       <c r="A704" s="3" t="n"/>
@@ -14394,7 +14412,7 @@
       <c r="C704" s="3" t="n"/>
       <c r="F704" s="3" t="n"/>
       <c r="G704" s="3" t="n"/>
-      <c r="H704" s="14" t="n"/>
+      <c r="H704" s="15" t="n"/>
     </row>
     <row r="705">
       <c r="A705" s="3" t="n"/>
@@ -14402,7 +14420,7 @@
       <c r="C705" s="3" t="n"/>
       <c r="F705" s="3" t="n"/>
       <c r="G705" s="3" t="n"/>
-      <c r="H705" s="14" t="n"/>
+      <c r="H705" s="15" t="n"/>
     </row>
     <row r="706">
       <c r="A706" s="3" t="n"/>
@@ -14410,7 +14428,7 @@
       <c r="C706" s="3" t="n"/>
       <c r="F706" s="3" t="n"/>
       <c r="G706" s="3" t="n"/>
-      <c r="H706" s="14" t="n"/>
+      <c r="H706" s="15" t="n"/>
     </row>
     <row r="707">
       <c r="A707" s="3" t="n"/>
@@ -14418,7 +14436,7 @@
       <c r="C707" s="3" t="n"/>
       <c r="F707" s="3" t="n"/>
       <c r="G707" s="3" t="n"/>
-      <c r="H707" s="14" t="n"/>
+      <c r="H707" s="15" t="n"/>
     </row>
     <row r="708">
       <c r="A708" s="3" t="n"/>
@@ -14426,7 +14444,7 @@
       <c r="C708" s="3" t="n"/>
       <c r="F708" s="3" t="n"/>
       <c r="G708" s="3" t="n"/>
-      <c r="H708" s="14" t="n"/>
+      <c r="H708" s="15" t="n"/>
     </row>
     <row r="709">
       <c r="A709" s="3" t="n"/>
@@ -14434,7 +14452,7 @@
       <c r="C709" s="3" t="n"/>
       <c r="F709" s="3" t="n"/>
       <c r="G709" s="3" t="n"/>
-      <c r="H709" s="14" t="n"/>
+      <c r="H709" s="15" t="n"/>
     </row>
     <row r="710">
       <c r="A710" s="3" t="n"/>
@@ -14442,7 +14460,7 @@
       <c r="C710" s="3" t="n"/>
       <c r="F710" s="3" t="n"/>
       <c r="G710" s="3" t="n"/>
-      <c r="H710" s="14" t="n"/>
+      <c r="H710" s="15" t="n"/>
     </row>
     <row r="711">
       <c r="A711" s="3" t="n"/>
@@ -14450,7 +14468,7 @@
       <c r="C711" s="3" t="n"/>
       <c r="F711" s="3" t="n"/>
       <c r="G711" s="3" t="n"/>
-      <c r="H711" s="14" t="n"/>
+      <c r="H711" s="15" t="n"/>
     </row>
     <row r="712">
       <c r="A712" s="3" t="n"/>
@@ -14458,7 +14476,7 @@
       <c r="C712" s="3" t="n"/>
       <c r="F712" s="3" t="n"/>
       <c r="G712" s="3" t="n"/>
-      <c r="H712" s="14" t="n"/>
+      <c r="H712" s="15" t="n"/>
     </row>
     <row r="713">
       <c r="A713" s="3" t="n"/>
@@ -14466,7 +14484,7 @@
       <c r="C713" s="3" t="n"/>
       <c r="F713" s="3" t="n"/>
       <c r="G713" s="3" t="n"/>
-      <c r="H713" s="14" t="n"/>
+      <c r="H713" s="15" t="n"/>
     </row>
     <row r="714">
       <c r="A714" s="3" t="n"/>
@@ -14474,7 +14492,7 @@
       <c r="C714" s="3" t="n"/>
       <c r="F714" s="3" t="n"/>
       <c r="G714" s="3" t="n"/>
-      <c r="H714" s="14" t="n"/>
+      <c r="H714" s="15" t="n"/>
     </row>
     <row r="715">
       <c r="A715" s="3" t="n"/>
@@ -14482,7 +14500,7 @@
       <c r="C715" s="3" t="n"/>
       <c r="F715" s="3" t="n"/>
       <c r="G715" s="3" t="n"/>
-      <c r="H715" s="14" t="n"/>
+      <c r="H715" s="15" t="n"/>
     </row>
     <row r="716">
       <c r="A716" s="3" t="n"/>
@@ -14490,7 +14508,7 @@
       <c r="C716" s="3" t="n"/>
       <c r="F716" s="3" t="n"/>
       <c r="G716" s="3" t="n"/>
-      <c r="H716" s="14" t="n"/>
+      <c r="H716" s="15" t="n"/>
     </row>
     <row r="717">
       <c r="A717" s="3" t="n"/>
@@ -14498,7 +14516,7 @@
       <c r="C717" s="3" t="n"/>
       <c r="F717" s="3" t="n"/>
       <c r="G717" s="3" t="n"/>
-      <c r="H717" s="14" t="n"/>
+      <c r="H717" s="15" t="n"/>
     </row>
     <row r="718">
       <c r="A718" s="3" t="n"/>
@@ -14506,7 +14524,7 @@
       <c r="C718" s="3" t="n"/>
       <c r="F718" s="3" t="n"/>
       <c r="G718" s="3" t="n"/>
-      <c r="H718" s="14" t="n"/>
+      <c r="H718" s="15" t="n"/>
     </row>
     <row r="719">
       <c r="A719" s="3" t="n"/>
@@ -14514,7 +14532,7 @@
       <c r="C719" s="3" t="n"/>
       <c r="F719" s="3" t="n"/>
       <c r="G719" s="3" t="n"/>
-      <c r="H719" s="14" t="n"/>
+      <c r="H719" s="15" t="n"/>
     </row>
     <row r="720">
       <c r="A720" s="3" t="n"/>
@@ -14522,7 +14540,7 @@
       <c r="C720" s="3" t="n"/>
       <c r="F720" s="3" t="n"/>
       <c r="G720" s="3" t="n"/>
-      <c r="H720" s="14" t="n"/>
+      <c r="H720" s="15" t="n"/>
     </row>
     <row r="721">
       <c r="A721" s="3" t="n"/>
@@ -14530,7 +14548,7 @@
       <c r="C721" s="3" t="n"/>
       <c r="F721" s="3" t="n"/>
       <c r="G721" s="3" t="n"/>
-      <c r="H721" s="14" t="n"/>
+      <c r="H721" s="15" t="n"/>
     </row>
     <row r="722">
       <c r="A722" s="3" t="n"/>
@@ -14538,7 +14556,7 @@
       <c r="C722" s="3" t="n"/>
       <c r="F722" s="3" t="n"/>
       <c r="G722" s="3" t="n"/>
-      <c r="H722" s="14" t="n"/>
+      <c r="H722" s="15" t="n"/>
     </row>
     <row r="723">
       <c r="A723" s="3" t="n"/>
@@ -14546,7 +14564,7 @@
       <c r="C723" s="3" t="n"/>
       <c r="F723" s="3" t="n"/>
       <c r="G723" s="3" t="n"/>
-      <c r="H723" s="14" t="n"/>
+      <c r="H723" s="15" t="n"/>
     </row>
     <row r="724">
       <c r="A724" s="3" t="n"/>
@@ -14554,7 +14572,7 @@
       <c r="C724" s="3" t="n"/>
       <c r="F724" s="3" t="n"/>
       <c r="G724" s="3" t="n"/>
-      <c r="H724" s="14" t="n"/>
+      <c r="H724" s="15" t="n"/>
     </row>
     <row r="725">
       <c r="A725" s="3" t="n"/>
@@ -14562,7 +14580,7 @@
       <c r="C725" s="3" t="n"/>
       <c r="F725" s="3" t="n"/>
       <c r="G725" s="3" t="n"/>
-      <c r="H725" s="14" t="n"/>
+      <c r="H725" s="15" t="n"/>
     </row>
     <row r="726">
       <c r="A726" s="3" t="n"/>
@@ -14570,7 +14588,7 @@
       <c r="C726" s="3" t="n"/>
       <c r="F726" s="3" t="n"/>
       <c r="G726" s="3" t="n"/>
-      <c r="H726" s="14" t="n"/>
+      <c r="H726" s="15" t="n"/>
     </row>
     <row r="727">
       <c r="A727" s="3" t="n"/>
@@ -14578,7 +14596,7 @@
       <c r="C727" s="3" t="n"/>
       <c r="F727" s="3" t="n"/>
       <c r="G727" s="3" t="n"/>
-      <c r="H727" s="14" t="n"/>
+      <c r="H727" s="15" t="n"/>
     </row>
     <row r="728">
       <c r="A728" s="3" t="n"/>
@@ -14586,7 +14604,7 @@
       <c r="C728" s="3" t="n"/>
       <c r="F728" s="3" t="n"/>
       <c r="G728" s="3" t="n"/>
-      <c r="H728" s="14" t="n"/>
+      <c r="H728" s="15" t="n"/>
     </row>
     <row r="729">
       <c r="A729" s="3" t="n"/>
@@ -14594,7 +14612,7 @@
       <c r="C729" s="3" t="n"/>
       <c r="F729" s="3" t="n"/>
       <c r="G729" s="3" t="n"/>
-      <c r="H729" s="14" t="n"/>
+      <c r="H729" s="15" t="n"/>
     </row>
     <row r="730">
       <c r="A730" s="3" t="n"/>
@@ -14602,7 +14620,7 @@
       <c r="C730" s="3" t="n"/>
       <c r="F730" s="3" t="n"/>
       <c r="G730" s="3" t="n"/>
-      <c r="H730" s="14" t="n"/>
+      <c r="H730" s="15" t="n"/>
     </row>
     <row r="731">
       <c r="A731" s="3" t="n"/>
@@ -14610,7 +14628,7 @@
       <c r="C731" s="3" t="n"/>
       <c r="F731" s="3" t="n"/>
       <c r="G731" s="3" t="n"/>
-      <c r="H731" s="14" t="n"/>
+      <c r="H731" s="15" t="n"/>
     </row>
     <row r="732">
       <c r="A732" s="3" t="n"/>
@@ -14618,7 +14636,7 @@
       <c r="C732" s="3" t="n"/>
       <c r="F732" s="3" t="n"/>
       <c r="G732" s="3" t="n"/>
-      <c r="H732" s="14" t="n"/>
+      <c r="H732" s="15" t="n"/>
     </row>
     <row r="733">
       <c r="A733" s="3" t="n"/>
@@ -14626,7 +14644,7 @@
       <c r="C733" s="3" t="n"/>
       <c r="F733" s="3" t="n"/>
       <c r="G733" s="3" t="n"/>
-      <c r="H733" s="14" t="n"/>
+      <c r="H733" s="15" t="n"/>
     </row>
     <row r="734">
       <c r="A734" s="3" t="n"/>
@@ -14634,7 +14652,7 @@
       <c r="C734" s="3" t="n"/>
       <c r="F734" s="3" t="n"/>
       <c r="G734" s="3" t="n"/>
-      <c r="H734" s="14" t="n"/>
+      <c r="H734" s="15" t="n"/>
     </row>
     <row r="735">
       <c r="A735" s="3" t="n"/>
@@ -14642,7 +14660,7 @@
       <c r="C735" s="3" t="n"/>
       <c r="F735" s="3" t="n"/>
       <c r="G735" s="3" t="n"/>
-      <c r="H735" s="14" t="n"/>
+      <c r="H735" s="15" t="n"/>
     </row>
     <row r="736">
       <c r="A736" s="3" t="n"/>
@@ -14650,7 +14668,7 @@
       <c r="C736" s="3" t="n"/>
       <c r="F736" s="3" t="n"/>
       <c r="G736" s="3" t="n"/>
-      <c r="H736" s="14" t="n"/>
+      <c r="H736" s="15" t="n"/>
     </row>
     <row r="737">
       <c r="A737" s="3" t="n"/>
@@ -14658,7 +14676,7 @@
       <c r="C737" s="3" t="n"/>
       <c r="F737" s="3" t="n"/>
       <c r="G737" s="3" t="n"/>
-      <c r="H737" s="14" t="n"/>
+      <c r="H737" s="15" t="n"/>
     </row>
     <row r="738">
       <c r="A738" s="3" t="n"/>
@@ -14666,7 +14684,7 @@
       <c r="C738" s="3" t="n"/>
       <c r="F738" s="3" t="n"/>
       <c r="G738" s="3" t="n"/>
-      <c r="H738" s="14" t="n"/>
+      <c r="H738" s="15" t="n"/>
     </row>
     <row r="739">
       <c r="A739" s="3" t="n"/>
@@ -14674,7 +14692,7 @@
       <c r="C739" s="3" t="n"/>
       <c r="F739" s="3" t="n"/>
       <c r="G739" s="3" t="n"/>
-      <c r="H739" s="14" t="n"/>
+      <c r="H739" s="15" t="n"/>
     </row>
     <row r="740">
       <c r="A740" s="3" t="n"/>
@@ -14682,7 +14700,7 @@
       <c r="C740" s="3" t="n"/>
       <c r="F740" s="3" t="n"/>
       <c r="G740" s="3" t="n"/>
-      <c r="H740" s="14" t="n"/>
+      <c r="H740" s="15" t="n"/>
     </row>
     <row r="741">
       <c r="A741" s="3" t="n"/>
@@ -14690,7 +14708,7 @@
       <c r="C741" s="3" t="n"/>
       <c r="F741" s="3" t="n"/>
       <c r="G741" s="3" t="n"/>
-      <c r="H741" s="14" t="n"/>
+      <c r="H741" s="15" t="n"/>
     </row>
     <row r="742">
       <c r="A742" s="3" t="n"/>
@@ -14698,7 +14716,7 @@
       <c r="C742" s="3" t="n"/>
       <c r="F742" s="3" t="n"/>
       <c r="G742" s="3" t="n"/>
-      <c r="H742" s="14" t="n"/>
+      <c r="H742" s="15" t="n"/>
     </row>
     <row r="743">
       <c r="A743" s="3" t="n"/>
@@ -14706,7 +14724,7 @@
       <c r="C743" s="3" t="n"/>
       <c r="F743" s="3" t="n"/>
       <c r="G743" s="3" t="n"/>
-      <c r="H743" s="14" t="n"/>
+      <c r="H743" s="15" t="n"/>
     </row>
     <row r="744">
       <c r="A744" s="3" t="n"/>
@@ -14714,7 +14732,7 @@
       <c r="C744" s="3" t="n"/>
       <c r="F744" s="3" t="n"/>
       <c r="G744" s="3" t="n"/>
-      <c r="H744" s="14" t="n"/>
+      <c r="H744" s="15" t="n"/>
     </row>
     <row r="745">
       <c r="A745" s="3" t="n"/>
@@ -14722,7 +14740,7 @@
       <c r="C745" s="3" t="n"/>
       <c r="F745" s="3" t="n"/>
       <c r="G745" s="3" t="n"/>
-      <c r="H745" s="14" t="n"/>
+      <c r="H745" s="15" t="n"/>
     </row>
     <row r="746">
       <c r="A746" s="3" t="n"/>
@@ -14730,7 +14748,7 @@
       <c r="C746" s="3" t="n"/>
       <c r="F746" s="3" t="n"/>
       <c r="G746" s="3" t="n"/>
-      <c r="H746" s="14" t="n"/>
+      <c r="H746" s="15" t="n"/>
     </row>
     <row r="747">
       <c r="A747" s="3" t="n"/>
@@ -14738,7 +14756,7 @@
       <c r="C747" s="3" t="n"/>
       <c r="F747" s="3" t="n"/>
       <c r="G747" s="3" t="n"/>
-      <c r="H747" s="14" t="n"/>
+      <c r="H747" s="15" t="n"/>
     </row>
     <row r="748">
       <c r="A748" s="3" t="n"/>
@@ -14746,7 +14764,7 @@
       <c r="C748" s="3" t="n"/>
       <c r="F748" s="3" t="n"/>
       <c r="G748" s="3" t="n"/>
-      <c r="H748" s="14" t="n"/>
+      <c r="H748" s="15" t="n"/>
     </row>
     <row r="749">
       <c r="A749" s="3" t="n"/>
@@ -14754,7 +14772,7 @@
       <c r="C749" s="3" t="n"/>
       <c r="F749" s="3" t="n"/>
       <c r="G749" s="3" t="n"/>
-      <c r="H749" s="14" t="n"/>
+      <c r="H749" s="15" t="n"/>
     </row>
     <row r="750">
       <c r="A750" s="3" t="n"/>
@@ -14762,7 +14780,7 @@
       <c r="C750" s="3" t="n"/>
       <c r="F750" s="3" t="n"/>
       <c r="G750" s="3" t="n"/>
-      <c r="H750" s="14" t="n"/>
+      <c r="H750" s="15" t="n"/>
     </row>
     <row r="751">
       <c r="A751" s="3" t="n"/>
@@ -14770,7 +14788,7 @@
       <c r="C751" s="3" t="n"/>
       <c r="F751" s="3" t="n"/>
       <c r="G751" s="3" t="n"/>
-      <c r="H751" s="14" t="n"/>
+      <c r="H751" s="15" t="n"/>
     </row>
     <row r="752">
       <c r="A752" s="3" t="n"/>
@@ -14778,7 +14796,7 @@
       <c r="C752" s="3" t="n"/>
       <c r="F752" s="3" t="n"/>
       <c r="G752" s="3" t="n"/>
-      <c r="H752" s="14" t="n"/>
+      <c r="H752" s="15" t="n"/>
     </row>
     <row r="753">
       <c r="A753" s="3" t="n"/>
@@ -14786,7 +14804,7 @@
       <c r="C753" s="3" t="n"/>
       <c r="F753" s="3" t="n"/>
       <c r="G753" s="3" t="n"/>
-      <c r="H753" s="14" t="n"/>
+      <c r="H753" s="15" t="n"/>
     </row>
     <row r="754">
       <c r="A754" s="3" t="n"/>
@@ -14794,7 +14812,7 @@
       <c r="C754" s="3" t="n"/>
       <c r="F754" s="3" t="n"/>
       <c r="G754" s="3" t="n"/>
-      <c r="H754" s="14" t="n"/>
+      <c r="H754" s="15" t="n"/>
     </row>
     <row r="755">
       <c r="A755" s="3" t="n"/>
@@ -14802,7 +14820,7 @@
       <c r="C755" s="3" t="n"/>
       <c r="F755" s="3" t="n"/>
       <c r="G755" s="3" t="n"/>
-      <c r="H755" s="14" t="n"/>
+      <c r="H755" s="15" t="n"/>
     </row>
     <row r="756">
       <c r="A756" s="3" t="n"/>
@@ -14810,7 +14828,7 @@
       <c r="C756" s="3" t="n"/>
       <c r="F756" s="3" t="n"/>
       <c r="G756" s="3" t="n"/>
-      <c r="H756" s="14" t="n"/>
+      <c r="H756" s="15" t="n"/>
     </row>
     <row r="757">
       <c r="A757" s="3" t="n"/>
@@ -14818,7 +14836,7 @@
       <c r="C757" s="3" t="n"/>
       <c r="F757" s="3" t="n"/>
       <c r="G757" s="3" t="n"/>
-      <c r="H757" s="14" t="n"/>
+      <c r="H757" s="15" t="n"/>
     </row>
     <row r="758">
       <c r="A758" s="3" t="n"/>
@@ -14826,7 +14844,7 @@
       <c r="C758" s="3" t="n"/>
       <c r="F758" s="3" t="n"/>
       <c r="G758" s="3" t="n"/>
-      <c r="H758" s="14" t="n"/>
+      <c r="H758" s="15" t="n"/>
     </row>
     <row r="759">
       <c r="A759" s="3" t="n"/>
@@ -14834,7 +14852,7 @@
       <c r="C759" s="3" t="n"/>
       <c r="F759" s="3" t="n"/>
       <c r="G759" s="3" t="n"/>
-      <c r="H759" s="14" t="n"/>
+      <c r="H759" s="15" t="n"/>
     </row>
     <row r="760">
       <c r="A760" s="3" t="n"/>
@@ -14842,7 +14860,7 @@
       <c r="C760" s="3" t="n"/>
       <c r="F760" s="3" t="n"/>
       <c r="G760" s="3" t="n"/>
-      <c r="H760" s="14" t="n"/>
+      <c r="H760" s="15" t="n"/>
     </row>
     <row r="761">
       <c r="A761" s="3" t="n"/>
@@ -14850,7 +14868,7 @@
       <c r="C761" s="3" t="n"/>
       <c r="F761" s="3" t="n"/>
       <c r="G761" s="3" t="n"/>
-      <c r="H761" s="14" t="n"/>
+      <c r="H761" s="15" t="n"/>
     </row>
     <row r="762">
       <c r="A762" s="3" t="n"/>
@@ -14858,7 +14876,7 @@
       <c r="C762" s="3" t="n"/>
       <c r="F762" s="3" t="n"/>
       <c r="G762" s="3" t="n"/>
-      <c r="H762" s="14" t="n"/>
+      <c r="H762" s="15" t="n"/>
     </row>
     <row r="763">
       <c r="A763" s="3" t="n"/>
@@ -14866,7 +14884,7 @@
       <c r="C763" s="3" t="n"/>
       <c r="F763" s="3" t="n"/>
       <c r="G763" s="3" t="n"/>
-      <c r="H763" s="14" t="n"/>
+      <c r="H763" s="15" t="n"/>
     </row>
     <row r="764">
       <c r="A764" s="3" t="n"/>
@@ -14874,7 +14892,7 @@
       <c r="C764" s="3" t="n"/>
       <c r="F764" s="3" t="n"/>
       <c r="G764" s="3" t="n"/>
-      <c r="H764" s="14" t="n"/>
+      <c r="H764" s="15" t="n"/>
     </row>
     <row r="765">
       <c r="A765" s="3" t="n"/>
@@ -14882,7 +14900,7 @@
       <c r="C765" s="3" t="n"/>
       <c r="F765" s="3" t="n"/>
       <c r="G765" s="3" t="n"/>
-      <c r="H765" s="14" t="n"/>
+      <c r="H765" s="15" t="n"/>
     </row>
     <row r="766">
       <c r="A766" s="3" t="n"/>
@@ -14890,7 +14908,7 @@
       <c r="C766" s="3" t="n"/>
       <c r="F766" s="3" t="n"/>
       <c r="G766" s="3" t="n"/>
-      <c r="H766" s="14" t="n"/>
+      <c r="H766" s="15" t="n"/>
     </row>
     <row r="767">
       <c r="A767" s="3" t="n"/>
@@ -14898,7 +14916,7 @@
       <c r="C767" s="3" t="n"/>
       <c r="F767" s="3" t="n"/>
       <c r="G767" s="3" t="n"/>
-      <c r="H767" s="14" t="n"/>
+      <c r="H767" s="15" t="n"/>
     </row>
     <row r="768">
       <c r="A768" s="3" t="n"/>
@@ -14906,7 +14924,7 @@
       <c r="C768" s="3" t="n"/>
       <c r="F768" s="3" t="n"/>
       <c r="G768" s="3" t="n"/>
-      <c r="H768" s="14" t="n"/>
+      <c r="H768" s="15" t="n"/>
     </row>
     <row r="769">
       <c r="A769" s="3" t="n"/>
@@ -14914,7 +14932,7 @@
       <c r="C769" s="3" t="n"/>
       <c r="F769" s="3" t="n"/>
       <c r="G769" s="3" t="n"/>
-      <c r="H769" s="14" t="n"/>
+      <c r="H769" s="15" t="n"/>
     </row>
     <row r="770">
       <c r="A770" s="3" t="n"/>
@@ -14922,7 +14940,7 @@
       <c r="C770" s="3" t="n"/>
       <c r="F770" s="3" t="n"/>
       <c r="G770" s="3" t="n"/>
-      <c r="H770" s="14" t="n"/>
+      <c r="H770" s="15" t="n"/>
     </row>
     <row r="771">
       <c r="A771" s="3" t="n"/>
@@ -14930,7 +14948,7 @@
       <c r="C771" s="3" t="n"/>
       <c r="F771" s="3" t="n"/>
       <c r="G771" s="3" t="n"/>
-      <c r="H771" s="14" t="n"/>
+      <c r="H771" s="15" t="n"/>
     </row>
     <row r="772">
       <c r="A772" s="3" t="n"/>
@@ -14938,7 +14956,7 @@
       <c r="C772" s="3" t="n"/>
       <c r="F772" s="3" t="n"/>
       <c r="G772" s="3" t="n"/>
-      <c r="H772" s="14" t="n"/>
+      <c r="H772" s="15" t="n"/>
     </row>
     <row r="773">
       <c r="A773" s="3" t="n"/>
@@ -14946,7 +14964,7 @@
       <c r="C773" s="3" t="n"/>
       <c r="F773" s="3" t="n"/>
       <c r="G773" s="3" t="n"/>
-      <c r="H773" s="14" t="n"/>
+      <c r="H773" s="15" t="n"/>
     </row>
     <row r="774">
       <c r="A774" s="3" t="n"/>
@@ -14954,7 +14972,7 @@
       <c r="C774" s="3" t="n"/>
       <c r="F774" s="3" t="n"/>
       <c r="G774" s="3" t="n"/>
-      <c r="H774" s="14" t="n"/>
+      <c r="H774" s="15" t="n"/>
     </row>
     <row r="775">
       <c r="A775" s="3" t="n"/>
@@ -14962,7 +14980,7 @@
       <c r="C775" s="3" t="n"/>
       <c r="F775" s="3" t="n"/>
       <c r="G775" s="3" t="n"/>
-      <c r="H775" s="14" t="n"/>
+      <c r="H775" s="15" t="n"/>
     </row>
     <row r="776">
       <c r="A776" s="3" t="n"/>
@@ -14970,7 +14988,7 @@
       <c r="C776" s="3" t="n"/>
       <c r="F776" s="3" t="n"/>
       <c r="G776" s="3" t="n"/>
-      <c r="H776" s="14" t="n"/>
+      <c r="H776" s="15" t="n"/>
     </row>
     <row r="777">
       <c r="A777" s="3" t="n"/>
@@ -14978,7 +14996,7 @@
       <c r="C777" s="3" t="n"/>
       <c r="F777" s="3" t="n"/>
       <c r="G777" s="3" t="n"/>
-      <c r="H777" s="14" t="n"/>
+      <c r="H777" s="15" t="n"/>
     </row>
     <row r="778">
       <c r="A778" s="3" t="n"/>
@@ -14986,7 +15004,7 @@
       <c r="C778" s="3" t="n"/>
       <c r="F778" s="3" t="n"/>
       <c r="G778" s="3" t="n"/>
-      <c r="H778" s="14" t="n"/>
+      <c r="H778" s="15" t="n"/>
     </row>
     <row r="779">
       <c r="A779" s="3" t="n"/>
@@ -14994,7 +15012,7 @@
       <c r="C779" s="3" t="n"/>
       <c r="F779" s="3" t="n"/>
       <c r="G779" s="3" t="n"/>
-      <c r="H779" s="14" t="n"/>
+      <c r="H779" s="15" t="n"/>
     </row>
     <row r="780">
       <c r="A780" s="3" t="n"/>
@@ -15002,7 +15020,7 @@
       <c r="C780" s="3" t="n"/>
       <c r="F780" s="3" t="n"/>
       <c r="G780" s="3" t="n"/>
-      <c r="H780" s="14" t="n"/>
+      <c r="H780" s="15" t="n"/>
     </row>
     <row r="781">
       <c r="A781" s="3" t="n"/>
@@ -15010,7 +15028,7 @@
       <c r="C781" s="3" t="n"/>
       <c r="F781" s="3" t="n"/>
       <c r="G781" s="3" t="n"/>
-      <c r="H781" s="14" t="n"/>
+      <c r="H781" s="15" t="n"/>
     </row>
     <row r="782">
       <c r="A782" s="3" t="n"/>
@@ -15018,7 +15036,7 @@
       <c r="C782" s="3" t="n"/>
       <c r="F782" s="3" t="n"/>
       <c r="G782" s="3" t="n"/>
-      <c r="H782" s="14" t="n"/>
+      <c r="H782" s="15" t="n"/>
     </row>
     <row r="783">
       <c r="A783" s="3" t="n"/>
@@ -15026,7 +15044,7 @@
       <c r="C783" s="3" t="n"/>
       <c r="F783" s="3" t="n"/>
       <c r="G783" s="3" t="n"/>
-      <c r="H783" s="14" t="n"/>
+      <c r="H783" s="15" t="n"/>
     </row>
     <row r="784">
       <c r="A784" s="3" t="n"/>
@@ -15034,7 +15052,7 @@
       <c r="C784" s="3" t="n"/>
       <c r="F784" s="3" t="n"/>
       <c r="G784" s="3" t="n"/>
-      <c r="H784" s="14" t="n"/>
+      <c r="H784" s="15" t="n"/>
     </row>
     <row r="785">
       <c r="A785" s="3" t="n"/>
@@ -15042,7 +15060,7 @@
       <c r="C785" s="3" t="n"/>
       <c r="F785" s="3" t="n"/>
       <c r="G785" s="3" t="n"/>
-      <c r="H785" s="14" t="n"/>
+      <c r="H785" s="15" t="n"/>
     </row>
     <row r="786">
       <c r="A786" s="3" t="n"/>
@@ -15050,7 +15068,7 @@
       <c r="C786" s="3" t="n"/>
       <c r="F786" s="3" t="n"/>
       <c r="G786" s="3" t="n"/>
-      <c r="H786" s="14" t="n"/>
+      <c r="H786" s="15" t="n"/>
     </row>
     <row r="787">
       <c r="A787" s="3" t="n"/>
@@ -15058,7 +15076,7 @@
       <c r="C787" s="3" t="n"/>
       <c r="F787" s="3" t="n"/>
       <c r="G787" s="3" t="n"/>
-      <c r="H787" s="14" t="n"/>
+      <c r="H787" s="15" t="n"/>
     </row>
     <row r="788">
       <c r="A788" s="3" t="n"/>
@@ -15066,7 +15084,7 @@
       <c r="C788" s="3" t="n"/>
       <c r="F788" s="3" t="n"/>
       <c r="G788" s="3" t="n"/>
-      <c r="H788" s="14" t="n"/>
+      <c r="H788" s="15" t="n"/>
     </row>
     <row r="789">
       <c r="A789" s="3" t="n"/>
@@ -15074,7 +15092,7 @@
       <c r="C789" s="3" t="n"/>
       <c r="F789" s="3" t="n"/>
       <c r="G789" s="3" t="n"/>
-      <c r="H789" s="14" t="n"/>
+      <c r="H789" s="15" t="n"/>
     </row>
     <row r="790">
       <c r="A790" s="3" t="n"/>
@@ -15082,7 +15100,7 @@
       <c r="C790" s="3" t="n"/>
       <c r="F790" s="3" t="n"/>
       <c r="G790" s="3" t="n"/>
-      <c r="H790" s="14" t="n"/>
+      <c r="H790" s="15" t="n"/>
     </row>
     <row r="791">
       <c r="A791" s="3" t="n"/>
@@ -15090,7 +15108,7 @@
       <c r="C791" s="3" t="n"/>
       <c r="F791" s="3" t="n"/>
       <c r="G791" s="3" t="n"/>
-      <c r="H791" s="14" t="n"/>
+      <c r="H791" s="15" t="n"/>
     </row>
     <row r="792">
       <c r="A792" s="3" t="n"/>
@@ -15098,7 +15116,7 @@
       <c r="C792" s="3" t="n"/>
       <c r="F792" s="3" t="n"/>
       <c r="G792" s="3" t="n"/>
-      <c r="H792" s="14" t="n"/>
+      <c r="H792" s="15" t="n"/>
     </row>
     <row r="793">
       <c r="A793" s="3" t="n"/>
@@ -15106,7 +15124,7 @@
       <c r="C793" s="3" t="n"/>
       <c r="F793" s="3" t="n"/>
       <c r="G793" s="3" t="n"/>
-      <c r="H793" s="14" t="n"/>
+      <c r="H793" s="15" t="n"/>
     </row>
     <row r="794">
       <c r="A794" s="3" t="n"/>
@@ -15114,7 +15132,7 @@
       <c r="C794" s="3" t="n"/>
       <c r="F794" s="3" t="n"/>
       <c r="G794" s="3" t="n"/>
-      <c r="H794" s="14" t="n"/>
+      <c r="H794" s="15" t="n"/>
     </row>
     <row r="795">
       <c r="A795" s="3" t="n"/>
@@ -15122,7 +15140,7 @@
       <c r="C795" s="3" t="n"/>
       <c r="F795" s="3" t="n"/>
       <c r="G795" s="3" t="n"/>
-      <c r="H795" s="14" t="n"/>
+      <c r="H795" s="15" t="n"/>
     </row>
     <row r="796">
       <c r="A796" s="3" t="n"/>
@@ -15130,7 +15148,7 @@
       <c r="C796" s="3" t="n"/>
       <c r="F796" s="3" t="n"/>
       <c r="G796" s="3" t="n"/>
-      <c r="H796" s="14" t="n"/>
+      <c r="H796" s="15" t="n"/>
     </row>
     <row r="797">
       <c r="A797" s="3" t="n"/>
@@ -15138,7 +15156,7 @@
       <c r="C797" s="3" t="n"/>
       <c r="F797" s="3" t="n"/>
       <c r="G797" s="3" t="n"/>
-      <c r="H797" s="14" t="n"/>
+      <c r="H797" s="15" t="n"/>
     </row>
     <row r="798">
       <c r="A798" s="3" t="n"/>
@@ -15146,7 +15164,7 @@
       <c r="C798" s="3" t="n"/>
       <c r="F798" s="3" t="n"/>
       <c r="G798" s="3" t="n"/>
-      <c r="H798" s="14" t="n"/>
+      <c r="H798" s="15" t="n"/>
     </row>
     <row r="799">
       <c r="A799" s="3" t="n"/>
@@ -15154,7 +15172,7 @@
       <c r="C799" s="3" t="n"/>
       <c r="F799" s="3" t="n"/>
       <c r="G799" s="3" t="n"/>
-      <c r="H799" s="14" t="n"/>
+      <c r="H799" s="15" t="n"/>
     </row>
     <row r="800">
       <c r="A800" s="3" t="n"/>
@@ -15162,7 +15180,7 @@
       <c r="C800" s="3" t="n"/>
       <c r="F800" s="3" t="n"/>
       <c r="G800" s="3" t="n"/>
-      <c r="H800" s="14" t="n"/>
+      <c r="H800" s="15" t="n"/>
     </row>
     <row r="801">
       <c r="A801" s="3" t="n"/>
@@ -15170,7 +15188,7 @@
       <c r="C801" s="3" t="n"/>
       <c r="F801" s="3" t="n"/>
       <c r="G801" s="3" t="n"/>
-      <c r="H801" s="14" t="n"/>
+      <c r="H801" s="15" t="n"/>
     </row>
     <row r="802">
       <c r="A802" s="3" t="n"/>
@@ -15178,7 +15196,7 @@
       <c r="C802" s="3" t="n"/>
       <c r="F802" s="3" t="n"/>
       <c r="G802" s="3" t="n"/>
-      <c r="H802" s="14" t="n"/>
+      <c r="H802" s="15" t="n"/>
     </row>
     <row r="803">
       <c r="A803" s="3" t="n"/>
@@ -15186,7 +15204,7 @@
       <c r="C803" s="3" t="n"/>
       <c r="F803" s="3" t="n"/>
       <c r="G803" s="3" t="n"/>
-      <c r="H803" s="14" t="n"/>
+      <c r="H803" s="15" t="n"/>
     </row>
     <row r="804">
       <c r="A804" s="3" t="n"/>
@@ -15194,7 +15212,7 @@
       <c r="C804" s="3" t="n"/>
       <c r="F804" s="3" t="n"/>
       <c r="G804" s="3" t="n"/>
-      <c r="H804" s="14" t="n"/>
+      <c r="H804" s="15" t="n"/>
     </row>
     <row r="805">
       <c r="A805" s="3" t="n"/>
@@ -15202,7 +15220,7 @@
       <c r="C805" s="3" t="n"/>
       <c r="F805" s="3" t="n"/>
       <c r="G805" s="3" t="n"/>
-      <c r="H805" s="14" t="n"/>
+      <c r="H805" s="15" t="n"/>
     </row>
     <row r="806">
       <c r="A806" s="3" t="n"/>
@@ -15210,7 +15228,7 @@
       <c r="C806" s="3" t="n"/>
       <c r="F806" s="3" t="n"/>
       <c r="G806" s="3" t="n"/>
-      <c r="H806" s="14" t="n"/>
+      <c r="H806" s="15" t="n"/>
     </row>
     <row r="807">
       <c r="A807" s="3" t="n"/>
@@ -15218,7 +15236,7 @@
       <c r="C807" s="3" t="n"/>
       <c r="F807" s="3" t="n"/>
       <c r="G807" s="3" t="n"/>
-      <c r="H807" s="14" t="n"/>
+      <c r="H807" s="15" t="n"/>
     </row>
     <row r="808">
       <c r="A808" s="3" t="n"/>
@@ -15226,7 +15244,7 @@
       <c r="C808" s="3" t="n"/>
       <c r="F808" s="3" t="n"/>
       <c r="G808" s="3" t="n"/>
-      <c r="H808" s="14" t="n"/>
+      <c r="H808" s="15" t="n"/>
     </row>
     <row r="809">
       <c r="A809" s="3" t="n"/>
@@ -15234,7 +15252,7 @@
       <c r="C809" s="3" t="n"/>
       <c r="F809" s="3" t="n"/>
       <c r="G809" s="3" t="n"/>
-      <c r="H809" s="14" t="n"/>
+      <c r="H809" s="15" t="n"/>
     </row>
     <row r="810">
       <c r="A810" s="3" t="n"/>
@@ -15242,7 +15260,7 @@
       <c r="C810" s="3" t="n"/>
       <c r="F810" s="3" t="n"/>
       <c r="G810" s="3" t="n"/>
-      <c r="H810" s="14" t="n"/>
+      <c r="H810" s="15" t="n"/>
     </row>
     <row r="811">
       <c r="A811" s="3" t="n"/>
@@ -15250,7 +15268,7 @@
       <c r="C811" s="3" t="n"/>
       <c r="F811" s="3" t="n"/>
       <c r="G811" s="3" t="n"/>
-      <c r="H811" s="14" t="n"/>
+      <c r="H811" s="15" t="n"/>
     </row>
     <row r="812">
       <c r="A812" s="3" t="n"/>
@@ -15258,7 +15276,7 @@
       <c r="C812" s="3" t="n"/>
       <c r="F812" s="3" t="n"/>
       <c r="G812" s="3" t="n"/>
-      <c r="H812" s="14" t="n"/>
+      <c r="H812" s="15" t="n"/>
     </row>
     <row r="813">
       <c r="A813" s="3" t="n"/>
@@ -15266,7 +15284,7 @@
       <c r="C813" s="3" t="n"/>
       <c r="F813" s="3" t="n"/>
       <c r="G813" s="3" t="n"/>
-      <c r="H813" s="14" t="n"/>
+      <c r="H813" s="15" t="n"/>
     </row>
     <row r="814">
       <c r="A814" s="3" t="n"/>
@@ -15274,7 +15292,7 @@
       <c r="C814" s="3" t="n"/>
       <c r="F814" s="3" t="n"/>
       <c r="G814" s="3" t="n"/>
-      <c r="H814" s="14" t="n"/>
+      <c r="H814" s="15" t="n"/>
     </row>
     <row r="815">
       <c r="A815" s="3" t="n"/>
@@ -15282,7 +15300,7 @@
       <c r="C815" s="3" t="n"/>
       <c r="F815" s="3" t="n"/>
       <c r="G815" s="3" t="n"/>
-      <c r="H815" s="14" t="n"/>
+      <c r="H815" s="15" t="n"/>
     </row>
     <row r="816">
       <c r="A816" s="3" t="n"/>
@@ -15290,7 +15308,7 @@
       <c r="C816" s="3" t="n"/>
       <c r="F816" s="3" t="n"/>
       <c r="G816" s="3" t="n"/>
-      <c r="H816" s="14" t="n"/>
+      <c r="H816" s="15" t="n"/>
     </row>
     <row r="817">
       <c r="A817" s="3" t="n"/>
@@ -15298,7 +15316,7 @@
       <c r="C817" s="3" t="n"/>
       <c r="F817" s="3" t="n"/>
       <c r="G817" s="3" t="n"/>
-      <c r="H817" s="14" t="n"/>
+      <c r="H817" s="15" t="n"/>
     </row>
     <row r="818">
       <c r="A818" s="3" t="n"/>
@@ -15306,7 +15324,7 @@
       <c r="C818" s="3" t="n"/>
       <c r="F818" s="3" t="n"/>
       <c r="G818" s="3" t="n"/>
-      <c r="H818" s="14" t="n"/>
+      <c r="H818" s="15" t="n"/>
     </row>
     <row r="819">
       <c r="A819" s="3" t="n"/>
@@ -15314,7 +15332,7 @@
       <c r="C819" s="3" t="n"/>
       <c r="F819" s="3" t="n"/>
       <c r="G819" s="3" t="n"/>
-      <c r="H819" s="14" t="n"/>
+      <c r="H819" s="15" t="n"/>
     </row>
     <row r="820">
       <c r="A820" s="3" t="n"/>
@@ -15322,7 +15340,7 @@
       <c r="C820" s="3" t="n"/>
       <c r="F820" s="3" t="n"/>
       <c r="G820" s="3" t="n"/>
-      <c r="H820" s="14" t="n"/>
+      <c r="H820" s="15" t="n"/>
     </row>
     <row r="821">
       <c r="A821" s="3" t="n"/>
@@ -15330,7 +15348,7 @@
       <c r="C821" s="3" t="n"/>
       <c r="F821" s="3" t="n"/>
       <c r="G821" s="3" t="n"/>
-      <c r="H821" s="14" t="n"/>
+      <c r="H821" s="15" t="n"/>
     </row>
     <row r="822">
       <c r="A822" s="3" t="n"/>
@@ -15338,7 +15356,7 @@
       <c r="C822" s="3" t="n"/>
       <c r="F822" s="3" t="n"/>
       <c r="G822" s="3" t="n"/>
-      <c r="H822" s="14" t="n"/>
+      <c r="H822" s="15" t="n"/>
     </row>
     <row r="823">
       <c r="A823" s="3" t="n"/>
@@ -15346,7 +15364,7 @@
       <c r="C823" s="3" t="n"/>
       <c r="F823" s="3" t="n"/>
       <c r="G823" s="3" t="n"/>
-      <c r="H823" s="14" t="n"/>
+      <c r="H823" s="15" t="n"/>
     </row>
     <row r="824">
       <c r="A824" s="3" t="n"/>
@@ -15354,7 +15372,7 @@
       <c r="C824" s="3" t="n"/>
       <c r="F824" s="3" t="n"/>
       <c r="G824" s="3" t="n"/>
-      <c r="H824" s="14" t="n"/>
+      <c r="H824" s="15" t="n"/>
     </row>
     <row r="825">
       <c r="A825" s="3" t="n"/>
@@ -15362,7 +15380,7 @@
       <c r="C825" s="3" t="n"/>
       <c r="F825" s="3" t="n"/>
       <c r="G825" s="3" t="n"/>
-      <c r="H825" s="14" t="n"/>
+      <c r="H825" s="15" t="n"/>
     </row>
     <row r="826">
       <c r="A826" s="3" t="n"/>
@@ -15370,7 +15388,7 @@
       <c r="C826" s="3" t="n"/>
       <c r="F826" s="3" t="n"/>
       <c r="G826" s="3" t="n"/>
-      <c r="H826" s="14" t="n"/>
+      <c r="H826" s="15" t="n"/>
     </row>
     <row r="827">
       <c r="A827" s="3" t="n"/>
@@ -15378,7 +15396,7 @@
       <c r="C827" s="3" t="n"/>
       <c r="F827" s="3" t="n"/>
       <c r="G827" s="3" t="n"/>
-      <c r="H827" s="14" t="n"/>
+      <c r="H827" s="15" t="n"/>
     </row>
     <row r="828">
       <c r="A828" s="3" t="n"/>
@@ -15386,7 +15404,7 @@
       <c r="C828" s="3" t="n"/>
       <c r="F828" s="3" t="n"/>
       <c r="G828" s="3" t="n"/>
-      <c r="H828" s="14" t="n"/>
+      <c r="H828" s="15" t="n"/>
     </row>
     <row r="829">
       <c r="A829" s="3" t="n"/>
@@ -15394,7 +15412,7 @@
       <c r="C829" s="3" t="n"/>
       <c r="F829" s="3" t="n"/>
       <c r="G829" s="3" t="n"/>
-      <c r="H829" s="14" t="n"/>
+      <c r="H829" s="15" t="n"/>
     </row>
     <row r="830">
       <c r="A830" s="3" t="n"/>
@@ -15402,7 +15420,7 @@
       <c r="C830" s="3" t="n"/>
       <c r="F830" s="3" t="n"/>
       <c r="G830" s="3" t="n"/>
-      <c r="H830" s="14" t="n"/>
+      <c r="H830" s="15" t="n"/>
     </row>
     <row r="831">
       <c r="A831" s="3" t="n"/>
@@ -15410,7 +15428,7 @@
       <c r="C831" s="3" t="n"/>
       <c r="F831" s="3" t="n"/>
       <c r="G831" s="3" t="n"/>
-      <c r="H831" s="14" t="n"/>
+      <c r="H831" s="15" t="n"/>
     </row>
     <row r="832">
       <c r="A832" s="3" t="n"/>
@@ -15418,7 +15436,7 @@
       <c r="C832" s="3" t="n"/>
       <c r="F832" s="3" t="n"/>
       <c r="G832" s="3" t="n"/>
-      <c r="H832" s="14" t="n"/>
+      <c r="H832" s="15" t="n"/>
     </row>
     <row r="833">
       <c r="A833" s="3" t="n"/>
@@ -15426,7 +15444,7 @@
       <c r="C833" s="3" t="n"/>
       <c r="F833" s="3" t="n"/>
       <c r="G833" s="3" t="n"/>
-      <c r="H833" s="14" t="n"/>
+      <c r="H833" s="15" t="n"/>
     </row>
     <row r="834">
       <c r="A834" s="3" t="n"/>
@@ -15434,7 +15452,7 @@
       <c r="C834" s="3" t="n"/>
       <c r="F834" s="3" t="n"/>
       <c r="G834" s="3" t="n"/>
-      <c r="H834" s="14" t="n"/>
+      <c r="H834" s="15" t="n"/>
     </row>
     <row r="835">
       <c r="A835" s="3" t="n"/>
@@ -15442,7 +15460,7 @@
       <c r="C835" s="3" t="n"/>
       <c r="F835" s="3" t="n"/>
       <c r="G835" s="3" t="n"/>
-      <c r="H835" s="14" t="n"/>
+      <c r="H835" s="15" t="n"/>
     </row>
     <row r="836">
       <c r="A836" s="3" t="n"/>
@@ -15450,7 +15468,7 @@
       <c r="C836" s="3" t="n"/>
       <c r="F836" s="3" t="n"/>
       <c r="G836" s="3" t="n"/>
-      <c r="H836" s="14" t="n"/>
+      <c r="H836" s="15" t="n"/>
     </row>
     <row r="837">
       <c r="A837" s="3" t="n"/>
@@ -15458,7 +15476,7 @@
       <c r="C837" s="3" t="n"/>
       <c r="F837" s="3" t="n"/>
       <c r="G837" s="3" t="n"/>
-      <c r="H837" s="14" t="n"/>
+      <c r="H837" s="15" t="n"/>
     </row>
     <row r="838">
       <c r="A838" s="3" t="n"/>
@@ -15466,7 +15484,7 @@
       <c r="C838" s="3" t="n"/>
       <c r="F838" s="3" t="n"/>
       <c r="G838" s="3" t="n"/>
-      <c r="H838" s="14" t="n"/>
+      <c r="H838" s="15" t="n"/>
     </row>
     <row r="839">
       <c r="A839" s="3" t="n"/>
@@ -15474,7 +15492,7 @@
       <c r="C839" s="3" t="n"/>
       <c r="F839" s="3" t="n"/>
       <c r="G839" s="3" t="n"/>
-      <c r="H839" s="14" t="n"/>
+      <c r="H839" s="15" t="n"/>
     </row>
     <row r="840">
       <c r="A840" s="3" t="n"/>
@@ -15482,7 +15500,7 @@
       <c r="C840" s="3" t="n"/>
       <c r="F840" s="3" t="n"/>
       <c r="G840" s="3" t="n"/>
-      <c r="H840" s="14" t="n"/>
+      <c r="H840" s="15" t="n"/>
     </row>
     <row r="841">
       <c r="A841" s="3" t="n"/>
@@ -15490,7 +15508,7 @@
       <c r="C841" s="3" t="n"/>
       <c r="F841" s="3" t="n"/>
       <c r="G841" s="3" t="n"/>
-      <c r="H841" s="14" t="n"/>
+      <c r="H841" s="15" t="n"/>
     </row>
     <row r="842">
       <c r="A842" s="3" t="n"/>
@@ -15498,7 +15516,7 @@
       <c r="C842" s="3" t="n"/>
       <c r="F842" s="3" t="n"/>
       <c r="G842" s="3" t="n"/>
-      <c r="H842" s="14" t="n"/>
+      <c r="H842" s="15" t="n"/>
     </row>
     <row r="843">
       <c r="A843" s="3" t="n"/>
@@ -15506,7 +15524,7 @@
       <c r="C843" s="3" t="n"/>
       <c r="F843" s="3" t="n"/>
       <c r="G843" s="3" t="n"/>
-      <c r="H843" s="14" t="n"/>
+      <c r="H843" s="15" t="n"/>
     </row>
     <row r="844">
       <c r="A844" s="3" t="n"/>
@@ -15514,7 +15532,7 @@
       <c r="C844" s="3" t="n"/>
       <c r="F844" s="3" t="n"/>
       <c r="G844" s="3" t="n"/>
-      <c r="H844" s="14" t="n"/>
+      <c r="H844" s="15" t="n"/>
     </row>
     <row r="845">
       <c r="A845" s="3" t="n"/>
@@ -15522,7 +15540,7 @@
       <c r="C845" s="3" t="n"/>
       <c r="F845" s="3" t="n"/>
       <c r="G845" s="3" t="n"/>
-      <c r="H845" s="14" t="n"/>
+      <c r="H845" s="15" t="n"/>
     </row>
     <row r="846">
       <c r="A846" s="3" t="n"/>
@@ -15530,7 +15548,7 @@
       <c r="C846" s="3" t="n"/>
       <c r="F846" s="3" t="n"/>
       <c r="G846" s="3" t="n"/>
-      <c r="H846" s="14" t="n"/>
+      <c r="H846" s="15" t="n"/>
     </row>
     <row r="847">
       <c r="A847" s="3" t="n"/>
@@ -15538,7 +15556,7 @@
       <c r="C847" s="3" t="n"/>
       <c r="F847" s="3" t="n"/>
       <c r="G847" s="3" t="n"/>
-      <c r="H847" s="14" t="n"/>
+      <c r="H847" s="15" t="n"/>
     </row>
     <row r="848">
       <c r="A848" s="3" t="n"/>
@@ -15546,7 +15564,7 @@
       <c r="C848" s="3" t="n"/>
       <c r="F848" s="3" t="n"/>
       <c r="G848" s="3" t="n"/>
-      <c r="H848" s="14" t="n"/>
+      <c r="H848" s="15" t="n"/>
     </row>
     <row r="849">
       <c r="A849" s="3" t="n"/>
@@ -15554,7 +15572,7 @@
       <c r="C849" s="3" t="n"/>
       <c r="F849" s="3" t="n"/>
       <c r="G849" s="3" t="n"/>
-      <c r="H849" s="14" t="n"/>
+      <c r="H849" s="15" t="n"/>
     </row>
     <row r="850">
       <c r="A850" s="3" t="n"/>
@@ -15562,7 +15580,7 @@
       <c r="C850" s="3" t="n"/>
       <c r="F850" s="3" t="n"/>
       <c r="G850" s="3" t="n"/>
-      <c r="H850" s="14" t="n"/>
+      <c r="H850" s="15" t="n"/>
     </row>
     <row r="851">
       <c r="A851" s="3" t="n"/>
@@ -15570,7 +15588,7 @@
       <c r="C851" s="3" t="n"/>
       <c r="F851" s="3" t="n"/>
       <c r="G851" s="3" t="n"/>
-      <c r="H851" s="14" t="n"/>
+      <c r="H851" s="15" t="n"/>
     </row>
     <row r="852">
       <c r="A852" s="3" t="n"/>
@@ -15578,7 +15596,7 @@
       <c r="C852" s="3" t="n"/>
       <c r="F852" s="3" t="n"/>
       <c r="G852" s="3" t="n"/>
-      <c r="H852" s="14" t="n"/>
+      <c r="H852" s="15" t="n"/>
     </row>
     <row r="853">
       <c r="A853" s="3" t="n"/>
@@ -15586,7 +15604,7 @@
       <c r="C853" s="3" t="n"/>
       <c r="F853" s="3" t="n"/>
       <c r="G853" s="3" t="n"/>
-      <c r="H853" s="14" t="n"/>
+      <c r="H853" s="15" t="n"/>
     </row>
     <row r="854">
       <c r="A854" s="3" t="n"/>
@@ -15594,7 +15612,7 @@
       <c r="C854" s="3" t="n"/>
       <c r="F854" s="3" t="n"/>
       <c r="G854" s="3" t="n"/>
-      <c r="H854" s="14" t="n"/>
+      <c r="H854" s="15" t="n"/>
     </row>
     <row r="855">
       <c r="A855" s="3" t="n"/>
@@ -15602,7 +15620,7 @@
       <c r="C855" s="3" t="n"/>
       <c r="F855" s="3" t="n"/>
       <c r="G855" s="3" t="n"/>
-      <c r="H855" s="14" t="n"/>
+      <c r="H855" s="15" t="n"/>
     </row>
     <row r="856">
       <c r="A856" s="3" t="n"/>
@@ -15610,7 +15628,7 @@
       <c r="C856" s="3" t="n"/>
       <c r="F856" s="3" t="n"/>
       <c r="G856" s="3" t="n"/>
-      <c r="H856" s="14" t="n"/>
+      <c r="H856" s="15" t="n"/>
     </row>
     <row r="857">
       <c r="A857" s="3" t="n"/>
@@ -15618,7 +15636,7 @@
       <c r="C857" s="3" t="n"/>
       <c r="F857" s="3" t="n"/>
       <c r="G857" s="3" t="n"/>
-      <c r="H857" s="14" t="n"/>
+      <c r="H857" s="15" t="n"/>
     </row>
     <row r="858">
       <c r="A858" s="3" t="n"/>
@@ -15626,7 +15644,7 @@
       <c r="C858" s="3" t="n"/>
       <c r="F858" s="3" t="n"/>
       <c r="G858" s="3" t="n"/>
-      <c r="H858" s="14" t="n"/>
+      <c r="H858" s="15" t="n"/>
     </row>
     <row r="859">
       <c r="A859" s="3" t="n"/>
@@ -15634,7 +15652,7 @@
       <c r="C859" s="3" t="n"/>
       <c r="F859" s="3" t="n"/>
       <c r="G859" s="3" t="n"/>
-      <c r="H859" s="14" t="n"/>
+      <c r="H859" s="15" t="n"/>
     </row>
     <row r="860">
       <c r="A860" s="3" t="n"/>
@@ -15642,7 +15660,7 @@
       <c r="C860" s="3" t="n"/>
       <c r="F860" s="3" t="n"/>
       <c r="G860" s="3" t="n"/>
-      <c r="H860" s="14" t="n"/>
+      <c r="H860" s="15" t="n"/>
     </row>
     <row r="861">
       <c r="A861" s="3" t="n"/>
@@ -15650,7 +15668,7 @@
       <c r="C861" s="3" t="n"/>
       <c r="F861" s="3" t="n"/>
       <c r="G861" s="3" t="n"/>
-      <c r="H861" s="14" t="n"/>
+      <c r="H861" s="15" t="n"/>
     </row>
     <row r="862">
       <c r="A862" s="3" t="n"/>
@@ -15658,7 +15676,7 @@
       <c r="C862" s="3" t="n"/>
       <c r="F862" s="3" t="n"/>
       <c r="G862" s="3" t="n"/>
-      <c r="H862" s="14" t="n"/>
+      <c r="H862" s="15" t="n"/>
     </row>
     <row r="863">
       <c r="A863" s="3" t="n"/>
@@ -15666,7 +15684,7 @@
       <c r="C863" s="3" t="n"/>
       <c r="F863" s="3" t="n"/>
       <c r="G863" s="3" t="n"/>
-      <c r="H863" s="14" t="n"/>
+      <c r="H863" s="15" t="n"/>
     </row>
     <row r="864">
       <c r="A864" s="3" t="n"/>
@@ -15674,7 +15692,7 @@
       <c r="C864" s="3" t="n"/>
       <c r="F864" s="3" t="n"/>
       <c r="G864" s="3" t="n"/>
-      <c r="H864" s="14" t="n"/>
+      <c r="H864" s="15" t="n"/>
     </row>
     <row r="865">
       <c r="A865" s="3" t="n"/>
@@ -15682,7 +15700,7 @@
       <c r="C865" s="3" t="n"/>
       <c r="F865" s="3" t="n"/>
       <c r="G865" s="3" t="n"/>
-      <c r="H865" s="14" t="n"/>
+      <c r="H865" s="15" t="n"/>
     </row>
     <row r="866">
       <c r="A866" s="3" t="n"/>
@@ -15690,7 +15708,7 @@
       <c r="C866" s="3" t="n"/>
       <c r="F866" s="3" t="n"/>
       <c r="G866" s="3" t="n"/>
-      <c r="H866" s="14" t="n"/>
+      <c r="H866" s="15" t="n"/>
     </row>
     <row r="867">
       <c r="A867" s="3" t="n"/>
@@ -15698,7 +15716,7 @@
       <c r="C867" s="3" t="n"/>
       <c r="F867" s="3" t="n"/>
       <c r="G867" s="3" t="n"/>
-      <c r="H867" s="14" t="n"/>
+      <c r="H867" s="15" t="n"/>
     </row>
     <row r="868">
       <c r="A868" s="3" t="n"/>
@@ -15706,7 +15724,7 @@
       <c r="C868" s="3" t="n"/>
       <c r="F868" s="3" t="n"/>
       <c r="G868" s="3" t="n"/>
-      <c r="H868" s="14" t="n"/>
+      <c r="H868" s="15" t="n"/>
     </row>
     <row r="869">
       <c r="A869" s="3" t="n"/>
@@ -15714,7 +15732,7 @@
       <c r="C869" s="3" t="n"/>
       <c r="F869" s="3" t="n"/>
       <c r="G869" s="3" t="n"/>
-      <c r="H869" s="14" t="n"/>
+      <c r="H869" s="15" t="n"/>
     </row>
     <row r="870">
       <c r="A870" s="3" t="n"/>
@@ -15722,7 +15740,7 @@
       <c r="C870" s="3" t="n"/>
       <c r="F870" s="3" t="n"/>
       <c r="G870" s="3" t="n"/>
-      <c r="H870" s="14" t="n"/>
+      <c r="H870" s="15" t="n"/>
     </row>
     <row r="871">
       <c r="A871" s="3" t="n"/>
@@ -15730,7 +15748,7 @@
       <c r="C871" s="3" t="n"/>
       <c r="F871" s="3" t="n"/>
       <c r="G871" s="3" t="n"/>
-      <c r="H871" s="14" t="n"/>
+      <c r="H871" s="15" t="n"/>
     </row>
     <row r="872">
       <c r="A872" s="3" t="n"/>
@@ -15738,7 +15756,7 @@
       <c r="C872" s="3" t="n"/>
       <c r="F872" s="3" t="n"/>
       <c r="G872" s="3" t="n"/>
-      <c r="H872" s="14" t="n"/>
+      <c r="H872" s="15" t="n"/>
     </row>
     <row r="873">
       <c r="A873" s="3" t="n"/>
@@ -15746,7 +15764,7 @@
       <c r="C873" s="3" t="n"/>
       <c r="F873" s="3" t="n"/>
       <c r="G873" s="3" t="n"/>
-      <c r="H873" s="14" t="n"/>
+      <c r="H873" s="15" t="n"/>
     </row>
     <row r="874">
       <c r="A874" s="3" t="n"/>
@@ -15754,7 +15772,7 @@
       <c r="C874" s="3" t="n"/>
       <c r="F874" s="3" t="n"/>
       <c r="G874" s="3" t="n"/>
-      <c r="H874" s="14" t="n"/>
+      <c r="H874" s="15" t="n"/>
     </row>
     <row r="875">
       <c r="A875" s="3" t="n"/>
@@ -15762,7 +15780,7 @@
       <c r="C875" s="3" t="n"/>
       <c r="F875" s="3" t="n"/>
       <c r="G875" s="3" t="n"/>
-      <c r="H875" s="14" t="n"/>
+      <c r="H875" s="15" t="n"/>
     </row>
     <row r="876">
       <c r="A876" s="3" t="n"/>
@@ -15770,7 +15788,7 @@
       <c r="C876" s="3" t="n"/>
       <c r="F876" s="3" t="n"/>
       <c r="G876" s="3" t="n"/>
-      <c r="H876" s="14" t="n"/>
+      <c r="H876" s="15" t="n"/>
     </row>
     <row r="877">
       <c r="A877" s="3" t="n"/>
@@ -15778,7 +15796,7 @@
       <c r="C877" s="3" t="n"/>
       <c r="F877" s="3" t="n"/>
       <c r="G877" s="3" t="n"/>
-      <c r="H877" s="14" t="n"/>
+      <c r="H877" s="15" t="n"/>
     </row>
     <row r="878">
       <c r="A878" s="3" t="n"/>
@@ -15786,7 +15804,7 @@
       <c r="C878" s="3" t="n"/>
       <c r="F878" s="3" t="n"/>
       <c r="G878" s="3" t="n"/>
-      <c r="H878" s="14" t="n"/>
+      <c r="H878" s="15" t="n"/>
     </row>
     <row r="879">
       <c r="A879" s="3" t="n"/>
@@ -15794,7 +15812,7 @@
       <c r="C879" s="3" t="n"/>
       <c r="F879" s="3" t="n"/>
       <c r="G879" s="3" t="n"/>
-      <c r="H879" s="14" t="n"/>
+      <c r="H879" s="15" t="n"/>
     </row>
     <row r="880">
       <c r="A880" s="3" t="n"/>
@@ -15802,7 +15820,7 @@
       <c r="C880" s="3" t="n"/>
       <c r="F880" s="3" t="n"/>
       <c r="G880" s="3" t="n"/>
-      <c r="H880" s="14" t="n"/>
+      <c r="H880" s="15" t="n"/>
     </row>
     <row r="881">
       <c r="A881" s="3" t="n"/>
@@ -15810,7 +15828,7 @@
       <c r="C881" s="3" t="n"/>
       <c r="F881" s="3" t="n"/>
       <c r="G881" s="3" t="n"/>
-      <c r="H881" s="14" t="n"/>
+      <c r="H881" s="15" t="n"/>
     </row>
     <row r="882">
       <c r="A882" s="3" t="n"/>
@@ -15818,7 +15836,7 @@
       <c r="C882" s="3" t="n"/>
       <c r="F882" s="3" t="n"/>
       <c r="G882" s="3" t="n"/>
-      <c r="H882" s="14" t="n"/>
+      <c r="H882" s="15" t="n"/>
     </row>
     <row r="883">
       <c r="A883" s="3" t="n"/>
@@ -15826,7 +15844,7 @@
       <c r="C883" s="3" t="n"/>
       <c r="F883" s="3" t="n"/>
       <c r="G883" s="3" t="n"/>
-      <c r="H883" s="14" t="n"/>
+      <c r="H883" s="15" t="n"/>
     </row>
     <row r="884">
       <c r="A884" s="3" t="n"/>
@@ -15834,7 +15852,7 @@
       <c r="C884" s="3" t="n"/>
       <c r="F884" s="3" t="n"/>
       <c r="G884" s="3" t="n"/>
-      <c r="H884" s="14" t="n"/>
+      <c r="H884" s="15" t="n"/>
     </row>
     <row r="885">
       <c r="A885" s="3" t="n"/>
@@ -15842,7 +15860,7 @@
       <c r="C885" s="3" t="n"/>
       <c r="F885" s="3" t="n"/>
       <c r="G885" s="3" t="n"/>
-      <c r="H885" s="14" t="n"/>
+      <c r="H885" s="15" t="n"/>
     </row>
     <row r="886">
       <c r="A886" s="3" t="n"/>
@@ -15850,7 +15868,7 @@
       <c r="C886" s="3" t="n"/>
       <c r="F886" s="3" t="n"/>
       <c r="G886" s="3" t="n"/>
-      <c r="H886" s="14" t="n"/>
+      <c r="H886" s="15" t="n"/>
     </row>
     <row r="887">
       <c r="A887" s="3" t="n"/>
@@ -15858,7 +15876,7 @@
       <c r="C887" s="3" t="n"/>
       <c r="F887" s="3" t="n"/>
       <c r="G887" s="3" t="n"/>
-      <c r="H887" s="14" t="n"/>
+      <c r="H887" s="15" t="n"/>
     </row>
     <row r="888">
       <c r="A888" s="3" t="n"/>
@@ -15866,7 +15884,7 @@
       <c r="C888" s="3" t="n"/>
       <c r="F888" s="3" t="n"/>
       <c r="G888" s="3" t="n"/>
-      <c r="H888" s="14" t="n"/>
+      <c r="H888" s="15" t="n"/>
     </row>
     <row r="889">
       <c r="A889" s="3" t="n"/>
@@ -15874,7 +15892,7 @@
       <c r="C889" s="3" t="n"/>
       <c r="F889" s="3" t="n"/>
       <c r="G889" s="3" t="n"/>
-      <c r="H889" s="14" t="n"/>
+      <c r="H889" s="15" t="n"/>
     </row>
     <row r="890">
       <c r="A890" s="3" t="n"/>
@@ -15882,7 +15900,7 @@
       <c r="C890" s="3" t="n"/>
       <c r="F890" s="3" t="n"/>
       <c r="G890" s="3" t="n"/>
-      <c r="H890" s="14" t="n"/>
+      <c r="H890" s="15" t="n"/>
     </row>
     <row r="891">
       <c r="A891" s="3" t="n"/>
@@ -15890,7 +15908,7 @@
       <c r="C891" s="3" t="n"/>
       <c r="F891" s="3" t="n"/>
       <c r="G891" s="3" t="n"/>
-      <c r="H891" s="14" t="n"/>
+      <c r="H891" s="15" t="n"/>
     </row>
     <row r="892">
       <c r="A892" s="3" t="n"/>
@@ -15898,7 +15916,7 @@
       <c r="C892" s="3" t="n"/>
       <c r="F892" s="3" t="n"/>
       <c r="G892" s="3" t="n"/>
-      <c r="H892" s="14" t="n"/>
+      <c r="H892" s="15" t="n"/>
     </row>
     <row r="893">
       <c r="A893" s="3" t="n"/>
@@ -15906,7 +15924,7 @@
       <c r="C893" s="3" t="n"/>
       <c r="F893" s="3" t="n"/>
       <c r="G893" s="3" t="n"/>
-      <c r="H893" s="14" t="n"/>
+      <c r="H893" s="15" t="n"/>
     </row>
     <row r="894">
       <c r="A894" s="3" t="n"/>
@@ -15914,7 +15932,7 @@
       <c r="C894" s="3" t="n"/>
       <c r="F894" s="3" t="n"/>
       <c r="G894" s="3" t="n"/>
-      <c r="H894" s="14" t="n"/>
+      <c r="H894" s="15" t="n"/>
     </row>
     <row r="895">
       <c r="A895" s="3" t="n"/>
@@ -15922,7 +15940,7 @@
       <c r="C895" s="3" t="n"/>
       <c r="F895" s="3" t="n"/>
       <c r="G895" s="3" t="n"/>
-      <c r="H895" s="14" t="n"/>
+      <c r="H895" s="15" t="n"/>
     </row>
     <row r="896">
       <c r="A896" s="3" t="n"/>
@@ -15930,7 +15948,7 @@
       <c r="C896" s="3" t="n"/>
       <c r="F896" s="3" t="n"/>
       <c r="G896" s="3" t="n"/>
-      <c r="H896" s="14" t="n"/>
+      <c r="H896" s="15" t="n"/>
     </row>
     <row r="897">
       <c r="A897" s="3" t="n"/>
@@ -15938,7 +15956,7 @@
       <c r="C897" s="3" t="n"/>
       <c r="F897" s="3" t="n"/>
       <c r="G897" s="3" t="n"/>
-      <c r="H897" s="14" t="n"/>
+      <c r="H897" s="15" t="n"/>
     </row>
     <row r="898">
       <c r="A898" s="3" t="n"/>
@@ -15946,7 +15964,7 @@
       <c r="C898" s="3" t="n"/>
       <c r="F898" s="3" t="n"/>
       <c r="G898" s="3" t="n"/>
-      <c r="H898" s="14" t="n"/>
+      <c r="H898" s="15" t="n"/>
     </row>
     <row r="899">
       <c r="A899" s="3" t="n"/>
@@ -15954,7 +15972,7 @@
       <c r="C899" s="3" t="n"/>
       <c r="F899" s="3" t="n"/>
       <c r="G899" s="3" t="n"/>
-      <c r="H899" s="14" t="n"/>
+      <c r="H899" s="15" t="n"/>
     </row>
     <row r="900">
       <c r="A900" s="3" t="n"/>
@@ -15962,7 +15980,7 @@
       <c r="C900" s="3" t="n"/>
       <c r="F900" s="3" t="n"/>
       <c r="G900" s="3" t="n"/>
-      <c r="H900" s="14" t="n"/>
+      <c r="H900" s="15" t="n"/>
     </row>
     <row r="901">
       <c r="A901" s="3" t="n"/>
@@ -15970,7 +15988,7 @@
       <c r="C901" s="3" t="n"/>
       <c r="F901" s="3" t="n"/>
       <c r="G901" s="3" t="n"/>
-      <c r="H901" s="14" t="n"/>
+      <c r="H901" s="15" t="n"/>
     </row>
     <row r="902">
       <c r="A902" s="3" t="n"/>
@@ -15978,7 +15996,7 @@
       <c r="C902" s="3" t="n"/>
       <c r="F902" s="3" t="n"/>
       <c r="G902" s="3" t="n"/>
-      <c r="H902" s="14" t="n"/>
+      <c r="H902" s="15" t="n"/>
     </row>
     <row r="903">
       <c r="A903" s="3" t="n"/>
@@ -15986,7 +16004,7 @@
       <c r="C903" s="3" t="n"/>
       <c r="F903" s="3" t="n"/>
       <c r="G903" s="3" t="n"/>
-      <c r="H903" s="14" t="n"/>
+      <c r="H903" s="15" t="n"/>
     </row>
     <row r="904">
       <c r="A904" s="3" t="n"/>
@@ -15994,7 +16012,7 @@
       <c r="C904" s="3" t="n"/>
       <c r="F904" s="3" t="n"/>
       <c r="G904" s="3" t="n"/>
-      <c r="H904" s="14" t="n"/>
+      <c r="H904" s="15" t="n"/>
     </row>
     <row r="905">
       <c r="A905" s="3" t="n"/>
@@ -16002,7 +16020,7 @@
       <c r="C905" s="3" t="n"/>
       <c r="F905" s="3" t="n"/>
       <c r="G905" s="3" t="n"/>
-      <c r="H905" s="14" t="n"/>
+      <c r="H905" s="15" t="n"/>
     </row>
     <row r="906">
       <c r="A906" s="3" t="n"/>
@@ -16010,7 +16028,7 @@
       <c r="C906" s="3" t="n"/>
       <c r="F906" s="3" t="n"/>
       <c r="G906" s="3" t="n"/>
-      <c r="H906" s="14" t="n"/>
+      <c r="H906" s="15" t="n"/>
     </row>
     <row r="907">
       <c r="A907" s="3" t="n"/>
@@ -16018,7 +16036,7 @@
       <c r="C907" s="3" t="n"/>
       <c r="F907" s="3" t="n"/>
       <c r="G907" s="3" t="n"/>
-      <c r="H907" s="14" t="n"/>
+      <c r="H907" s="15" t="n"/>
     </row>
     <row r="908">
       <c r="A908" s="3" t="n"/>
@@ -16026,7 +16044,7 @@
       <c r="C908" s="3" t="n"/>
       <c r="F908" s="3" t="n"/>
       <c r="G908" s="3" t="n"/>
-      <c r="H908" s="14" t="n"/>
+      <c r="H908" s="15" t="n"/>
     </row>
     <row r="909">
       <c r="A909" s="3" t="n"/>
@@ -16034,7 +16052,7 @@
       <c r="C909" s="3" t="n"/>
       <c r="F909" s="3" t="n"/>
       <c r="G909" s="3" t="n"/>
-      <c r="H909" s="14" t="n"/>
+      <c r="H909" s="15" t="n"/>
     </row>
     <row r="910">
       <c r="A910" s="3" t="n"/>
@@ -16042,7 +16060,7 @@
       <c r="C910" s="3" t="n"/>
       <c r="F910" s="3" t="n"/>
       <c r="G910" s="3" t="n"/>
-      <c r="H910" s="14" t="n"/>
+      <c r="H910" s="15" t="n"/>
     </row>
     <row r="911">
       <c r="A911" s="3" t="n"/>
@@ -16050,7 +16068,7 @@
       <c r="C911" s="3" t="n"/>
       <c r="F911" s="3" t="n"/>
       <c r="G911" s="3" t="n"/>
-      <c r="H911" s="14" t="n"/>
+      <c r="H911" s="15" t="n"/>
     </row>
     <row r="912">
       <c r="A912" s="3" t="n"/>
@@ -16058,7 +16076,7 @@
       <c r="C912" s="3" t="n"/>
       <c r="F912" s="3" t="n"/>
       <c r="G912" s="3" t="n"/>
-      <c r="H912" s="14" t="n"/>
+      <c r="H912" s="15" t="n"/>
     </row>
     <row r="913">
       <c r="A913" s="3" t="n"/>
@@ -16066,7 +16084,7 @@
       <c r="C913" s="3" t="n"/>
       <c r="F913" s="3" t="n"/>
       <c r="G913" s="3" t="n"/>
-      <c r="H913" s="14" t="n"/>
+      <c r="H913" s="15" t="n"/>
     </row>
     <row r="914">
       <c r="A914" s="3" t="n"/>
@@ -16074,7 +16092,7 @@
       <c r="C914" s="3" t="n"/>
       <c r="F914" s="3" t="n"/>
       <c r="G914" s="3" t="n"/>
-      <c r="H914" s="14" t="n"/>
+      <c r="H914" s="15" t="n"/>
     </row>
     <row r="915">
       <c r="A915" s="3" t="n"/>
@@ -16082,7 +16100,7 @@
       <c r="C915" s="3" t="n"/>
       <c r="F915" s="3" t="n"/>
       <c r="G915" s="3" t="n"/>
-      <c r="H915" s="14" t="n"/>
+      <c r="H915" s="15" t="n"/>
     </row>
     <row r="916">
       <c r="A916" s="3" t="n"/>
@@ -16090,7 +16108,7 @@
       <c r="C916" s="3" t="n"/>
       <c r="F916" s="3" t="n"/>
       <c r="G916" s="3" t="n"/>
-      <c r="H916" s="14" t="n"/>
+      <c r="H916" s="15" t="n"/>
     </row>
     <row r="917">
       <c r="A917" s="3" t="n"/>
@@ -16098,7 +16116,7 @@
       <c r="C917" s="3" t="n"/>
       <c r="F917" s="3" t="n"/>
       <c r="G917" s="3" t="n"/>
-      <c r="H917" s="14" t="n"/>
+      <c r="H917" s="15" t="n"/>
     </row>
     <row r="918">
       <c r="A918" s="3" t="n"/>
@@ -16106,7 +16124,7 @@
       <c r="C918" s="3" t="n"/>
       <c r="F918" s="3" t="n"/>
       <c r="G918" s="3" t="n"/>
-      <c r="H918" s="14" t="n"/>
+      <c r="H918" s="15" t="n"/>
     </row>
     <row r="919">
       <c r="A919" s="3" t="n"/>
@@ -16114,7 +16132,7 @@
       <c r="C919" s="3" t="n"/>
       <c r="F919" s="3" t="n"/>
       <c r="G919" s="3" t="n"/>
-      <c r="H919" s="14" t="n"/>
+      <c r="H919" s="15" t="n"/>
     </row>
     <row r="920">
       <c r="A920" s="3" t="n"/>
@@ -16122,7 +16140,7 @@
       <c r="C920" s="3" t="n"/>
       <c r="F920" s="3" t="n"/>
       <c r="G920" s="3" t="n"/>
-      <c r="H920" s="14" t="n"/>
+      <c r="H920" s="15" t="n"/>
     </row>
     <row r="921">
       <c r="A921" s="3" t="n"/>
@@ -16130,7 +16148,7 @@
       <c r="C921" s="3" t="n"/>
       <c r="F921" s="3" t="n"/>
       <c r="G921" s="3" t="n"/>
-      <c r="H921" s="14" t="n"/>
+      <c r="H921" s="15" t="n"/>
     </row>
     <row r="922">
       <c r="A922" s="3" t="n"/>
@@ -16138,7 +16156,7 @@
       <c r="C922" s="3" t="n"/>
       <c r="F922" s="3" t="n"/>
       <c r="G922" s="3" t="n"/>
-      <c r="H922" s="14" t="n"/>
+      <c r="H922" s="15" t="n"/>
     </row>
     <row r="923">
       <c r="A923" s="3" t="n"/>
@@ -16146,7 +16164,7 @@
       <c r="C923" s="3" t="n"/>
       <c r="F923" s="3" t="n"/>
       <c r="G923" s="3" t="n"/>
-      <c r="H923" s="14" t="n"/>
+      <c r="H923" s="15" t="n"/>
     </row>
     <row r="924">
       <c r="A924" s="3" t="n"/>
@@ -16154,7 +16172,7 @@
       <c r="C924" s="3" t="n"/>
       <c r="F924" s="3" t="n"/>
       <c r="G924" s="3" t="n"/>
-      <c r="H924" s="14" t="n"/>
+      <c r="H924" s="15" t="n"/>
     </row>
     <row r="925">
       <c r="A925" s="3" t="n"/>
@@ -16162,7 +16180,7 @@
       <c r="C925" s="3" t="n"/>
       <c r="F925" s="3" t="n"/>
       <c r="G925" s="3" t="n"/>
-      <c r="H925" s="14" t="n"/>
+      <c r="H925" s="15" t="n"/>
     </row>
     <row r="926">
       <c r="A926" s="3" t="n"/>
@@ -16170,7 +16188,7 @@
       <c r="C926" s="3" t="n"/>
       <c r="F926" s="3" t="n"/>
       <c r="G926" s="3" t="n"/>
-      <c r="H926" s="14" t="n"/>
+      <c r="H926" s="15" t="n"/>
     </row>
     <row r="927">
       <c r="A927" s="3" t="n"/>
@@ -16178,7 +16196,7 @@
       <c r="C927" s="3" t="n"/>
       <c r="F927" s="3" t="n"/>
       <c r="G927" s="3" t="n"/>
-      <c r="H927" s="14" t="n"/>
+      <c r="H927" s="15" t="n"/>
     </row>
     <row r="928">
       <c r="A928" s="3" t="n"/>
@@ -16186,7 +16204,7 @@
       <c r="C928" s="3" t="n"/>
       <c r="F928" s="3" t="n"/>
       <c r="G928" s="3" t="n"/>
-      <c r="H928" s="14" t="n"/>
+      <c r="H928" s="15" t="n"/>
     </row>
     <row r="929">
       <c r="A929" s="3" t="n"/>
@@ -16194,7 +16212,7 @@
       <c r="C929" s="3" t="n"/>
       <c r="F929" s="3" t="n"/>
       <c r="G929" s="3" t="n"/>
-      <c r="H929" s="14" t="n"/>
+      <c r="H929" s="15" t="n"/>
     </row>
     <row r="930">
       <c r="A930" s="3" t="n"/>
@@ -16202,7 +16220,7 @@
       <c r="C930" s="3" t="n"/>
       <c r="F930" s="3" t="n"/>
       <c r="G930" s="3" t="n"/>
-      <c r="H930" s="14" t="n"/>
+      <c r="H930" s="15" t="n"/>
     </row>
     <row r="931">
       <c r="A931" s="3" t="n"/>
@@ -16210,7 +16228,7 @@
       <c r="C931" s="3" t="n"/>
       <c r="F931" s="3" t="n"/>
       <c r="G931" s="3" t="n"/>
-      <c r="H931" s="14" t="n"/>
+      <c r="H931" s="15" t="n"/>
     </row>
     <row r="932">
       <c r="A932" s="3" t="n"/>
@@ -16218,7 +16236,7 @@
       <c r="C932" s="3" t="n"/>
       <c r="F932" s="3" t="n"/>
       <c r="G932" s="3" t="n"/>
-      <c r="H932" s="14" t="n"/>
+      <c r="H932" s="15" t="n"/>
     </row>
     <row r="933">
       <c r="A933" s="3" t="n"/>
@@ -16226,7 +16244,7 @@
       <c r="C933" s="3" t="n"/>
       <c r="F933" s="3" t="n"/>
       <c r="G933" s="3" t="n"/>
-      <c r="H933" s="14" t="n"/>
+      <c r="H933" s="15" t="n"/>
     </row>
     <row r="934">
       <c r="A934" s="3" t="n"/>
@@ -16234,7 +16252,7 @@
       <c r="C934" s="3" t="n"/>
       <c r="F934" s="3" t="n"/>
       <c r="G934" s="3" t="n"/>
-      <c r="H934" s="14" t="n"/>
+      <c r="H934" s="15" t="n"/>
     </row>
     <row r="935">
       <c r="A935" s="3" t="n"/>
@@ -16242,7 +16260,7 @@
       <c r="C935" s="3" t="n"/>
       <c r="F935" s="3" t="n"/>
       <c r="G935" s="3" t="n"/>
-      <c r="H935" s="14" t="n"/>
+      <c r="H935" s="15" t="n"/>
     </row>
     <row r="936">
       <c r="A936" s="3" t="n"/>
@@ -16250,7 +16268,7 @@
       <c r="C936" s="3" t="n"/>
       <c r="F936" s="3" t="n"/>
       <c r="G936" s="3" t="n"/>
-      <c r="H936" s="14" t="n"/>
+      <c r="H936" s="15" t="n"/>
     </row>
     <row r="937">
       <c r="A937" s="3" t="n"/>
@@ -16258,7 +16276,7 @@
       <c r="C937" s="3" t="n"/>
       <c r="F937" s="3" t="n"/>
       <c r="G937" s="3" t="n"/>
-      <c r="H937" s="14" t="n"/>
+      <c r="H937" s="15" t="n"/>
     </row>
     <row r="938">
       <c r="A938" s="3" t="n"/>
@@ -16266,7 +16284,7 @@
       <c r="C938" s="3" t="n"/>
       <c r="F938" s="3" t="n"/>
       <c r="G938" s="3" t="n"/>
-      <c r="H938" s="14" t="n"/>
+      <c r="H938" s="15" t="n"/>
     </row>
     <row r="939">
       <c r="A939" s="3" t="n"/>
@@ -16274,7 +16292,7 @@
       <c r="C939" s="3" t="n"/>
       <c r="F939" s="3" t="n"/>
       <c r="G939" s="3" t="n"/>
-      <c r="H939" s="14" t="n"/>
+      <c r="H939" s="15" t="n"/>
     </row>
     <row r="940">
       <c r="A940" s="3" t="n"/>
@@ -16282,7 +16300,7 @@
       <c r="C940" s="3" t="n"/>
       <c r="F940" s="3" t="n"/>
       <c r="G940" s="3" t="n"/>
-      <c r="H940" s="14" t="n"/>
+      <c r="H940" s="15" t="n"/>
     </row>
     <row r="941">
       <c r="A941" s="3" t="n"/>
@@ -16290,7 +16308,7 @@
       <c r="C941" s="3" t="n"/>
       <c r="F941" s="3" t="n"/>
       <c r="G941" s="3" t="n"/>
-      <c r="H941" s="14" t="n"/>
+      <c r="H941" s="15" t="n"/>
     </row>
     <row r="942">
       <c r="A942" s="3" t="n"/>
@@ -16298,7 +16316,7 @@
       <c r="C942" s="3" t="n"/>
       <c r="F942" s="3" t="n"/>
       <c r="G942" s="3" t="n"/>
-      <c r="H942" s="14" t="n"/>
+      <c r="H942" s="15" t="n"/>
     </row>
     <row r="943">
       <c r="A943" s="3" t="n"/>
@@ -16306,7 +16324,7 @@
       <c r="C943" s="3" t="n"/>
       <c r="F943" s="3" t="n"/>
       <c r="G943" s="3" t="n"/>
-      <c r="H943" s="14" t="n"/>
+      <c r="H943" s="15" t="n"/>
     </row>
     <row r="944">
       <c r="A944" s="3" t="n"/>
@@ -16314,7 +16332,7 @@
       <c r="C944" s="3" t="n"/>
       <c r="F944" s="3" t="n"/>
       <c r="G944" s="3" t="n"/>
-      <c r="H944" s="14" t="n"/>
+      <c r="H944" s="15" t="n"/>
     </row>
     <row r="945">
       <c r="A945" s="3" t="n"/>
@@ -16322,7 +16340,7 @@
       <c r="C945" s="3" t="n"/>
       <c r="F945" s="3" t="n"/>
       <c r="G945" s="3" t="n"/>
-      <c r="H945" s="14" t="n"/>
+      <c r="H945" s="15" t="n"/>
     </row>
     <row r="946">
       <c r="A946" s="3" t="n"/>
@@ -16330,7 +16348,7 @@
       <c r="C946" s="3" t="n"/>
       <c r="F946" s="3" t="n"/>
       <c r="G946" s="3" t="n"/>
-      <c r="H946" s="14" t="n"/>
+      <c r="H946" s="15" t="n"/>
     </row>
     <row r="947">
       <c r="A947" s="3" t="n"/>
@@ -16338,7 +16356,7 @@
       <c r="C947" s="3" t="n"/>
       <c r="F947" s="3" t="n"/>
       <c r="G947" s="3" t="n"/>
-      <c r="H947" s="14" t="n"/>
+      <c r="H947" s="15" t="n"/>
     </row>
     <row r="948">
       <c r="A948" s="3" t="n"/>
@@ -16346,7 +16364,7 @@
       <c r="C948" s="3" t="n"/>
       <c r="F948" s="3" t="n"/>
       <c r="G948" s="3" t="n"/>
-      <c r="H948" s="14" t="n"/>
+      <c r="H948" s="15" t="n"/>
     </row>
     <row r="949">
       <c r="A949" s="3" t="n"/>
@@ -16354,7 +16372,7 @@
       <c r="C949" s="3" t="n"/>
       <c r="F949" s="3" t="n"/>
       <c r="G949" s="3" t="n"/>
-      <c r="H949" s="14" t="n"/>
+      <c r="H949" s="15" t="n"/>
     </row>
     <row r="950">
       <c r="A950" s="3" t="n"/>
@@ -16362,7 +16380,7 @@
       <c r="C950" s="3" t="n"/>
       <c r="F950" s="3" t="n"/>
       <c r="G950" s="3" t="n"/>
-      <c r="H950" s="14" t="n"/>
+      <c r="H950" s="15" t="n"/>
     </row>
     <row r="951">
       <c r="A951" s="3" t="n"/>
@@ -16370,7 +16388,7 @@
       <c r="C951" s="3" t="n"/>
       <c r="F951" s="3" t="n"/>
       <c r="G951" s="3" t="n"/>
-      <c r="H951" s="14" t="n"/>
+      <c r="H951" s="15" t="n"/>
     </row>
     <row r="952">
       <c r="A952" s="3" t="n"/>
@@ -16378,7 +16396,7 @@
       <c r="C952" s="3" t="n"/>
       <c r="F952" s="3" t="n"/>
       <c r="G952" s="3" t="n"/>
-      <c r="H952" s="14" t="n"/>
+      <c r="H952" s="15" t="n"/>
     </row>
     <row r="953">
       <c r="A953" s="3" t="n"/>
@@ -16386,7 +16404,7 @@
       <c r="C953" s="3" t="n"/>
       <c r="F953" s="3" t="n"/>
       <c r="G953" s="3" t="n"/>
-      <c r="H953" s="14" t="n"/>
+      <c r="H953" s="15" t="n"/>
     </row>
     <row r="954">
       <c r="A954" s="3" t="n"/>
@@ -16394,7 +16412,7 @@
       <c r="C954" s="3" t="n"/>
       <c r="F954" s="3" t="n"/>
       <c r="G954" s="3" t="n"/>
-      <c r="H954" s="14" t="n"/>
+      <c r="H954" s="15" t="n"/>
     </row>
     <row r="955">
       <c r="A955" s="3" t="n"/>
@@ -16402,7 +16420,7 @@
       <c r="C955" s="3" t="n"/>
       <c r="F955" s="3" t="n"/>
       <c r="G955" s="3" t="n"/>
-      <c r="H955" s="14" t="n"/>
+      <c r="H955" s="15" t="n"/>
     </row>
     <row r="956">
       <c r="A956" s="3" t="n"/>
@@ -16410,7 +16428,7 @@
       <c r="C956" s="3" t="n"/>
       <c r="F956" s="3" t="n"/>
       <c r="G956" s="3" t="n"/>
-      <c r="H956" s="14" t="n"/>
+      <c r="H956" s="15" t="n"/>
     </row>
     <row r="957">
       <c r="A957" s="3" t="n"/>
@@ -16418,7 +16436,7 @@
       <c r="C957" s="3" t="n"/>
       <c r="F957" s="3" t="n"/>
       <c r="G957" s="3" t="n"/>
-      <c r="H957" s="14" t="n"/>
+      <c r="H957" s="15" t="n"/>
     </row>
     <row r="958">
       <c r="A958" s="3" t="n"/>
@@ -16426,7 +16444,7 @@
       <c r="C958" s="3" t="n"/>
       <c r="F958" s="3" t="n"/>
       <c r="G958" s="3" t="n"/>
-      <c r="H958" s="14" t="n"/>
+      <c r="H958" s="15" t="n"/>
     </row>
     <row r="959">
       <c r="A959" s="3" t="n"/>
@@ -16434,7 +16452,7 @@
       <c r="C959" s="3" t="n"/>
       <c r="F959" s="3" t="n"/>
       <c r="G959" s="3" t="n"/>
-      <c r="H959" s="14" t="n"/>
+      <c r="H959" s="15" t="n"/>
     </row>
     <row r="960">
       <c r="A960" s="3" t="n"/>
@@ -16442,7 +16460,7 @@
       <c r="C960" s="3" t="n"/>
       <c r="F960" s="3" t="n"/>
       <c r="G960" s="3" t="n"/>
-      <c r="H960" s="14" t="n"/>
+      <c r="H960" s="15" t="n"/>
     </row>
     <row r="961">
       <c r="A961" s="3" t="n"/>
@@ -16450,7 +16468,7 @@
       <c r="C961" s="3" t="n"/>
       <c r="F961" s="3" t="n"/>
       <c r="G961" s="3" t="n"/>
-      <c r="H961" s="14" t="n"/>
+      <c r="H961" s="15" t="n"/>
     </row>
     <row r="962">
       <c r="A962" s="3" t="n"/>
@@ -16458,7 +16476,7 @@
       <c r="C962" s="3" t="n"/>
       <c r="F962" s="3" t="n"/>
       <c r="G962" s="3" t="n"/>
-      <c r="H962" s="14" t="n"/>
+      <c r="H962" s="15" t="n"/>
     </row>
     <row r="963">
       <c r="A963" s="3" t="n"/>
@@ -16466,7 +16484,7 @@
       <c r="C963" s="3" t="n"/>
       <c r="F963" s="3" t="n"/>
       <c r="G963" s="3" t="n"/>
-      <c r="H963" s="14" t="n"/>
+      <c r="H963" s="15" t="n"/>
     </row>
     <row r="964">
       <c r="A964" s="3" t="n"/>
@@ -16474,7 +16492,7 @@
       <c r="C964" s="3" t="n"/>
       <c r="F964" s="3" t="n"/>
       <c r="G964" s="3" t="n"/>
-      <c r="H964" s="14" t="n"/>
+      <c r="H964" s="15" t="n"/>
     </row>
     <row r="965">
       <c r="A965" s="3" t="n"/>
@@ -16482,7 +16500,7 @@
       <c r="C965" s="3" t="n"/>
       <c r="F965" s="3" t="n"/>
       <c r="G965" s="3" t="n"/>
-      <c r="H965" s="14" t="n"/>
+      <c r="H965" s="15" t="n"/>
     </row>
     <row r="966">
       <c r="A966" s="3" t="n"/>
@@ -16490,7 +16508,7 @@
       <c r="C966" s="3" t="n"/>
       <c r="F966" s="3" t="n"/>
       <c r="G966" s="3" t="n"/>
-      <c r="H966" s="14" t="n"/>
+      <c r="H966" s="15" t="n"/>
     </row>
     <row r="967">
       <c r="A967" s="3" t="n"/>
@@ -16498,7 +16516,7 @@
       <c r="C967" s="3" t="n"/>
       <c r="F967" s="3" t="n"/>
       <c r="G967" s="3" t="n"/>
-      <c r="H967" s="14" t="n"/>
+      <c r="H967" s="15" t="n"/>
     </row>
     <row r="968">
       <c r="A968" s="3" t="n"/>
@@ -16506,7 +16524,7 @@
       <c r="C968" s="3" t="n"/>
       <c r="F968" s="3" t="n"/>
       <c r="G968" s="3" t="n"/>
-      <c r="H968" s="14" t="n"/>
+      <c r="H968" s="15" t="n"/>
     </row>
     <row r="969">
       <c r="A969" s="3" t="n"/>
@@ -16514,7 +16532,7 @@
       <c r="C969" s="3" t="n"/>
       <c r="F969" s="3" t="n"/>
       <c r="G969" s="3" t="n"/>
-      <c r="H969" s="14" t="n"/>
+      <c r="H969" s="15" t="n"/>
     </row>
     <row r="970">
       <c r="A970" s="3" t="n"/>
@@ -16522,7 +16540,7 @@
       <c r="C970" s="3" t="n"/>
       <c r="F970" s="3" t="n"/>
       <c r="G970" s="3" t="n"/>
-      <c r="H970" s="14" t="n"/>
+      <c r="H970" s="15" t="n"/>
     </row>
     <row r="971">
       <c r="A971" s="3" t="n"/>
@@ -16530,7 +16548,7 @@
       <c r="C971" s="3" t="n"/>
       <c r="F971" s="3" t="n"/>
       <c r="G971" s="3" t="n"/>
-      <c r="H971" s="14" t="n"/>
+      <c r="H971" s="15" t="n"/>
     </row>
     <row r="972">
       <c r="A972" s="3" t="n"/>
@@ -16538,7 +16556,7 @@
       <c r="C972" s="3" t="n"/>
       <c r="F972" s="3" t="n"/>
       <c r="G972" s="3" t="n"/>
-      <c r="H972" s="14" t="n"/>
+      <c r="H972" s="15" t="n"/>
     </row>
     <row r="973">
       <c r="A973" s="3" t="n"/>
@@ -16546,7 +16564,7 @@
       <c r="C973" s="3" t="n"/>
       <c r="F973" s="3" t="n"/>
       <c r="G973" s="3" t="n"/>
-      <c r="H973" s="14" t="n"/>
+      <c r="H973" s="15" t="n"/>
     </row>
     <row r="974">
       <c r="A974" s="3" t="n"/>
@@ -16554,7 +16572,7 @@
       <c r="C974" s="3" t="n"/>
       <c r="F974" s="3" t="n"/>
       <c r="G974" s="3" t="n"/>
-      <c r="H974" s="14" t="n"/>
+      <c r="H974" s="15" t="n"/>
     </row>
     <row r="975">
       <c r="A975" s="3" t="n"/>
@@ -16562,7 +16580,7 @@
       <c r="C975" s="3" t="n"/>
       <c r="F975" s="3" t="n"/>
       <c r="G975" s="3" t="n"/>
-      <c r="H975" s="14" t="n"/>
+      <c r="H975" s="15" t="n"/>
     </row>
     <row r="976">
       <c r="A976" s="3" t="n"/>
@@ -16570,7 +16588,7 @@
       <c r="C976" s="3" t="n"/>
       <c r="F976" s="3" t="n"/>
       <c r="G976" s="3" t="n"/>
-      <c r="H976" s="14" t="n"/>
+      <c r="H976" s="15" t="n"/>
     </row>
     <row r="977">
       <c r="A977" s="3" t="n"/>
@@ -16578,7 +16596,7 @@
       <c r="C977" s="3" t="n"/>
       <c r="F977" s="3" t="n"/>
       <c r="G977" s="3" t="n"/>
-      <c r="H977" s="14" t="n"/>
+      <c r="H977" s="15" t="n"/>
     </row>
     <row r="978">
       <c r="A978" s="3" t="n"/>
@@ -16586,7 +16604,7 @@
       <c r="C978" s="3" t="n"/>
       <c r="F978" s="3" t="n"/>
       <c r="G978" s="3" t="n"/>
-      <c r="H978" s="14" t="n"/>
+      <c r="H978" s="15" t="n"/>
     </row>
     <row r="979">
       <c r="A979" s="3" t="n"/>
@@ -16594,7 +16612,7 @@
       <c r="C979" s="3" t="n"/>
       <c r="F979" s="3" t="n"/>
       <c r="G979" s="3" t="n"/>
-      <c r="H979" s="14" t="n"/>
+      <c r="H979" s="15" t="n"/>
     </row>
     <row r="980">
       <c r="A980" s="3" t="n"/>
@@ -16602,7 +16620,7 @@
       <c r="C980" s="3" t="n"/>
       <c r="F980" s="3" t="n"/>
       <c r="G980" s="3" t="n"/>
-      <c r="H980" s="14" t="n"/>
+      <c r="H980" s="15" t="n"/>
     </row>
     <row r="981">
       <c r="A981" s="3" t="n"/>
@@ -16610,7 +16628,7 @@
       <c r="C981" s="3" t="n"/>
       <c r="F981" s="3" t="n"/>
       <c r="G981" s="3" t="n"/>
-      <c r="H981" s="14" t="n"/>
+      <c r="H981" s="15" t="n"/>
     </row>
     <row r="982">
       <c r="A982" s="3" t="n"/>
@@ -16618,7 +16636,7 @@
       <c r="C982" s="3" t="n"/>
       <c r="F982" s="3" t="n"/>
       <c r="G982" s="3" t="n"/>
-      <c r="H982" s="14" t="n"/>
+      <c r="H982" s="15" t="n"/>
     </row>
     <row r="983">
       <c r="A983" s="3" t="n"/>
@@ -16626,7 +16644,7 @@
       <c r="C983" s="3" t="n"/>
       <c r="F983" s="3" t="n"/>
       <c r="G983" s="3" t="n"/>
-      <c r="H983" s="14" t="n"/>
+      <c r="H983" s="15" t="n"/>
     </row>
     <row r="984">
       <c r="A984" s="3" t="n"/>
@@ -16634,7 +16652,7 @@
       <c r="C984" s="3" t="n"/>
       <c r="F984" s="3" t="n"/>
       <c r="G984" s="3" t="n"/>
-      <c r="H984" s="14" t="n"/>
+      <c r="H984" s="15" t="n"/>
     </row>
     <row r="985">
       <c r="A985" s="3" t="n"/>
@@ -16642,7 +16660,7 @@
       <c r="C985" s="3" t="n"/>
       <c r="F985" s="3" t="n"/>
       <c r="G985" s="3" t="n"/>
-      <c r="H985" s="14" t="n"/>
+      <c r="H985" s="15" t="n"/>
     </row>
     <row r="986">
       <c r="A986" s="3" t="n"/>
@@ -16650,7 +16668,7 @@
       <c r="C986" s="3" t="n"/>
       <c r="F986" s="3" t="n"/>
       <c r="G986" s="3" t="n"/>
-      <c r="H986" s="14" t="n"/>
+      <c r="H986" s="15" t="n"/>
     </row>
     <row r="987">
       <c r="A987" s="3" t="n"/>
@@ -16658,7 +16676,7 @@
       <c r="C987" s="3" t="n"/>
       <c r="F987" s="3" t="n"/>
       <c r="G987" s="3" t="n"/>
-      <c r="H987" s="14" t="n"/>
+      <c r="H987" s="15" t="n"/>
     </row>
     <row r="988">
       <c r="A988" s="3" t="n"/>
@@ -16666,7 +16684,7 @@
       <c r="C988" s="3" t="n"/>
       <c r="F988" s="3" t="n"/>
       <c r="G988" s="3" t="n"/>
-      <c r="H988" s="14" t="n"/>
+      <c r="H988" s="15" t="n"/>
     </row>
     <row r="989">
       <c r="A989" s="3" t="n"/>
@@ -16674,7 +16692,7 @@
       <c r="C989" s="3" t="n"/>
       <c r="F989" s="3" t="n"/>
       <c r="G989" s="3" t="n"/>
-      <c r="H989" s="14" t="n"/>
+      <c r="H989" s="15" t="n"/>
     </row>
     <row r="990">
       <c r="A990" s="3" t="n"/>
@@ -16682,7 +16700,7 @@
       <c r="C990" s="3" t="n"/>
       <c r="F990" s="3" t="n"/>
       <c r="G990" s="3" t="n"/>
-      <c r="H990" s="14" t="n"/>
+      <c r="H990" s="15" t="n"/>
     </row>
     <row r="991">
       <c r="A991" s="3" t="n"/>
@@ -16690,7 +16708,7 @@
       <c r="C991" s="3" t="n"/>
       <c r="F991" s="3" t="n"/>
       <c r="G991" s="3" t="n"/>
-      <c r="H991" s="14" t="n"/>
+      <c r="H991" s="15" t="n"/>
     </row>
     <row r="992">
       <c r="A992" s="3" t="n"/>
@@ -16698,7 +16716,7 @@
       <c r="C992" s="3" t="n"/>
       <c r="F992" s="3" t="n"/>
       <c r="G992" s="3" t="n"/>
-      <c r="H992" s="14" t="n"/>
+      <c r="H992" s="15" t="n"/>
     </row>
     <row r="993">
       <c r="A993" s="3" t="n"/>
@@ -16706,7 +16724,7 @@
       <c r="C993" s="3" t="n"/>
       <c r="F993" s="3" t="n"/>
       <c r="G993" s="3" t="n"/>
-      <c r="H993" s="14" t="n"/>
+      <c r="H993" s="15" t="n"/>
     </row>
     <row r="994">
       <c r="A994" s="3" t="n"/>
@@ -16714,7 +16732,7 @@
       <c r="C994" s="3" t="n"/>
       <c r="F994" s="3" t="n"/>
       <c r="G994" s="3" t="n"/>
-      <c r="H994" s="14" t="n"/>
+      <c r="H994" s="15" t="n"/>
     </row>
     <row r="995">
       <c r="A995" s="3" t="n"/>
@@ -16722,7 +16740,7 @@
       <c r="C995" s="3" t="n"/>
       <c r="F995" s="3" t="n"/>
       <c r="G995" s="3" t="n"/>
-      <c r="H995" s="14" t="n"/>
+      <c r="H995" s="15" t="n"/>
     </row>
     <row r="996">
       <c r="A996" s="3" t="n"/>
@@ -16730,7 +16748,7 @@
       <c r="C996" s="3" t="n"/>
       <c r="F996" s="3" t="n"/>
       <c r="G996" s="3" t="n"/>
-      <c r="H996" s="14" t="n"/>
+      <c r="H996" s="15" t="n"/>
     </row>
     <row r="997">
       <c r="A997" s="3" t="n"/>
@@ -16738,7 +16756,7 @@
       <c r="C997" s="3" t="n"/>
       <c r="F997" s="3" t="n"/>
       <c r="G997" s="3" t="n"/>
-      <c r="H997" s="14" t="n"/>
+      <c r="H997" s="15" t="n"/>
     </row>
     <row r="998">
       <c r="A998" s="3" t="n"/>
@@ -16746,7 +16764,7 @@
       <c r="C998" s="3" t="n"/>
       <c r="F998" s="3" t="n"/>
       <c r="G998" s="3" t="n"/>
-      <c r="H998" s="14" t="n"/>
+      <c r="H998" s="15" t="n"/>
     </row>
     <row r="999">
       <c r="A999" s="3" t="n"/>
@@ -16754,7 +16772,7 @@
       <c r="C999" s="3" t="n"/>
       <c r="F999" s="3" t="n"/>
       <c r="G999" s="3" t="n"/>
-      <c r="H999" s="14" t="n"/>
+      <c r="H999" s="15" t="n"/>
     </row>
     <row r="1000">
       <c r="A1000" s="3" t="n"/>
@@ -16762,7 +16780,7 @@
       <c r="C1000" s="3" t="n"/>
       <c r="F1000" s="3" t="n"/>
       <c r="G1000" s="3" t="n"/>
-      <c r="H1000" s="14" t="n"/>
+      <c r="H1000" s="15" t="n"/>
     </row>
     <row r="1001">
       <c r="A1001" s="3" t="n"/>
@@ -16770,7 +16788,7 @@
       <c r="C1001" s="3" t="n"/>
       <c r="F1001" s="3" t="n"/>
       <c r="G1001" s="3" t="n"/>
-      <c r="H1001" s="14" t="n"/>
+      <c r="H1001" s="15" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
@@ -16795,7 +16813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16854,376 +16872,383 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>NEVER put Social Security numbers, bank account or routing numbers in this file. RoadCoda has no place for them and does not store them: the upload ignores them, and any file sent to RoadCoda that contains them is deleted. If you include them anyway, you do so at your own risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Column</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Required?</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>What to enter</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Allowed values</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Full Name</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>As it should appear in RoadCoda.</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Donna Reilly</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Their work email. RoadCoda sends a set-password invitation here, after you confirm.</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>donna@yourcompany.example.com</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Sets which screens they get; you can fine-tune each person afterwards on the Users screen.</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Billing</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>Owner, Dispatcher, Billing, Safety, Payroll, Accountant</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Super User (Y/N)</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr"/>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr"/>
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Y lets them manage other users and reopen locked invoices and pay weeks.</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Y, N</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr"/>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr"/>
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Job title.</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>Billing Manager</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Employee #</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr"/>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr"/>
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Kept as text.</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>00118</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr"/>
-    </row>
-    <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>OFFICE PAY TAB (optional, red): only if you use RoadCoda's office payroll. Fill it in and upload it yourself from inside RoadCoda (Office payroll screen). Please DON'T email a file with pay rates or salaries to anyone, RoadCoda included.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>Column (pay tab)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>Required?</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>What to enter</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D22" s="17" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>Allowed values</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>Full Name</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>Must match the name on the first tab.</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Donna Reilly</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="E23" s="19" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>Must match the email on the first tab.</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>donna@yourcompany.example.com</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="E24" s="19" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>Pay Type</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>Hourly or Salary.</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>Hourly</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="E25" s="19" t="inlineStr">
         <is>
           <t>Hourly, Salary</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>Hourly Rate</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr"/>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr"/>
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>For hourly staff, dollars per hour.</t>
         </is>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D26" s="19" t="n">
         <v>26.5</v>
       </c>
-      <c r="E24" s="18" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="E26" s="19" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Annual Salary</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr"/>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr"/>
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>For salaried staff, dollars per year.</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr"/>
-      <c r="E25" s="18" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr"/>
+      <c r="E27" s="19" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>Overtime Eligible (Y/N)</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr"/>
-      <c r="C26" s="18" t="inlineStr"/>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr"/>
+      <c r="C28" s="19" t="inlineStr"/>
+      <c r="D28" s="19" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
+      <c r="E28" s="19" t="inlineStr">
         <is>
           <t>Y, N</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>Time Entry</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr"/>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr"/>
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>Typed = office types hours; Clock = they clock in on RoadCoda; None = salaried, no hours.</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
+      <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Clock</t>
         </is>
       </c>
-      <c r="E27" s="18" t="inlineStr">
+      <c r="E29" s="19" t="inlineStr">
         <is>
           <t>Typed, Clock, None</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>Hire Date</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr"/>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr"/>
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>MM/DD/YYYY.</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>06/01/2022</t>
         </is>
       </c>
-      <c r="E28" s="18" t="inlineStr"/>
+      <c r="E30" s="19" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A9:E9"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
